--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="965">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2329,943 +2329,606 @@
     <t>XC392</t>
   </si>
   <si>
-    <t>XC001</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>1*1半光横条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*2*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50S*50S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*40S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*215*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75T400消 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*5*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>X字格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条2*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4+28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>238克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条1*4</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4+38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯200米克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T400横条1*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75闪电斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*2T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克385</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克370</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克350</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*210</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>半光大猫眼</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100半低*150半T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D低弹*50T800 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>23*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*57</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50DT8*50DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T8五面埋伏</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T800双链条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克265</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>空变T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯370克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光75DT800 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.5*4*48</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*40S+150D T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯188克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*51</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*35S+150DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>天丝棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*3*32</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>80S*三合一</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>270-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>210-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>加厚钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.5*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>230-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯300克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>张：18962500118  盛泽温州商区13幢1号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <t>XC001</t>
+  </si>
+  <si>
+    <t>1*1半光横条</t>
+  </si>
+  <si>
+    <t>22*3*38</t>
   </si>
   <si>
     <t>22*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>消半光珍珠点50*50*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*2*25</t>
+  </si>
+  <si>
+    <t>17*3*28</t>
   </si>
   <si>
     <t>17*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>25梭T400无捻牛津</t>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>26梭T400无捻牛津</t>
+  </si>
+  <si>
+    <t>17*2*26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+  </si>
+  <si>
+    <t>17*2*30</t>
+  </si>
+  <si>
+    <t>50S*50S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+  </si>
+  <si>
+    <t>40S*40S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50S*75D 酷丝棉绮兵</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
   </si>
   <si>
     <t>XC186</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
   </si>
   <si>
     <t>40S*75DT400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+  </si>
+  <si>
+    <t>100*150T8 4/2斜</t>
+  </si>
+  <si>
+    <t>17*4*215*40</t>
   </si>
   <si>
     <t>100D*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*150T400 消3/3斜</t>
+  </si>
+  <si>
+    <t>75*75T400消 3/3斜</t>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*4*46</t>
+  </si>
+  <si>
+    <t>75*75 消光2/2 斜</t>
+  </si>
+  <si>
+    <t>17*4*43</t>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75-T800消光骑士斜</t>
   </si>
   <si>
     <t>75消*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>19*5*45</t>
+  </si>
+  <si>
+    <t>19*3*39</t>
+  </si>
+  <si>
+    <t>X字格</t>
+  </si>
+  <si>
+    <t>16*4*46</t>
+  </si>
+  <si>
+    <t>T400横条2*1</t>
+  </si>
+  <si>
+    <t>16*4+28</t>
+  </si>
+  <si>
+    <t>238克</t>
+  </si>
+  <si>
+    <t>T400横条1*4</t>
+  </si>
+  <si>
+    <t>17*4+38</t>
+  </si>
+  <si>
+    <t>白坯200米克</t>
+  </si>
+  <si>
+    <t>T400横条1*1</t>
+  </si>
+  <si>
+    <t>16*4*30</t>
+  </si>
+  <si>
+    <t>40S*75闪电斜</t>
   </si>
   <si>
     <t>18*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75</t>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300 3/2变化斜</t>
+  </si>
+  <si>
+    <t>13.5*4*28</t>
+  </si>
+  <si>
+    <t>40S*150*2T400</t>
+  </si>
+  <si>
+    <t>米克385</t>
+  </si>
+  <si>
+    <t>100D半光*35S-3/3斜</t>
   </si>
   <si>
     <t>16*4*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平0.5格</t>
   </si>
   <si>
     <t>17*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*35S</t>
+  </si>
+  <si>
+    <t>米克370</t>
   </si>
   <si>
     <t>120D扁平3/3斜-44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*44</t>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*45</t>
   </si>
   <si>
     <t>米克375</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D消光多乐3/3斜</t>
   </si>
   <si>
     <t>15*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克300</t>
+  </si>
+  <si>
+    <t>120D扁平1/2斜</t>
   </si>
   <si>
     <t>17*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克350</t>
+  </si>
+  <si>
+    <t>120D扁平T800变化斜</t>
   </si>
   <si>
     <t>17*4*29</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*150T800</t>
   </si>
   <si>
     <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
   </si>
   <si>
     <t>13.5*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/1斜 31</t>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300 酷丝棉3/2斜</t>
+  </si>
+  <si>
+    <t>13.5*4*27</t>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*300酷丝绵珍珠点</t>
   </si>
   <si>
     <t>40S*150*300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克368</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*75双线格酷丝绵</t>
+  </si>
+  <si>
+    <t>75 T800半光0.5格</t>
+  </si>
+  <si>
+    <t>75*75*210</t>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*2*40</t>
+  </si>
+  <si>
+    <t>半光大猫眼</t>
+  </si>
+  <si>
+    <t>100半低*150半T800</t>
+  </si>
+  <si>
+    <t>50D低弹*50T800 平纹</t>
+  </si>
+  <si>
+    <t>23*2*40</t>
   </si>
   <si>
     <t>30D T8 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>30*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*57</t>
+  </si>
+  <si>
+    <t>75D经纬T8平纹</t>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
   </si>
   <si>
     <t>21*3*53</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50DT8*50DT8</t>
+  </si>
+  <si>
+    <t>T8五面埋伏</t>
+  </si>
+  <si>
+    <t>14*4*38</t>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50D*50D*100D T800</t>
+  </si>
+  <si>
+    <t>T800双链条</t>
+  </si>
+  <si>
+    <t>米克265</t>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*26</t>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*4*38</t>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>空变T8平纹</t>
+  </si>
+  <si>
+    <t>40S*75T8酷丝棉3/1.超钛棉</t>
   </si>
   <si>
     <t>17.5*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T800</t>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*4*27</t>
   </si>
   <si>
     <t>40S*150*2-T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯370克</t>
+  </si>
+  <si>
+    <t>100D消光75DT800 3/3斜</t>
+  </si>
+  <si>
+    <t>15.5*4*48</t>
+  </si>
+  <si>
+    <t>100*75T8</t>
   </si>
   <si>
     <t>米克250</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*40S+150D T8</t>
+  </si>
+  <si>
+    <t>白坯188克</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斜纹毛巾底 </t>
+  </si>
+  <si>
+    <t>13.5*4*51</t>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫眼酷丝绵(东风)</t>
+  </si>
+  <si>
+    <t>40S*35S*2</t>
+  </si>
+  <si>
+    <t>白坯365克</t>
   </si>
   <si>
     <t>网纹3/3-180</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*35S+150DT8</t>
+  </si>
+  <si>
+    <t>白坯300克</t>
   </si>
   <si>
     <t>天丝棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*3*32</t>
+  </si>
+  <si>
+    <t>80S*三合一</t>
   </si>
   <si>
     <t>白坯195克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯368克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*31</t>
+  </si>
+  <si>
+    <t>270-钛金棉</t>
+  </si>
+  <si>
+    <t>白坯360克</t>
   </si>
   <si>
     <t>生态棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-钛金棉</t>
   </si>
   <si>
     <t>17*3*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>加厚钛金棉</t>
+  </si>
+  <si>
+    <t>15.5*4*30</t>
   </si>
   <si>
     <t>白坯390克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*30S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>230-钛金棉</t>
   </si>
   <si>
     <t xml:space="preserve">生态棉 加厚 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*31</t>
   </si>
   <si>
     <t>270单股钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*18S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>登山布</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>12.5*4*215*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75*450</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10克</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯310克</t>
   </si>
   <si>
     <t>40*300平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*24</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300D</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3338,13 +3001,6 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -4150,16 +3806,16 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>889</v>
+        <v>4</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4179,7 +3835,7 @@
         <v>697</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>888</v>
+        <v>767</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.15">
@@ -4846,7 +4502,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4871,7 +4527,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>890</v>
+        <v>771</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -5159,7 +4815,7 @@
         <v>165</v>
       </c>
       <c r="H41" s="10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I41" s="11"/>
     </row>
@@ -5318,7 +4974,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>891</v>
+        <v>772</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>116</v>
@@ -5523,7 +5179,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>134</v>
@@ -6050,7 +5706,7 @@
         <v>192</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>892</v>
+        <v>73</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>143</v>
@@ -6788,7 +6444,7 @@
         <v>165</v>
       </c>
       <c r="H106" s="22">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I106" s="11"/>
     </row>
@@ -7400,7 +7056,7 @@
         <v>329</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>147</v>
@@ -8019,7 +7675,7 @@
         <v>220</v>
       </c>
       <c r="H155" s="10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I155" s="11"/>
     </row>
@@ -8085,7 +7741,7 @@
         <v>402</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>893</v>
+        <v>775</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>392</v>
@@ -8159,7 +7815,7 @@
         <v>410</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>411</v>
@@ -8177,7 +7833,7 @@
         <v>208</v>
       </c>
       <c r="H161" s="22">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I161" s="11"/>
     </row>
@@ -8231,7 +7887,7 @@
         <v>208</v>
       </c>
       <c r="H163" s="22">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="I163" s="11"/>
     </row>
@@ -8240,7 +7896,7 @@
         <v>419</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>894</v>
+        <v>777</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>420</v>
@@ -8267,10 +7923,10 @@
         <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>412</v>
@@ -8285,7 +7941,7 @@
         <v>208</v>
       </c>
       <c r="H165" s="22">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I165" s="11"/>
     </row>
@@ -8307,13 +7963,13 @@
         <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8334,13 +7990,13 @@
         <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>895</v>
+        <v>415</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8361,7 +8017,7 @@
         <v>425</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>426</v>
@@ -8379,7 +8035,7 @@
         <v>208</v>
       </c>
       <c r="H169" s="18">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I169" s="32"/>
     </row>
@@ -8388,7 +8044,7 @@
         <v>428</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>429</v>
@@ -8415,7 +8071,7 @@
         <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>237</v>
@@ -8469,7 +8125,7 @@
         <v>433</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>896</v>
+        <v>788</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>434</v>
@@ -8496,7 +8152,7 @@
         <v>436</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>897</v>
+        <v>789</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>437</v>
@@ -8514,7 +8170,7 @@
         <v>215</v>
       </c>
       <c r="H174" s="32">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="I174" s="32"/>
     </row>
@@ -8523,7 +8179,7 @@
         <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>898</v>
+        <v>790</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8541,7 +8197,7 @@
         <v>215</v>
       </c>
       <c r="H175" s="32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I175" s="32"/>
     </row>
@@ -8568,7 +8224,7 @@
         <v>215</v>
       </c>
       <c r="H176" s="18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I176" s="32"/>
     </row>
@@ -8604,7 +8260,7 @@
         <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>418</v>
@@ -8658,7 +8314,7 @@
         <v>448</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>449</v>
@@ -8685,7 +8341,7 @@
         <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>899</v>
+        <v>793</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>443</v>
@@ -8712,7 +8368,7 @@
         <v>451</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>900</v>
+        <v>794</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>308</v>
@@ -8730,7 +8386,7 @@
         <v>215</v>
       </c>
       <c r="H182" s="34">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I182" s="11"/>
     </row>
@@ -8739,7 +8395,7 @@
         <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>308</v>
@@ -8757,7 +8413,7 @@
         <v>215</v>
       </c>
       <c r="H183" s="34">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I183" s="11"/>
     </row>
@@ -8793,13 +8449,13 @@
         <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>786</v>
+        <v>796</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>787</v>
+        <v>443</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>901</v>
+        <v>427</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8820,7 +8476,7 @@
         <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>308</v>
@@ -8838,19 +8494,19 @@
         <v>215</v>
       </c>
       <c r="H186" s="34">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I186" s="11"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A187" s="9" t="s">
-        <v>902</v>
+        <v>798</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>789</v>
+        <v>237</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>435</v>
@@ -8865,7 +8521,7 @@
         <v>215</v>
       </c>
       <c r="H187" s="18">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I187" s="11"/>
     </row>
@@ -8874,13 +8530,13 @@
         <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>791</v>
+        <v>271</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>903</v>
+        <v>800</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8901,7 +8557,7 @@
         <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>443</v>
@@ -8919,7 +8575,7 @@
         <v>215</v>
       </c>
       <c r="H189" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I189" s="11"/>
     </row>
@@ -8928,13 +8584,13 @@
         <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>793</v>
+        <v>802</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>904</v>
+        <v>804</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8955,10 +8611,10 @@
         <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>905</v>
+        <v>790</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>789</v>
+        <v>237</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>435</v>
@@ -8973,7 +8629,7 @@
         <v>215</v>
       </c>
       <c r="H191" s="32">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I191" s="11"/>
     </row>
@@ -9008,10 +8664,10 @@
         <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>796</v>
+        <v>384</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>147</v>
@@ -9035,7 +8691,7 @@
         <v>467</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>797</v>
+        <v>806</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>468</v>
@@ -9062,10 +8718,10 @@
         <v>469</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>906</v>
+        <v>807</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>470</v>
@@ -9089,10 +8745,10 @@
         <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>799</v>
+        <v>809</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>907</v>
+        <v>810</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>385</v>
@@ -9116,7 +8772,7 @@
         <v>472</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>908</v>
+        <v>811</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>473</v>
@@ -9134,7 +8790,7 @@
         <v>215</v>
       </c>
       <c r="H198" s="45">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I198" s="37"/>
     </row>
@@ -9143,13 +8799,13 @@
         <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>801</v>
+        <v>400</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>909</v>
+        <v>813</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -9161,7 +8817,7 @@
         <v>215</v>
       </c>
       <c r="H199" s="45">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I199" s="37"/>
     </row>
@@ -9327,7 +8983,7 @@
         <v>494</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9342,7 +8998,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I208" s="11"/>
     </row>
@@ -9390,7 +9046,7 @@
         <v>499</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9412,10 +9068,10 @@
         <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>143</v>
@@ -9428,7 +9084,7 @@
         <v>175</v>
       </c>
       <c r="H212" s="35">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I212" s="37"/>
     </row>
@@ -9467,7 +9123,7 @@
         <v>505</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>143</v>
@@ -9580,10 +9236,10 @@
         <v>517</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="D220" s="49" t="s">
         <v>518</v>
@@ -9598,10 +9254,10 @@
         <v>215</v>
       </c>
       <c r="H220" s="10">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.15">
@@ -9609,13 +9265,13 @@
         <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="D221" s="49" t="s">
-        <v>889</v>
+        <v>4</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9630,7 +9286,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.15">
@@ -9638,13 +9294,13 @@
         <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>814</v>
+        <v>518</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9692,13 +9348,13 @@
         <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>910</v>
+        <v>827</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9746,10 +9402,10 @@
         <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>911</v>
+        <v>829</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>789</v>
+        <v>237</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>435</v>
@@ -9764,7 +9420,7 @@
         <v>215</v>
       </c>
       <c r="H226" s="35">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I226" s="37"/>
     </row>
@@ -9773,10 +9429,10 @@
         <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>912</v>
+        <v>830</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>789</v>
+        <v>237</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>435</v>
@@ -9791,7 +9447,7 @@
         <v>215</v>
       </c>
       <c r="H227" s="35">
-        <v>4.5999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I227" s="37"/>
     </row>
@@ -9818,7 +9474,7 @@
         <v>215</v>
       </c>
       <c r="H228" s="35">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I228" s="11"/>
     </row>
@@ -9845,7 +9501,7 @@
         <v>215</v>
       </c>
       <c r="H229" s="35">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I229" s="11"/>
     </row>
@@ -9872,7 +9528,7 @@
         <v>215</v>
       </c>
       <c r="H230" s="51">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I230" s="11"/>
     </row>
@@ -9934,13 +9590,13 @@
         <v>542</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>818</v>
+        <v>832</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="E234" s="52">
         <v>190</v>
@@ -9955,7 +9611,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" s="54" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.15">
@@ -9963,13 +9619,13 @@
         <v>543</v>
       </c>
       <c r="B235" s="51" t="s">
-        <v>821</v>
+        <v>835</v>
       </c>
       <c r="C235" s="51" t="s">
-        <v>913</v>
+        <v>836</v>
       </c>
       <c r="D235" s="51" t="s">
-        <v>914</v>
+        <v>837</v>
       </c>
       <c r="E235" s="51">
         <v>155</v>
@@ -10005,13 +9661,13 @@
         <v>546</v>
       </c>
       <c r="B237" s="51" t="s">
-        <v>915</v>
+        <v>838</v>
       </c>
       <c r="C237" s="51" t="s">
         <v>547</v>
       </c>
       <c r="D237" s="51" t="s">
-        <v>916</v>
+        <v>839</v>
       </c>
       <c r="E237" s="51">
         <v>155</v>
@@ -10034,13 +9690,13 @@
         <v>548</v>
       </c>
       <c r="B238" s="51" t="s">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="C238" s="51" t="s">
-        <v>917</v>
+        <v>841</v>
       </c>
       <c r="D238" s="51" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="E238" s="52">
         <v>190</v>
@@ -10055,7 +9711,7 @@
         <v>5.7</v>
       </c>
       <c r="I238" s="54" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.15">
@@ -10063,13 +9719,13 @@
         <v>549</v>
       </c>
       <c r="B239" s="51" t="s">
-        <v>918</v>
+        <v>844</v>
       </c>
       <c r="C239" s="51" t="s">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="D239" s="51" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="E239" s="52">
         <v>180</v>
@@ -10084,7 +9740,7 @@
         <v>5.7</v>
       </c>
       <c r="I239" s="54" t="s">
-        <v>824</v>
+        <v>843</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.15">
@@ -10092,13 +9748,13 @@
         <v>550</v>
       </c>
       <c r="B240" s="51" t="s">
-        <v>919</v>
+        <v>846</v>
       </c>
       <c r="C240" s="51" t="s">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="D240" s="51" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="E240" s="52">
         <v>190</v>
@@ -10110,10 +9766,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="35">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I240" s="54" t="s">
-        <v>920</v>
+        <v>848</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.15">
@@ -10121,10 +9777,10 @@
         <v>551</v>
       </c>
       <c r="B241" s="51" t="s">
-        <v>826</v>
+        <v>849</v>
       </c>
       <c r="C241" s="51" t="s">
-        <v>921</v>
+        <v>850</v>
       </c>
       <c r="D241" s="11" t="s">
         <v>552</v>
@@ -10142,7 +9798,7 @@
         <v>5.3</v>
       </c>
       <c r="I241" s="55" t="s">
-        <v>827</v>
+        <v>851</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.15">
@@ -10150,13 +9806,13 @@
         <v>553</v>
       </c>
       <c r="B242" s="51" t="s">
-        <v>828</v>
+        <v>852</v>
       </c>
       <c r="C242" s="51" t="s">
-        <v>922</v>
+        <v>853</v>
       </c>
       <c r="D242" s="51" t="s">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="E242" s="52">
         <v>160</v>
@@ -10171,7 +9827,7 @@
         <v>5.4</v>
       </c>
       <c r="I242" s="54" t="s">
-        <v>829</v>
+        <v>854</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.15">
@@ -10179,13 +9835,13 @@
         <v>554</v>
       </c>
       <c r="B243" s="51" t="s">
-        <v>830</v>
+        <v>855</v>
       </c>
       <c r="C243" s="51" t="s">
-        <v>923</v>
+        <v>856</v>
       </c>
       <c r="D243" s="51" t="s">
-        <v>831</v>
+        <v>857</v>
       </c>
       <c r="E243" s="52">
         <v>190</v>
@@ -10200,7 +9856,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="54" t="s">
-        <v>924</v>
+        <v>858</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.15">
@@ -10208,18 +9864,20 @@
         <v>555</v>
       </c>
       <c r="B244" s="51" t="s">
-        <v>925</v>
+        <v>859</v>
       </c>
       <c r="C244" s="51" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="D244" s="51" t="s">
-        <v>926</v>
+        <v>857</v>
       </c>
       <c r="E244" s="51">
-        <v>150</v>
-      </c>
-      <c r="F244" s="38"/>
+        <v>110</v>
+      </c>
+      <c r="F244" s="38">
+        <v>160</v>
+      </c>
       <c r="G244" s="55">
         <v>220</v>
       </c>
@@ -10246,13 +9904,13 @@
         <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>927</v>
+        <v>862</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>928</v>
+        <v>427</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10273,7 +9931,7 @@
         <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>835</v>
+        <v>863</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>527</v>
@@ -10291,7 +9949,7 @@
         <v>215</v>
       </c>
       <c r="H247" s="18">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I247" s="56"/>
     </row>
@@ -10300,7 +9958,7 @@
         <v>559</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>929</v>
+        <v>864</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>560</v>
@@ -10318,7 +9976,7 @@
         <v>215</v>
       </c>
       <c r="H248" s="18">
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I248" s="57"/>
     </row>
@@ -10327,10 +9985,10 @@
         <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>930</v>
+        <v>865</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>836</v>
+        <v>437</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>427</v>
@@ -10354,7 +10012,7 @@
         <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>837</v>
+        <v>866</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>152</v>
@@ -10381,7 +10039,7 @@
         <v>563</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>931</v>
+        <v>867</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>564</v>
@@ -10408,10 +10066,10 @@
         <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>836</v>
+        <v>437</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>427</v>
@@ -10435,7 +10093,7 @@
         <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>932</v>
+        <v>869</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>564</v>
@@ -10462,13 +10120,13 @@
         <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>839</v>
+        <v>870</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>840</v>
+        <v>871</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10480,10 +10138,10 @@
         <v>215</v>
       </c>
       <c r="H254" s="18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I254" s="54" t="s">
-        <v>832</v>
+        <v>858</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.15">
@@ -10491,7 +10149,7 @@
         <v>568</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>933</v>
+        <v>872</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>569</v>
@@ -10518,13 +10176,13 @@
         <v>570</v>
       </c>
       <c r="B256" s="52" t="s">
-        <v>841</v>
+        <v>873</v>
       </c>
       <c r="C256" s="18" t="s">
-        <v>934</v>
+        <v>160</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>935</v>
+        <v>874</v>
       </c>
       <c r="E256" s="52">
         <v>190</v>
@@ -10536,10 +10194,10 @@
         <v>215</v>
       </c>
       <c r="H256" s="60">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I256" s="54" t="s">
-        <v>936</v>
+        <v>875</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.15">
@@ -10547,13 +10205,13 @@
         <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>937</v>
+        <v>876</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>938</v>
+        <v>320</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>901</v>
+        <v>427</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10565,7 +10223,7 @@
         <v>215</v>
       </c>
       <c r="H257" s="60">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I257" s="60"/>
     </row>
@@ -10574,7 +10232,7 @@
         <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>837</v>
+        <v>866</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>152</v>
@@ -10633,7 +10291,7 @@
         <v>577</v>
       </c>
       <c r="D261" s="49" t="s">
-        <v>939</v>
+        <v>877</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10645,7 +10303,7 @@
         <v>210</v>
       </c>
       <c r="H261" s="10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I261" s="60"/>
     </row>
@@ -10654,7 +10312,7 @@
         <v>578</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>579</v>
@@ -10672,7 +10330,7 @@
         <v>208</v>
       </c>
       <c r="H262" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I262" s="60"/>
     </row>
@@ -10699,7 +10357,7 @@
         <v>208</v>
       </c>
       <c r="H263" s="27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I263" s="60"/>
     </row>
@@ -10753,7 +10411,7 @@
         <v>215</v>
       </c>
       <c r="H265" s="35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I265" s="60"/>
     </row>
@@ -10762,13 +10420,13 @@
         <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>843</v>
+        <v>879</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>940</v>
+        <v>860</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>844</v>
+        <v>880</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10789,13 +10447,13 @@
         <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>941</v>
+        <v>881</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>845</v>
+        <v>882</v>
       </c>
       <c r="D267" s="49" t="s">
-        <v>846</v>
+        <v>143</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10960,13 +10618,13 @@
         <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>847</v>
+        <v>883</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>942</v>
+        <v>547</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>848</v>
+        <v>884</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10987,10 +10645,10 @@
         <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>849</v>
+        <v>885</v>
       </c>
       <c r="C279" s="49" t="s">
-        <v>850</v>
+        <v>886</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>143</v>
@@ -11014,13 +10672,13 @@
         <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>943</v>
+        <v>887</v>
       </c>
       <c r="C280" s="49" t="s">
-        <v>851</v>
+        <v>888</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>944</v>
+        <v>487</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -11066,7 +10724,7 @@
         <v>614</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="C282" s="49" t="s">
         <v>615</v>
@@ -11093,10 +10751,10 @@
         <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>945</v>
+        <v>890</v>
       </c>
       <c r="C283" s="49" t="s">
-        <v>946</v>
+        <v>891</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11120,13 +10778,13 @@
         <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>853</v>
+        <v>892</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>947</v>
+        <v>893</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>854</v>
+        <v>894</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11153,7 +10811,7 @@
         <v>620</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>854</v>
+        <v>894</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11174,10 +10832,10 @@
         <v>621</v>
       </c>
       <c r="B286" s="52" t="s">
-        <v>855</v>
+        <v>895</v>
       </c>
       <c r="C286" s="52" t="s">
-        <v>856</v>
+        <v>896</v>
       </c>
       <c r="D286" s="52" t="s">
         <v>622</v>
@@ -11201,13 +10859,13 @@
         <v>623</v>
       </c>
       <c r="B287" s="52" t="s">
-        <v>948</v>
+        <v>897</v>
       </c>
       <c r="C287" s="52" t="s">
-        <v>949</v>
+        <v>898</v>
       </c>
       <c r="D287" s="52" t="s">
-        <v>857</v>
+        <v>899</v>
       </c>
       <c r="E287" s="52">
         <v>88</v>
@@ -11228,7 +10886,7 @@
         <v>624</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>858</v>
+        <v>900</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>625</v>
@@ -11276,7 +10934,7 @@
         <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>859</v>
+        <v>901</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.15">
@@ -11311,10 +10969,10 @@
         <v>633</v>
       </c>
       <c r="B291" s="64" t="s">
-        <v>950</v>
+        <v>902</v>
       </c>
       <c r="C291" s="64" t="s">
-        <v>860</v>
+        <v>903</v>
       </c>
       <c r="D291" s="64" t="s">
         <v>634</v>
@@ -11338,7 +10996,7 @@
         <v>635</v>
       </c>
       <c r="B292" s="64" t="s">
-        <v>951</v>
+        <v>904</v>
       </c>
       <c r="C292" s="64" t="s">
         <v>636</v>
@@ -11365,10 +11023,10 @@
         <v>638</v>
       </c>
       <c r="B293" s="65" t="s">
-        <v>952</v>
+        <v>905</v>
       </c>
       <c r="C293" s="64" t="s">
-        <v>861</v>
+        <v>906</v>
       </c>
       <c r="D293" s="64" t="s">
         <v>39</v>
@@ -11392,13 +11050,13 @@
         <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>953</v>
+        <v>907</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>787</v>
+        <v>443</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>954</v>
+        <v>908</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11419,7 +11077,7 @@
         <v>640</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>862</v>
+        <v>909</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>641</v>
@@ -11467,13 +11125,13 @@
         <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>955</v>
+        <v>911</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>864</v>
+        <v>912</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11494,13 +11152,13 @@
         <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>956</v>
+        <v>913</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>865</v>
+        <v>914</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>957</v>
+        <v>915</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11515,7 +11173,7 @@
         <v>5.8</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>866</v>
+        <v>916</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.15">
@@ -11523,13 +11181,13 @@
         <v>649</v>
       </c>
       <c r="B299" s="51" t="s">
-        <v>867</v>
+        <v>917</v>
       </c>
       <c r="C299" s="51" t="s">
-        <v>868</v>
+        <v>918</v>
       </c>
       <c r="D299" s="51" t="s">
-        <v>869</v>
+        <v>919</v>
       </c>
       <c r="E299" s="51">
         <v>124</v>
@@ -11541,10 +11199,10 @@
         <v>218</v>
       </c>
       <c r="H299" s="51">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I299" s="55" t="s">
-        <v>958</v>
+        <v>920</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.15">
@@ -11578,13 +11236,13 @@
         <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>959</v>
+        <v>921</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>960</v>
+        <v>922</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>870</v>
+        <v>923</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11611,7 +11269,7 @@
         <v>655</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>870</v>
+        <v>923</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11635,7 +11293,7 @@
         <v>657</v>
       </c>
       <c r="C304" s="64" t="s">
-        <v>961</v>
+        <v>250</v>
       </c>
       <c r="D304" s="64" t="s">
         <v>658</v>
@@ -11653,7 +11311,7 @@
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>871</v>
+        <v>924</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.15">
@@ -11661,13 +11319,13 @@
         <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>872</v>
+        <v>925</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>873</v>
+        <v>926</v>
       </c>
       <c r="D305" s="18" t="s">
-        <v>962</v>
+        <v>927</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11679,7 +11337,7 @@
         <v>225</v>
       </c>
       <c r="H305" s="61">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I305" s="61"/>
     </row>
@@ -11687,14 +11345,30 @@
       <c r="A306" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="B306" s="36"/>
-      <c r="C306" s="36"/>
-      <c r="D306" s="36"/>
-      <c r="E306" s="36"/>
-      <c r="F306" s="36"/>
-      <c r="G306" s="36"/>
-      <c r="H306" s="61"/>
-      <c r="I306" s="61"/>
+      <c r="B306" s="36" t="s">
+        <v>928</v>
+      </c>
+      <c r="C306" s="36" t="s">
+        <v>871</v>
+      </c>
+      <c r="D306" s="36" t="s">
+        <v>929</v>
+      </c>
+      <c r="E306" s="36">
+        <v>185</v>
+      </c>
+      <c r="F306" s="36">
+        <v>270</v>
+      </c>
+      <c r="G306" s="36">
+        <v>215</v>
+      </c>
+      <c r="H306" s="61">
+        <v>6.2</v>
+      </c>
+      <c r="I306" s="61" t="s">
+        <v>930</v>
+      </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A307" s="9" t="s">
@@ -11756,7 +11430,7 @@
         <v>666</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>963</v>
+        <v>670</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>667</v>
@@ -11798,7 +11472,7 @@
         <v>208</v>
       </c>
       <c r="H312" s="10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I312" s="61"/>
     </row>
@@ -11833,13 +11507,13 @@
         <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>964</v>
+        <v>931</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>965</v>
+        <v>841</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>966</v>
+        <v>932</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11854,7 +11528,7 @@
         <v>5</v>
       </c>
       <c r="I315" s="61" t="s">
-        <v>967</v>
+        <v>933</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.15">
@@ -11862,13 +11536,13 @@
         <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>968</v>
+        <v>934</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>969</v>
+        <v>935</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>874</v>
+        <v>936</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11883,7 +11557,7 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="61" t="s">
-        <v>970</v>
+        <v>937</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.15">
@@ -11891,13 +11565,13 @@
         <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>971</v>
+        <v>938</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>876</v>
+        <v>939</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>877</v>
+        <v>940</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11909,10 +11583,10 @@
         <v>188</v>
       </c>
       <c r="H317" s="11">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>972</v>
+        <v>941</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.15">
@@ -11920,13 +11594,13 @@
         <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>875</v>
+        <v>938</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>878</v>
+        <v>942</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>877</v>
+        <v>940</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11947,13 +11621,13 @@
         <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>879</v>
+        <v>943</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>865</v>
+        <v>914</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>880</v>
+        <v>929</v>
       </c>
       <c r="E319" s="18">
         <v>185</v>
@@ -11965,10 +11639,10 @@
         <v>225</v>
       </c>
       <c r="H319" s="18">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.15">
@@ -11976,13 +11650,13 @@
         <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>974</v>
+        <v>945</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>975</v>
+        <v>946</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11997,7 +11671,7 @@
         <v>5.7</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>866</v>
+        <v>916</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.15">
@@ -12005,13 +11679,13 @@
         <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>882</v>
+        <v>947</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>976</v>
+        <v>948</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>977</v>
+        <v>949</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -12026,7 +11700,7 @@
         <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>978</v>
+        <v>950</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.15">
@@ -12034,13 +11708,13 @@
         <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>883</v>
+        <v>951</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>884</v>
+        <v>952</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>880</v>
+        <v>929</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -12055,7 +11729,7 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>979</v>
+        <v>953</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.15">
@@ -12063,13 +11737,13 @@
         <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>885</v>
+        <v>954</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>980</v>
+        <v>146</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>981</v>
+        <v>949</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -12084,7 +11758,7 @@
         <v>4.7</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>886</v>
+        <v>937</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.15">
@@ -12092,13 +11766,13 @@
         <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>982</v>
+        <v>955</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>887</v>
+        <v>956</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>880</v>
+        <v>929</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -12113,7 +11787,7 @@
         <v>6.7</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>979</v>
+        <v>953</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.15">
@@ -12121,13 +11795,13 @@
         <v>684</v>
       </c>
       <c r="B325" s="18" t="s">
-        <v>983</v>
+        <v>957</v>
       </c>
       <c r="C325" s="18" t="s">
-        <v>984</v>
+        <v>914</v>
       </c>
       <c r="D325" s="18" t="s">
-        <v>985</v>
+        <v>958</v>
       </c>
       <c r="E325" s="18">
         <v>185</v>
@@ -12139,10 +11813,10 @@
         <v>225</v>
       </c>
       <c r="H325" s="18">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="I325" s="11" t="s">
-        <v>973</v>
+        <v>944</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.15">
@@ -12150,13 +11824,13 @@
         <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
-        <v>986</v>
+        <v>959</v>
       </c>
       <c r="C326" s="36" t="s">
-        <v>987</v>
+        <v>960</v>
       </c>
       <c r="D326" s="36" t="s">
-        <v>988</v>
+        <v>961</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -12166,10 +11840,10 @@
         <v>220</v>
       </c>
       <c r="H326" s="61">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I326" s="61" t="s">
-        <v>989</v>
+        <v>962</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.15">
@@ -12177,13 +11851,13 @@
         <v>700</v>
       </c>
       <c r="B327" s="36" t="s">
-        <v>990</v>
+        <v>963</v>
       </c>
       <c r="C327" s="36" t="s">
-        <v>991</v>
+        <v>449</v>
       </c>
       <c r="D327" s="36" t="s">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="E327" s="36">
         <v>150</v>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="1008">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2334,601 +2334,998 @@
   </si>
   <si>
     <t>XC001</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>消半光珍珠点50*50*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>12*4*16</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*45</t>
-  </si>
-  <si>
-    <t>米克375</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克350</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
-  </si>
-  <si>
-    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*2*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫眼酷丝绵(东风)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯365克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>30*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2-T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯370克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
-  </si>
-  <si>
-    <t>猫眼酷丝绵(东风)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>网纹3/3-180</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75D*50S+10DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯米克245</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>网纹3/3-220</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>15*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100D*35S+150DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>天丝棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*3*32</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*三合一</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯195克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>天丝棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*三合一</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>270-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯360克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯370克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*30S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯285克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>加厚钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
-  </si>
-  <si>
-    <t>白坯365克</t>
-  </si>
-  <si>
-    <t>网纹3/3-180</t>
-  </si>
-  <si>
-    <t>75D*50S+10DT8</t>
-  </si>
-  <si>
-    <t>白坯米克245</t>
-  </si>
-  <si>
-    <t>网纹3/3-220</t>
-  </si>
-  <si>
-    <t>15*4*44</t>
-  </si>
-  <si>
-    <t>100D*35S+150DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯390克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>230-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*30S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯300克</t>
-  </si>
-  <si>
-    <t>天丝棉</t>
-  </si>
-  <si>
-    <t>20*3*32</t>
-  </si>
-  <si>
-    <t>80S*三合一</t>
-  </si>
-  <si>
-    <t>白坯195克</t>
-  </si>
-  <si>
-    <t>21*3*31</t>
-  </si>
-  <si>
-    <t>270-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">生态棉 加厚 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯390克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>270单股钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*18S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯360克</t>
-  </si>
-  <si>
-    <t>生态棉</t>
-  </si>
-  <si>
-    <t>40S*35S</t>
-  </si>
-  <si>
-    <t>210-钛金棉</t>
-  </si>
-  <si>
-    <t>17*3*27</t>
-  </si>
-  <si>
-    <t>40S*30S</t>
-  </si>
-  <si>
-    <t>白坯285克</t>
-  </si>
-  <si>
-    <t>加厚钛金棉</t>
-  </si>
-  <si>
-    <t>15.5*4*30</t>
-  </si>
-  <si>
-    <t>白坯390克</t>
-  </si>
-  <si>
-    <t>230-钛金棉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生态棉 加厚 </t>
-  </si>
-  <si>
-    <t>16*4*31</t>
-  </si>
-  <si>
-    <t>270单股钛金棉</t>
-  </si>
-  <si>
-    <t>40S*18S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>登山布</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>12.5*4*215*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75*450</t>
-  </si>
-  <si>
-    <t>白坯310克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40*300平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*24</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300D</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3001,6 +3398,13 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -3179,7 +3583,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3357,10 +3761,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3434,6 +3834,26 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3815,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>4</v>
+        <v>770</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4502,7 +4922,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4527,7 +4947,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -4740,7 +5160,7 @@
         <v>165</v>
       </c>
       <c r="H38" s="10">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I38" s="11"/>
     </row>
@@ -4802,7 +5222,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>3</v>
+        <v>773</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>98</v>
@@ -4974,7 +5394,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>116</v>
@@ -5179,7 +5599,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>134</v>
@@ -5706,7 +6126,7 @@
         <v>192</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>73</v>
+        <v>776</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>143</v>
@@ -6431,13 +6851,13 @@
         <v>267</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>253</v>
+        <v>777</v>
       </c>
       <c r="D106" s="22" t="s">
         <v>268</v>
       </c>
       <c r="E106" s="22">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F106" s="9"/>
       <c r="G106" s="11">
@@ -7056,7 +7476,7 @@
         <v>329</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>147</v>
@@ -7192,7 +7612,7 @@
         <v>165</v>
       </c>
       <c r="H136" s="26">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I136" s="11"/>
     </row>
@@ -7621,7 +8041,7 @@
         <v>216</v>
       </c>
       <c r="H153" s="13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I153" s="11"/>
     </row>
@@ -7729,7 +8149,7 @@
         <v>208</v>
       </c>
       <c r="H157" s="13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I157" s="11"/>
     </row>
@@ -7741,7 +8161,7 @@
         <v>402</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>392</v>
@@ -7815,7 +8235,7 @@
         <v>410</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>411</v>
@@ -7896,7 +8316,7 @@
         <v>419</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>420</v>
@@ -7923,10 +8343,10 @@
         <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>412</v>
@@ -7963,13 +8383,13 @@
         <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -7990,13 +8410,13 @@
         <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>415</v>
+        <v>788</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8017,7 +8437,7 @@
         <v>425</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>426</v>
@@ -8044,7 +8464,7 @@
         <v>428</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>429</v>
@@ -8071,7 +8491,7 @@
         <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>237</v>
@@ -8125,7 +8545,7 @@
         <v>433</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>434</v>
@@ -8152,7 +8572,7 @@
         <v>436</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>437</v>
@@ -8179,7 +8599,7 @@
         <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8260,7 +8680,7 @@
         <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>418</v>
@@ -8314,7 +8734,7 @@
         <v>448</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>449</v>
@@ -8341,7 +8761,7 @@
         <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>443</v>
@@ -8368,7 +8788,7 @@
         <v>451</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>308</v>
@@ -8395,7 +8815,7 @@
         <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>308</v>
@@ -8449,13 +8869,13 @@
         <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>443</v>
+        <v>802</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8476,7 +8896,7 @@
         <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>308</v>
@@ -8500,13 +8920,13 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A187" s="9" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>435</v>
@@ -8530,13 +8950,13 @@
         <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>271</v>
+        <v>808</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8557,7 +8977,7 @@
         <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>443</v>
@@ -8584,13 +9004,13 @@
         <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8611,10 +9031,10 @@
         <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>790</v>
+        <v>814</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>435</v>
@@ -8664,10 +9084,10 @@
         <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>384</v>
+        <v>816</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>147</v>
@@ -8676,10 +9096,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="44">
+        <v>180</v>
+      </c>
+      <c r="G194" s="42">
         <v>215</v>
-      </c>
-      <c r="G194" s="42">
-        <v>225</v>
       </c>
       <c r="H194" s="41">
         <v>4.0999999999999996</v>
@@ -8691,7 +9111,7 @@
         <v>467</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>468</v>
@@ -8706,7 +9126,7 @@
         <v>165</v>
       </c>
       <c r="G195" s="42">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H195" s="41">
         <v>3.9</v>
@@ -8718,10 +9138,10 @@
         <v>469</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>470</v>
@@ -8729,10 +9149,10 @@
       <c r="E196" s="45">
         <v>105</v>
       </c>
-      <c r="F196" s="36">
+      <c r="F196" s="65">
         <v>155</v>
       </c>
-      <c r="G196" s="11">
+      <c r="G196" s="66">
         <v>215</v>
       </c>
       <c r="H196" s="45">
@@ -8745,10 +9165,10 @@
         <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>385</v>
@@ -8756,10 +9176,10 @@
       <c r="E197" s="45">
         <v>100</v>
       </c>
-      <c r="F197" s="29">
+      <c r="F197" s="44">
         <v>150</v>
       </c>
-      <c r="G197" s="11">
+      <c r="G197" s="66">
         <v>215</v>
       </c>
       <c r="H197" s="45">
@@ -8772,7 +9192,7 @@
         <v>472</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>473</v>
@@ -8783,10 +9203,10 @@
       <c r="E198" s="45">
         <v>129</v>
       </c>
-      <c r="F198" s="46">
+      <c r="F198" s="67">
         <v>183</v>
       </c>
-      <c r="G198" s="11">
+      <c r="G198" s="66">
         <v>215</v>
       </c>
       <c r="H198" s="45">
@@ -8799,21 +9219,21 @@
         <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>400</v>
+        <v>824</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
       </c>
-      <c r="F199" s="29">
+      <c r="F199" s="44">
         <v>145</v>
       </c>
-      <c r="G199" s="11">
+      <c r="G199" s="66">
         <v>215</v>
       </c>
       <c r="H199" s="45">
@@ -8887,10 +9307,10 @@
         <v>483</v>
       </c>
       <c r="E204" s="24"/>
-      <c r="F204" s="47">
+      <c r="F204" s="46">
         <v>52</v>
       </c>
-      <c r="G204" s="48">
+      <c r="G204" s="47">
         <v>175</v>
       </c>
       <c r="H204" s="24">
@@ -8908,16 +9328,16 @@
       <c r="C205" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="D205" s="48" t="s">
+      <c r="D205" s="47" t="s">
         <v>487</v>
       </c>
       <c r="E205" s="24">
         <v>47</v>
       </c>
-      <c r="F205" s="47">
+      <c r="F205" s="46">
         <v>58</v>
       </c>
-      <c r="G205" s="48">
+      <c r="G205" s="47">
         <v>174</v>
       </c>
       <c r="H205" s="24">
@@ -8935,16 +9355,16 @@
       <c r="C206" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="D206" s="48" t="s">
+      <c r="D206" s="47" t="s">
         <v>487</v>
       </c>
       <c r="E206" s="24">
         <v>47</v>
       </c>
-      <c r="F206" s="47">
+      <c r="F206" s="46">
         <v>54</v>
       </c>
-      <c r="G206" s="48">
+      <c r="G206" s="47">
         <v>174</v>
       </c>
       <c r="H206" s="24">
@@ -8983,7 +9403,7 @@
         <v>494</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9046,7 +9466,7 @@
         <v>499</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9068,10 +9488,10 @@
         <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>143</v>
@@ -9123,7 +9543,7 @@
         <v>505</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>817</v>
+        <v>830</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>143</v>
@@ -9236,12 +9656,12 @@
         <v>517</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>818</v>
+        <v>831</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>819</v>
-      </c>
-      <c r="D220" s="49" t="s">
+        <v>832</v>
+      </c>
+      <c r="D220" s="48" t="s">
         <v>518</v>
       </c>
       <c r="E220" s="10">
@@ -9257,7 +9677,7 @@
         <v>3.6</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>820</v>
+        <v>833</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.15">
@@ -9265,13 +9685,13 @@
         <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>822</v>
-      </c>
-      <c r="D221" s="49" t="s">
-        <v>4</v>
+        <v>835</v>
+      </c>
+      <c r="D221" s="48" t="s">
+        <v>770</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9286,7 +9706,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>823</v>
+        <v>836</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.15">
@@ -9294,13 +9714,13 @@
         <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>824</v>
+        <v>837</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>825</v>
-      </c>
-      <c r="D222" s="49" t="s">
-        <v>518</v>
+        <v>838</v>
+      </c>
+      <c r="D222" s="48" t="s">
+        <v>839</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9326,7 +9746,7 @@
       <c r="C223" s="35" t="s">
         <v>523</v>
       </c>
-      <c r="D223" s="50" t="s">
+      <c r="D223" s="49" t="s">
         <v>4</v>
       </c>
       <c r="E223" s="35">
@@ -9348,13 +9768,13 @@
         <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9402,10 +9822,10 @@
         <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>435</v>
@@ -9429,10 +9849,10 @@
         <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>237</v>
+        <v>845</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>435</v>
@@ -9509,137 +9929,137 @@
       <c r="A230" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="B230" s="51" t="s">
+      <c r="B230" s="27" t="s">
         <v>535</v>
       </c>
-      <c r="C230" s="51" t="s">
+      <c r="C230" s="27" t="s">
         <v>456</v>
       </c>
-      <c r="D230" s="51" t="s">
+      <c r="D230" s="27" t="s">
         <v>435</v>
       </c>
-      <c r="E230" s="51">
+      <c r="E230" s="27">
         <v>145</v>
       </c>
-      <c r="F230" s="36">
+      <c r="F230" s="61">
         <v>225</v>
       </c>
-      <c r="G230" s="11">
+      <c r="G230" s="20">
         <v>215</v>
       </c>
-      <c r="H230" s="51">
+      <c r="H230" s="27">
         <v>5</v>
       </c>
-      <c r="I230" s="11"/>
+      <c r="I230" s="20"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A231" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B231" s="18"/>
-      <c r="C231" s="18"/>
-      <c r="D231" s="33"/>
-      <c r="E231" s="18"/>
-      <c r="F231" s="31"/>
-      <c r="G231" s="32"/>
-      <c r="H231" s="18"/>
-      <c r="I231" s="11"/>
+      <c r="B231" s="27"/>
+      <c r="C231" s="27"/>
+      <c r="D231" s="49"/>
+      <c r="E231" s="27"/>
+      <c r="F231" s="29"/>
+      <c r="G231" s="20"/>
+      <c r="H231" s="27"/>
+      <c r="I231" s="20"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A232" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="B232" s="35"/>
-      <c r="C232" s="35"/>
-      <c r="D232" s="35"/>
-      <c r="E232" s="35"/>
-      <c r="F232" s="36"/>
-      <c r="G232" s="37"/>
-      <c r="H232" s="35"/>
-      <c r="I232" s="37"/>
+      <c r="B232" s="39"/>
+      <c r="C232" s="39"/>
+      <c r="D232" s="39"/>
+      <c r="E232" s="39"/>
+      <c r="F232" s="61"/>
+      <c r="G232" s="40"/>
+      <c r="H232" s="39"/>
+      <c r="I232" s="40"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A233" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="B233" s="35" t="s">
+      <c r="B233" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="C233" s="35" t="s">
+      <c r="C233" s="39" t="s">
         <v>540</v>
       </c>
-      <c r="D233" s="35" t="s">
+      <c r="D233" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="E233" s="35">
+      <c r="E233" s="39">
         <v>185</v>
       </c>
-      <c r="F233" s="36">
+      <c r="F233" s="61">
         <v>270</v>
       </c>
-      <c r="G233" s="37">
+      <c r="G233" s="40">
         <v>215</v>
       </c>
-      <c r="H233" s="35">
+      <c r="H233" s="39">
         <v>5.3</v>
       </c>
-      <c r="I233" s="37"/>
+      <c r="I233" s="40"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A234" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="B234" s="52" t="s">
-        <v>831</v>
-      </c>
-      <c r="C234" s="52" t="s">
-        <v>832</v>
-      </c>
-      <c r="D234" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="E234" s="52">
+      <c r="B234" s="68" t="s">
+        <v>846</v>
+      </c>
+      <c r="C234" s="68" t="s">
+        <v>847</v>
+      </c>
+      <c r="D234" s="49" t="s">
+        <v>848</v>
+      </c>
+      <c r="E234" s="68">
         <v>190</v>
       </c>
-      <c r="F234" s="36">
+      <c r="F234" s="61">
         <v>275</v>
       </c>
-      <c r="G234" s="53">
+      <c r="G234" s="69">
         <v>215</v>
       </c>
-      <c r="H234" s="52">
+      <c r="H234" s="68">
         <v>5.8</v>
       </c>
-      <c r="I234" s="54" t="s">
-        <v>834</v>
+      <c r="I234" s="40" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A235" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B235" s="51" t="s">
-        <v>835</v>
-      </c>
-      <c r="C235" s="51" t="s">
-        <v>836</v>
-      </c>
-      <c r="D235" s="51" t="s">
-        <v>837</v>
-      </c>
-      <c r="E235" s="51">
+      <c r="B235" s="27" t="s">
+        <v>850</v>
+      </c>
+      <c r="C235" s="27" t="s">
+        <v>851</v>
+      </c>
+      <c r="D235" s="27" t="s">
+        <v>852</v>
+      </c>
+      <c r="E235" s="27">
         <v>155</v>
       </c>
-      <c r="F235" s="36">
+      <c r="F235" s="61">
         <v>230</v>
       </c>
-      <c r="G235" s="55">
+      <c r="G235" s="20">
         <v>215</v>
       </c>
-      <c r="H235" s="51">
+      <c r="H235" s="27">
         <v>4.7</v>
       </c>
-      <c r="I235" s="55" t="s">
+      <c r="I235" s="20" t="s">
         <v>544</v>
       </c>
     </row>
@@ -9647,41 +10067,41 @@
       <c r="A236" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="B236" s="51"/>
-      <c r="C236" s="51"/>
-      <c r="D236" s="51"/>
-      <c r="E236" s="51"/>
-      <c r="F236" s="36"/>
-      <c r="G236" s="55"/>
-      <c r="H236" s="51"/>
-      <c r="I236" s="54"/>
+      <c r="B236" s="27"/>
+      <c r="C236" s="27"/>
+      <c r="D236" s="27"/>
+      <c r="E236" s="27"/>
+      <c r="F236" s="61"/>
+      <c r="G236" s="20"/>
+      <c r="H236" s="27"/>
+      <c r="I236" s="40"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A237" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="B237" s="51" t="s">
-        <v>838</v>
-      </c>
-      <c r="C237" s="51" t="s">
+      <c r="B237" s="27" t="s">
+        <v>853</v>
+      </c>
+      <c r="C237" s="27" t="s">
         <v>547</v>
       </c>
-      <c r="D237" s="51" t="s">
-        <v>839</v>
-      </c>
-      <c r="E237" s="51">
+      <c r="D237" s="27" t="s">
+        <v>854</v>
+      </c>
+      <c r="E237" s="27">
         <v>155</v>
       </c>
-      <c r="F237" s="36">
+      <c r="F237" s="61">
         <v>230</v>
       </c>
-      <c r="G237" s="55">
+      <c r="G237" s="20">
         <v>218</v>
       </c>
-      <c r="H237" s="51">
+      <c r="H237" s="27">
         <v>5</v>
       </c>
-      <c r="I237" s="55" t="s">
+      <c r="I237" s="20" t="s">
         <v>544</v>
       </c>
     </row>
@@ -9689,202 +10109,202 @@
       <c r="A238" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="B238" s="51" t="s">
-        <v>840</v>
-      </c>
-      <c r="C238" s="51" t="s">
-        <v>841</v>
-      </c>
-      <c r="D238" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E238" s="52">
+      <c r="B238" s="27" t="s">
+        <v>855</v>
+      </c>
+      <c r="C238" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="D238" s="27" t="s">
+        <v>857</v>
+      </c>
+      <c r="E238" s="68">
         <v>190</v>
       </c>
-      <c r="F238" s="36">
+      <c r="F238" s="61">
         <v>270</v>
       </c>
-      <c r="G238" s="55">
+      <c r="G238" s="20">
         <v>216</v>
       </c>
-      <c r="H238" s="51">
+      <c r="H238" s="27">
         <v>5.7</v>
       </c>
-      <c r="I238" s="54" t="s">
-        <v>843</v>
+      <c r="I238" s="40" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A239" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="B239" s="51" t="s">
-        <v>844</v>
-      </c>
-      <c r="C239" s="51" t="s">
-        <v>845</v>
-      </c>
-      <c r="D239" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E239" s="52">
+      <c r="B239" s="27" t="s">
+        <v>859</v>
+      </c>
+      <c r="C239" s="27" t="s">
+        <v>860</v>
+      </c>
+      <c r="D239" s="27" t="s">
+        <v>857</v>
+      </c>
+      <c r="E239" s="68">
         <v>180</v>
       </c>
-      <c r="F239" s="36">
+      <c r="F239" s="61">
         <v>268</v>
       </c>
-      <c r="G239" s="55">
+      <c r="G239" s="20">
         <v>220</v>
       </c>
-      <c r="H239" s="51">
+      <c r="H239" s="27">
         <v>5.7</v>
       </c>
-      <c r="I239" s="54" t="s">
-        <v>843</v>
+      <c r="I239" s="40" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A240" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B240" s="51" t="s">
-        <v>846</v>
-      </c>
-      <c r="C240" s="51" t="s">
-        <v>847</v>
-      </c>
-      <c r="D240" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E240" s="52">
+      <c r="B240" s="27" t="s">
+        <v>862</v>
+      </c>
+      <c r="C240" s="27" t="s">
+        <v>863</v>
+      </c>
+      <c r="D240" s="27" t="s">
+        <v>857</v>
+      </c>
+      <c r="E240" s="68">
         <v>190</v>
       </c>
-      <c r="F240" s="36">
+      <c r="F240" s="61">
         <v>270</v>
       </c>
-      <c r="G240" s="55">
+      <c r="G240" s="20">
         <v>225</v>
       </c>
-      <c r="H240" s="35">
+      <c r="H240" s="39">
         <v>5.9</v>
       </c>
-      <c r="I240" s="54" t="s">
-        <v>848</v>
+      <c r="I240" s="40" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A241" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="B241" s="51" t="s">
-        <v>849</v>
-      </c>
-      <c r="C241" s="51" t="s">
-        <v>850</v>
-      </c>
-      <c r="D241" s="11" t="s">
+      <c r="B241" s="27" t="s">
+        <v>865</v>
+      </c>
+      <c r="C241" s="27" t="s">
+        <v>866</v>
+      </c>
+      <c r="D241" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="E241" s="51">
+      <c r="E241" s="27">
         <v>150</v>
       </c>
-      <c r="F241" s="36">
+      <c r="F241" s="61">
         <v>230</v>
       </c>
-      <c r="G241" s="55">
+      <c r="G241" s="20">
         <v>220</v>
       </c>
-      <c r="H241" s="52">
+      <c r="H241" s="68">
         <v>5.3</v>
       </c>
-      <c r="I241" s="55" t="s">
-        <v>851</v>
+      <c r="I241" s="20" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A242" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="B242" s="51" t="s">
-        <v>852</v>
-      </c>
-      <c r="C242" s="51" t="s">
-        <v>853</v>
-      </c>
-      <c r="D242" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E242" s="52">
+      <c r="B242" s="27" t="s">
+        <v>868</v>
+      </c>
+      <c r="C242" s="27" t="s">
+        <v>869</v>
+      </c>
+      <c r="D242" s="27" t="s">
+        <v>870</v>
+      </c>
+      <c r="E242" s="68">
         <v>160</v>
       </c>
-      <c r="F242" s="36">
+      <c r="F242" s="61">
         <v>250</v>
       </c>
-      <c r="G242" s="55">
+      <c r="G242" s="20">
         <v>225</v>
       </c>
-      <c r="H242" s="35">
+      <c r="H242" s="39">
         <v>5.4</v>
       </c>
-      <c r="I242" s="54" t="s">
-        <v>854</v>
+      <c r="I242" s="40" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A243" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="B243" s="51" t="s">
-        <v>855</v>
-      </c>
-      <c r="C243" s="51" t="s">
-        <v>856</v>
-      </c>
-      <c r="D243" s="51" t="s">
-        <v>857</v>
-      </c>
-      <c r="E243" s="52">
+      <c r="B243" s="27" t="s">
+        <v>872</v>
+      </c>
+      <c r="C243" s="27" t="s">
+        <v>873</v>
+      </c>
+      <c r="D243" s="27" t="s">
+        <v>874</v>
+      </c>
+      <c r="E243" s="68">
         <v>190</v>
       </c>
-      <c r="F243" s="36">
+      <c r="F243" s="61">
         <v>280</v>
       </c>
-      <c r="G243" s="55">
+      <c r="G243" s="20">
         <v>220</v>
       </c>
-      <c r="H243" s="35">
+      <c r="H243" s="39">
         <v>5.6</v>
       </c>
-      <c r="I243" s="54" t="s">
-        <v>858</v>
+      <c r="I243" s="40" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A244" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="B244" s="51" t="s">
-        <v>859</v>
-      </c>
-      <c r="C244" s="51" t="s">
-        <v>860</v>
-      </c>
-      <c r="D244" s="51" t="s">
-        <v>857</v>
-      </c>
-      <c r="E244" s="51">
+      <c r="B244" s="27" t="s">
+        <v>876</v>
+      </c>
+      <c r="C244" s="27" t="s">
+        <v>877</v>
+      </c>
+      <c r="D244" s="27" t="s">
+        <v>874</v>
+      </c>
+      <c r="E244" s="27">
         <v>110</v>
       </c>
-      <c r="F244" s="38">
+      <c r="F244" s="61">
         <v>160</v>
       </c>
-      <c r="G244" s="55">
+      <c r="G244" s="20">
         <v>220</v>
       </c>
-      <c r="H244" s="35">
+      <c r="H244" s="39">
         <v>3.9</v>
       </c>
-      <c r="I244" s="54"/>
+      <c r="I244" s="40"/>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A245" s="9" t="s">
@@ -9904,13 +10324,13 @@
         <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>861</v>
+        <v>878</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -9931,7 +10351,7 @@
         <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>863</v>
+        <v>880</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>527</v>
@@ -9951,14 +10371,14 @@
       <c r="H247" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I247" s="56"/>
+      <c r="I247" s="55"/>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A248" s="31" t="s">
         <v>559</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>864</v>
+        <v>881</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>560</v>
@@ -9978,17 +10398,17 @@
       <c r="H248" s="18">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I248" s="57"/>
+      <c r="I248" s="56"/>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A249" s="31" t="s">
         <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>437</v>
+        <v>883</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>427</v>
@@ -9996,7 +10416,7 @@
       <c r="E249" s="32">
         <v>105</v>
       </c>
-      <c r="F249" s="58">
+      <c r="F249" s="57">
         <v>155</v>
       </c>
       <c r="G249" s="32">
@@ -10005,14 +10425,14 @@
       <c r="H249" s="32">
         <v>3.4</v>
       </c>
-      <c r="I249" s="57"/>
+      <c r="I249" s="56"/>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A250" s="31" t="s">
         <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>152</v>
@@ -10023,7 +10443,7 @@
       <c r="E250" s="32">
         <v>108</v>
       </c>
-      <c r="F250" s="58">
+      <c r="F250" s="57">
         <v>150</v>
       </c>
       <c r="G250" s="32">
@@ -10039,7 +10459,7 @@
         <v>563</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>867</v>
+        <v>885</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>564</v>
@@ -10050,7 +10470,7 @@
       <c r="E251" s="18">
         <v>116</v>
       </c>
-      <c r="F251" s="58">
+      <c r="F251" s="57">
         <v>180</v>
       </c>
       <c r="G251" s="32">
@@ -10066,10 +10486,10 @@
         <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>868</v>
+        <v>886</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>437</v>
+        <v>887</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>427</v>
@@ -10077,7 +10497,7 @@
       <c r="E252" s="18">
         <v>105</v>
       </c>
-      <c r="F252" s="58">
+      <c r="F252" s="57">
         <v>155</v>
       </c>
       <c r="G252" s="32">
@@ -10093,7 +10513,7 @@
         <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>564</v>
@@ -10104,7 +10524,7 @@
       <c r="E253" s="18">
         <v>116</v>
       </c>
-      <c r="F253" s="58">
+      <c r="F253" s="57">
         <v>180</v>
       </c>
       <c r="G253" s="32">
@@ -10120,13 +10540,13 @@
         <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>870</v>
+        <v>889</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10140,8 +10560,8 @@
       <c r="H254" s="18">
         <v>5.5</v>
       </c>
-      <c r="I254" s="54" t="s">
-        <v>858</v>
+      <c r="I254" s="53" t="s">
+        <v>891</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.15">
@@ -10149,7 +10569,7 @@
         <v>568</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>569</v>
@@ -10157,47 +10577,47 @@
       <c r="D255" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="E255" s="59">
+      <c r="E255" s="58">
         <v>88</v>
       </c>
       <c r="F255" s="31">
         <v>130</v>
       </c>
-      <c r="G255" s="56">
+      <c r="G255" s="55">
         <v>208</v>
       </c>
-      <c r="H255" s="59">
+      <c r="H255" s="58">
         <v>3</v>
       </c>
-      <c r="I255" s="54"/>
+      <c r="I255" s="53"/>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A256" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="B256" s="52" t="s">
-        <v>873</v>
-      </c>
-      <c r="C256" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D256" s="50" t="s">
-        <v>874</v>
-      </c>
-      <c r="E256" s="52">
+      <c r="B256" s="51" t="s">
+        <v>893</v>
+      </c>
+      <c r="C256" s="27" t="s">
+        <v>894</v>
+      </c>
+      <c r="D256" s="49" t="s">
+        <v>895</v>
+      </c>
+      <c r="E256" s="51">
         <v>190</v>
       </c>
       <c r="F256" s="36">
         <v>265</v>
       </c>
-      <c r="G256" s="53">
+      <c r="G256" s="52">
         <v>215</v>
       </c>
-      <c r="H256" s="60">
+      <c r="H256" s="59">
         <v>5.4</v>
       </c>
-      <c r="I256" s="54" t="s">
-        <v>875</v>
+      <c r="I256" s="53" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.15">
@@ -10205,13 +10625,13 @@
         <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>320</v>
+        <v>897</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>427</v>
+        <v>898</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10222,17 +10642,17 @@
       <c r="G257" s="36">
         <v>215</v>
       </c>
-      <c r="H257" s="60">
+      <c r="H257" s="59">
         <v>4.7</v>
       </c>
-      <c r="I257" s="60"/>
+      <c r="I257" s="59"/>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A258" s="9" t="s">
         <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>866</v>
+        <v>899</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>152</v>
@@ -10243,7 +10663,7 @@
       <c r="E258" s="32">
         <v>108</v>
       </c>
-      <c r="F258" s="58">
+      <c r="F258" s="57">
         <v>160</v>
       </c>
       <c r="G258" s="32">
@@ -10252,7 +10672,7 @@
       <c r="H258" s="32">
         <v>3.4</v>
       </c>
-      <c r="I258" s="60"/>
+      <c r="I258" s="59"/>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A259" s="9" t="s">
@@ -10264,8 +10684,8 @@
       <c r="E259" s="36"/>
       <c r="F259" s="36"/>
       <c r="G259" s="36"/>
-      <c r="H259" s="60"/>
-      <c r="I259" s="60"/>
+      <c r="H259" s="59"/>
+      <c r="I259" s="59"/>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A260" s="9" t="s">
@@ -10277,8 +10697,8 @@
       <c r="E260" s="36"/>
       <c r="F260" s="36"/>
       <c r="G260" s="36"/>
-      <c r="H260" s="60"/>
-      <c r="I260" s="60"/>
+      <c r="H260" s="59"/>
+      <c r="I260" s="59"/>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A261" s="9" t="s">
@@ -10290,8 +10710,8 @@
       <c r="C261" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="D261" s="49" t="s">
-        <v>877</v>
+      <c r="D261" s="48" t="s">
+        <v>900</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10305,19 +10725,19 @@
       <c r="H261" s="10">
         <v>3.6</v>
       </c>
-      <c r="I261" s="60"/>
+      <c r="I261" s="59"/>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A262" s="9" t="s">
         <v>578</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>878</v>
+        <v>901</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="D262" s="49" t="s">
+      <c r="D262" s="48" t="s">
         <v>580</v>
       </c>
       <c r="E262" s="10">
@@ -10332,7 +10752,7 @@
       <c r="H262" s="10">
         <v>3.8</v>
       </c>
-      <c r="I262" s="60"/>
+      <c r="I262" s="59"/>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A263" s="9" t="s">
@@ -10359,7 +10779,7 @@
       <c r="H263" s="27">
         <v>3.4</v>
       </c>
-      <c r="I263" s="60"/>
+      <c r="I263" s="59"/>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A264" s="9" t="s">
@@ -10386,7 +10806,7 @@
       <c r="H264" s="10">
         <v>3.8</v>
       </c>
-      <c r="I264" s="60"/>
+      <c r="I264" s="59"/>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A265" s="9" t="s">
@@ -10413,20 +10833,20 @@
       <c r="H265" s="35">
         <v>3.6</v>
       </c>
-      <c r="I265" s="60"/>
+      <c r="I265" s="59"/>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A266" s="9" t="s">
         <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>879</v>
+        <v>902</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>860</v>
+        <v>903</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>880</v>
+        <v>904</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10440,20 +10860,20 @@
       <c r="H266" s="35">
         <v>3.5</v>
       </c>
-      <c r="I266" s="60"/>
+      <c r="I266" s="59"/>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A267" s="9" t="s">
         <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="D267" s="49" t="s">
-        <v>143</v>
+        <v>906</v>
+      </c>
+      <c r="D267" s="48" t="s">
+        <v>907</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10467,7 +10887,7 @@
       <c r="H267" s="10">
         <v>4</v>
       </c>
-      <c r="I267" s="61"/>
+      <c r="I267" s="60"/>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A268" s="9" t="s">
@@ -10479,8 +10899,8 @@
       <c r="E268" s="36"/>
       <c r="F268" s="36"/>
       <c r="G268" s="36"/>
-      <c r="H268" s="60"/>
-      <c r="I268" s="60"/>
+      <c r="H268" s="59"/>
+      <c r="I268" s="59"/>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A269" s="9" t="s">
@@ -10492,8 +10912,8 @@
       <c r="E269" s="36"/>
       <c r="F269" s="36"/>
       <c r="G269" s="36"/>
-      <c r="H269" s="60"/>
-      <c r="I269" s="60"/>
+      <c r="H269" s="59"/>
+      <c r="I269" s="59"/>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A270" s="9" t="s">
@@ -10505,8 +10925,8 @@
       <c r="E270" s="36"/>
       <c r="F270" s="36"/>
       <c r="G270" s="36"/>
-      <c r="H270" s="60"/>
-      <c r="I270" s="60"/>
+      <c r="H270" s="59"/>
+      <c r="I270" s="59"/>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A271" s="9" t="s">
@@ -10518,8 +10938,8 @@
       <c r="E271" s="36"/>
       <c r="F271" s="36"/>
       <c r="G271" s="36"/>
-      <c r="H271" s="60"/>
-      <c r="I271" s="60"/>
+      <c r="H271" s="59"/>
+      <c r="I271" s="59"/>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A272" s="9" t="s">
@@ -10531,8 +10951,8 @@
       <c r="E272" s="36"/>
       <c r="F272" s="36"/>
       <c r="G272" s="36"/>
-      <c r="H272" s="60"/>
-      <c r="I272" s="60"/>
+      <c r="H272" s="59"/>
+      <c r="I272" s="59"/>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A273" s="9" t="s">
@@ -10544,8 +10964,8 @@
       <c r="E273" s="36"/>
       <c r="F273" s="36"/>
       <c r="G273" s="36"/>
-      <c r="H273" s="60"/>
-      <c r="I273" s="60"/>
+      <c r="H273" s="59"/>
+      <c r="I273" s="59"/>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A274" s="9" t="s">
@@ -10557,8 +10977,8 @@
       <c r="E274" s="36"/>
       <c r="F274" s="36"/>
       <c r="G274" s="36"/>
-      <c r="H274" s="60"/>
-      <c r="I274" s="60"/>
+      <c r="H274" s="59"/>
+      <c r="I274" s="59"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A275" s="9" t="s">
@@ -10570,66 +10990,82 @@
       <c r="E275" s="36"/>
       <c r="F275" s="36"/>
       <c r="G275" s="36"/>
-      <c r="H275" s="60"/>
-      <c r="I275" s="60"/>
+      <c r="H275" s="59"/>
+      <c r="I275" s="59"/>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A276" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="B276" s="36"/>
-      <c r="C276" s="36"/>
-      <c r="D276" s="36"/>
-      <c r="E276" s="36"/>
-      <c r="F276" s="36"/>
-      <c r="G276" s="36"/>
-      <c r="H276" s="60"/>
-      <c r="I276" s="60"/>
+      <c r="B276" s="36" t="s">
+        <v>908</v>
+      </c>
+      <c r="C276" s="36" t="s">
+        <v>909</v>
+      </c>
+      <c r="D276" s="27" t="s">
+        <v>910</v>
+      </c>
+      <c r="E276" s="36">
+        <v>185</v>
+      </c>
+      <c r="F276" s="36">
+        <v>270</v>
+      </c>
+      <c r="G276" s="36">
+        <v>215</v>
+      </c>
+      <c r="H276" s="60">
+        <v>6.2</v>
+      </c>
+      <c r="I276" s="11" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A277" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="B277" s="52" t="s">
+      <c r="B277" s="51" t="s">
         <v>605</v>
       </c>
-      <c r="C277" s="52" t="s">
+      <c r="C277" s="51" t="s">
         <v>606</v>
       </c>
-      <c r="D277" s="52" t="s">
+      <c r="D277" s="51" t="s">
         <v>607</v>
       </c>
-      <c r="E277" s="52">
+      <c r="E277" s="51">
         <v>105</v>
       </c>
       <c r="F277" s="36">
         <v>140</v>
       </c>
-      <c r="G277" s="53">
+      <c r="G277" s="52">
         <v>215</v>
       </c>
-      <c r="H277" s="52">
+      <c r="H277" s="51">
         <v>4</v>
       </c>
-      <c r="I277" s="60"/>
+      <c r="I277" s="59"/>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A278" s="9" t="s">
         <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>883</v>
+        <v>912</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>547</v>
+        <v>913</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>884</v>
+        <v>914</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
       </c>
-      <c r="F278" s="62">
+      <c r="F278" s="61">
         <v>230</v>
       </c>
       <c r="G278" s="20">
@@ -10638,17 +11074,17 @@
       <c r="H278" s="27">
         <v>4.7</v>
       </c>
-      <c r="I278" s="60"/>
+      <c r="I278" s="59"/>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A279" s="9" t="s">
         <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>885</v>
-      </c>
-      <c r="C279" s="49" t="s">
-        <v>886</v>
+        <v>915</v>
+      </c>
+      <c r="C279" s="48" t="s">
+        <v>916</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>143</v>
@@ -10665,20 +11101,20 @@
       <c r="H279" s="10">
         <v>3.5</v>
       </c>
-      <c r="I279" s="60"/>
+      <c r="I279" s="59"/>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A280" s="9" t="s">
         <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>887</v>
-      </c>
-      <c r="C280" s="49" t="s">
-        <v>888</v>
+        <v>917</v>
+      </c>
+      <c r="C280" s="48" t="s">
+        <v>918</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>487</v>
+        <v>919</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10690,7 +11126,7 @@
       <c r="H280" s="10">
         <v>4.7</v>
       </c>
-      <c r="I280" s="60"/>
+      <c r="I280" s="59"/>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A281" s="9" t="s">
@@ -10699,7 +11135,7 @@
       <c r="B281" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="C281" s="49" t="s">
+      <c r="C281" s="48" t="s">
         <v>613</v>
       </c>
       <c r="D281" s="10" t="s">
@@ -10717,16 +11153,16 @@
       <c r="H281" s="10">
         <v>3.5</v>
       </c>
-      <c r="I281" s="60"/>
+      <c r="I281" s="59"/>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A282" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>889</v>
-      </c>
-      <c r="C282" s="49" t="s">
+        <v>920</v>
+      </c>
+      <c r="C282" s="48" t="s">
         <v>615</v>
       </c>
       <c r="D282" s="10" t="s">
@@ -10744,17 +11180,17 @@
       <c r="H282" s="10">
         <v>2.8</v>
       </c>
-      <c r="I282" s="60"/>
+      <c r="I282" s="59"/>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A283" s="9" t="s">
         <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>890</v>
-      </c>
-      <c r="C283" s="49" t="s">
-        <v>891</v>
+        <v>921</v>
+      </c>
+      <c r="C283" s="48" t="s">
+        <v>922</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -10771,20 +11207,20 @@
       <c r="H283" s="10">
         <v>3.7</v>
       </c>
-      <c r="I283" s="60"/>
+      <c r="I283" s="59"/>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A284" s="9" t="s">
         <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>892</v>
+        <v>923</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>893</v>
+        <v>924</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -10795,10 +11231,10 @@
       <c r="G284" s="36">
         <v>208</v>
       </c>
-      <c r="H284" s="60">
+      <c r="H284" s="59">
         <v>4.5</v>
       </c>
-      <c r="I284" s="60"/>
+      <c r="I284" s="59"/>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A285" s="9" t="s">
@@ -10807,11 +11243,11 @@
       <c r="B285" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C285" s="49" t="s">
+      <c r="C285" s="48" t="s">
         <v>620</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>894</v>
+        <v>925</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -10825,73 +11261,73 @@
       <c r="H285" s="10">
         <v>3.7</v>
       </c>
-      <c r="I285" s="60"/>
+      <c r="I285" s="59"/>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A286" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="52" t="s">
-        <v>895</v>
-      </c>
-      <c r="C286" s="52" t="s">
-        <v>896</v>
-      </c>
-      <c r="D286" s="52" t="s">
+      <c r="B286" s="51" t="s">
+        <v>926</v>
+      </c>
+      <c r="C286" s="51" t="s">
+        <v>927</v>
+      </c>
+      <c r="D286" s="51" t="s">
         <v>622</v>
       </c>
-      <c r="E286" s="52">
+      <c r="E286" s="51">
         <v>85</v>
       </c>
       <c r="F286" s="36">
         <v>121</v>
       </c>
-      <c r="G286" s="53">
+      <c r="G286" s="52">
         <v>208</v>
       </c>
-      <c r="H286" s="52">
+      <c r="H286" s="51">
         <v>4</v>
       </c>
-      <c r="I286" s="60"/>
+      <c r="I286" s="59"/>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A287" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="52" t="s">
-        <v>897</v>
-      </c>
-      <c r="C287" s="52" t="s">
-        <v>898</v>
-      </c>
-      <c r="D287" s="52" t="s">
-        <v>899</v>
-      </c>
-      <c r="E287" s="52">
+      <c r="B287" s="51" t="s">
+        <v>928</v>
+      </c>
+      <c r="C287" s="51" t="s">
+        <v>929</v>
+      </c>
+      <c r="D287" s="51" t="s">
+        <v>930</v>
+      </c>
+      <c r="E287" s="51">
         <v>88</v>
       </c>
       <c r="F287" s="36">
         <v>140</v>
       </c>
-      <c r="G287" s="53">
+      <c r="G287" s="52">
         <v>218</v>
       </c>
-      <c r="H287" s="52">
+      <c r="H287" s="51">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I287" s="61"/>
+      <c r="I287" s="60"/>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A288" s="9" t="s">
         <v>624</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>900</v>
+        <v>931</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>625</v>
       </c>
-      <c r="D288" s="50" t="s">
+      <c r="D288" s="49" t="s">
         <v>4</v>
       </c>
       <c r="E288" s="27">
@@ -10906,7 +11342,7 @@
       <c r="H288" s="27">
         <v>5</v>
       </c>
-      <c r="I288" s="61"/>
+      <c r="I288" s="60"/>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A289" s="9" t="s">
@@ -10918,7 +11354,7 @@
       <c r="C289" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="D289" s="49" t="s">
+      <c r="D289" s="48" t="s">
         <v>629</v>
       </c>
       <c r="E289" s="10">
@@ -10934,7 +11370,7 @@
         <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>901</v>
+        <v>932</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.15">
@@ -10947,7 +11383,7 @@
       <c r="C290" s="24" t="s">
         <v>632</v>
       </c>
-      <c r="D290" s="63" t="s">
+      <c r="D290" s="62" t="s">
         <v>39</v>
       </c>
       <c r="E290" s="24">
@@ -10956,107 +11392,107 @@
       <c r="F290" s="36">
         <v>100</v>
       </c>
-      <c r="G290" s="55">
+      <c r="G290" s="54">
         <v>220</v>
       </c>
       <c r="H290" s="24">
         <v>2.7</v>
       </c>
-      <c r="I290" s="61"/>
+      <c r="I290" s="60"/>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A291" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="B291" s="64" t="s">
-        <v>902</v>
-      </c>
-      <c r="C291" s="64" t="s">
-        <v>903</v>
-      </c>
-      <c r="D291" s="64" t="s">
+      <c r="B291" s="63" t="s">
+        <v>933</v>
+      </c>
+      <c r="C291" s="63" t="s">
+        <v>934</v>
+      </c>
+      <c r="D291" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="E291" s="64">
+      <c r="E291" s="63">
         <v>88</v>
       </c>
       <c r="F291" s="36">
         <v>130</v>
       </c>
-      <c r="G291" s="54">
+      <c r="G291" s="53">
         <v>220</v>
       </c>
-      <c r="H291" s="64">
+      <c r="H291" s="63">
         <v>3.5</v>
       </c>
-      <c r="I291" s="61"/>
+      <c r="I291" s="60"/>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A292" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>904</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="B292" s="63" t="s">
+        <v>935</v>
+      </c>
+      <c r="C292" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="D292" s="64" t="s">
+      <c r="D292" s="63" t="s">
         <v>637</v>
       </c>
-      <c r="E292" s="64">
+      <c r="E292" s="63">
         <v>80</v>
       </c>
       <c r="F292" s="36">
         <v>135</v>
       </c>
-      <c r="G292" s="54">
+      <c r="G292" s="53">
         <v>215</v>
       </c>
-      <c r="H292" s="64">
+      <c r="H292" s="63">
         <v>3.6</v>
       </c>
-      <c r="I292" s="61"/>
+      <c r="I292" s="60"/>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A293" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="B293" s="65" t="s">
-        <v>905</v>
-      </c>
-      <c r="C293" s="64" t="s">
-        <v>906</v>
-      </c>
-      <c r="D293" s="64" t="s">
+      <c r="B293" s="64" t="s">
+        <v>936</v>
+      </c>
+      <c r="C293" s="63" t="s">
+        <v>937</v>
+      </c>
+      <c r="D293" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="E293" s="65">
+      <c r="E293" s="64">
         <v>106</v>
       </c>
       <c r="F293" s="36">
         <v>145</v>
       </c>
-      <c r="G293" s="53">
+      <c r="G293" s="52">
         <v>215</v>
       </c>
-      <c r="H293" s="65">
+      <c r="H293" s="64">
         <v>3.7</v>
       </c>
-      <c r="I293" s="61"/>
+      <c r="I293" s="60"/>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A294" s="9" t="s">
         <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>907</v>
+        <v>938</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>443</v>
+        <v>802</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>908</v>
+        <v>939</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11070,14 +11506,14 @@
       <c r="H294" s="18">
         <v>5</v>
       </c>
-      <c r="I294" s="61"/>
+      <c r="I294" s="60"/>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A295" s="9" t="s">
         <v>640</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>909</v>
+        <v>940</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>641</v>
@@ -11093,7 +11529,7 @@
       <c r="H295" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I295" s="61"/>
+      <c r="I295" s="60"/>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A296" s="9" t="s">
@@ -11118,20 +11554,20 @@
       <c r="H296" s="35">
         <v>3.8</v>
       </c>
-      <c r="I296" s="61"/>
+      <c r="I296" s="60"/>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A297" s="9" t="s">
         <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>910</v>
+        <v>941</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>911</v>
+        <v>942</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>912</v>
+        <v>943</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11145,20 +11581,20 @@
       <c r="H297" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I297" s="54"/>
+      <c r="I297" s="53"/>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A298" s="9" t="s">
         <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>913</v>
+        <v>944</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>914</v>
+        <v>945</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>915</v>
+        <v>946</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11173,36 +11609,36 @@
         <v>5.8</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>916</v>
+        <v>947</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A299" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="B299" s="51" t="s">
-        <v>917</v>
-      </c>
-      <c r="C299" s="51" t="s">
-        <v>918</v>
-      </c>
-      <c r="D299" s="51" t="s">
-        <v>919</v>
-      </c>
-      <c r="E299" s="51">
+      <c r="B299" s="50" t="s">
+        <v>948</v>
+      </c>
+      <c r="C299" s="50" t="s">
+        <v>949</v>
+      </c>
+      <c r="D299" s="50" t="s">
+        <v>950</v>
+      </c>
+      <c r="E299" s="50">
         <v>124</v>
       </c>
       <c r="F299" s="36">
         <v>180</v>
       </c>
-      <c r="G299" s="55">
+      <c r="G299" s="54">
         <v>218</v>
       </c>
-      <c r="H299" s="51">
+      <c r="H299" s="50">
         <v>5</v>
       </c>
-      <c r="I299" s="55" t="s">
-        <v>920</v>
+      <c r="I299" s="54" t="s">
+        <v>951</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.15">
@@ -11215,8 +11651,8 @@
       <c r="E300" s="36"/>
       <c r="F300" s="36"/>
       <c r="G300" s="36"/>
-      <c r="H300" s="61"/>
-      <c r="I300" s="61"/>
+      <c r="H300" s="60"/>
+      <c r="I300" s="60"/>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A301" s="9" t="s">
@@ -11228,21 +11664,21 @@
       <c r="E301" s="36"/>
       <c r="F301" s="36"/>
       <c r="G301" s="36"/>
-      <c r="H301" s="61"/>
-      <c r="I301" s="61"/>
+      <c r="H301" s="60"/>
+      <c r="I301" s="60"/>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A302" s="9" t="s">
         <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>921</v>
+        <v>952</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>922</v>
+        <v>953</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>923</v>
+        <v>954</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11254,9 +11690,9 @@
         <v>215</v>
       </c>
       <c r="H302" s="11">
-        <v>4.7</v>
-      </c>
-      <c r="I302" s="61"/>
+        <v>4.8</v>
+      </c>
+      <c r="I302" s="60"/>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A303" s="9" t="s">
@@ -11269,7 +11705,7 @@
         <v>655</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>923</v>
+        <v>955</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11281,24 +11717,24 @@
         <v>215</v>
       </c>
       <c r="H303" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="I303" s="61"/>
+        <v>4.3</v>
+      </c>
+      <c r="I303" s="60"/>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A304" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="B304" s="63" t="s">
         <v>657</v>
       </c>
-      <c r="C304" s="64" t="s">
-        <v>250</v>
-      </c>
-      <c r="D304" s="64" t="s">
+      <c r="C304" s="63" t="s">
+        <v>956</v>
+      </c>
+      <c r="D304" s="63" t="s">
         <v>658</v>
       </c>
-      <c r="E304" s="64">
+      <c r="E304" s="63">
         <v>90</v>
       </c>
       <c r="F304" s="36">
@@ -11307,11 +11743,11 @@
       <c r="G304" s="37">
         <v>218</v>
       </c>
-      <c r="H304" s="64">
+      <c r="H304" s="63">
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>924</v>
+        <v>957</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.15">
@@ -11319,13 +11755,13 @@
         <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>925</v>
+        <v>958</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>926</v>
-      </c>
-      <c r="D305" s="18" t="s">
-        <v>927</v>
+        <v>959</v>
+      </c>
+      <c r="D305" s="27" t="s">
+        <v>960</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11336,39 +11772,23 @@
       <c r="G305" s="36">
         <v>225</v>
       </c>
-      <c r="H305" s="61">
+      <c r="H305" s="60">
         <v>7.2</v>
       </c>
-      <c r="I305" s="61"/>
+      <c r="I305" s="60"/>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A306" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="B306" s="36" t="s">
-        <v>928</v>
-      </c>
-      <c r="C306" s="36" t="s">
-        <v>871</v>
-      </c>
-      <c r="D306" s="36" t="s">
-        <v>929</v>
-      </c>
-      <c r="E306" s="36">
-        <v>185</v>
-      </c>
-      <c r="F306" s="36">
-        <v>270</v>
-      </c>
-      <c r="G306" s="36">
-        <v>215</v>
-      </c>
-      <c r="H306" s="61">
-        <v>6.2</v>
-      </c>
-      <c r="I306" s="61" t="s">
-        <v>930</v>
-      </c>
+      <c r="B306" s="36"/>
+      <c r="C306" s="36"/>
+      <c r="D306" s="27"/>
+      <c r="E306" s="36"/>
+      <c r="F306" s="36"/>
+      <c r="G306" s="36"/>
+      <c r="H306" s="60"/>
+      <c r="I306" s="11"/>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A307" s="9" t="s">
@@ -11380,8 +11800,8 @@
       <c r="E307" s="36"/>
       <c r="F307" s="36"/>
       <c r="G307" s="36"/>
-      <c r="H307" s="61"/>
-      <c r="I307" s="61"/>
+      <c r="H307" s="60"/>
+      <c r="I307" s="60"/>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A308" s="9" t="s">
@@ -11393,8 +11813,8 @@
       <c r="E308" s="36"/>
       <c r="F308" s="36"/>
       <c r="G308" s="36"/>
-      <c r="H308" s="61"/>
-      <c r="I308" s="61"/>
+      <c r="H308" s="60"/>
+      <c r="I308" s="60"/>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A309" s="9" t="s">
@@ -11406,8 +11826,8 @@
       <c r="E309" s="36"/>
       <c r="F309" s="36"/>
       <c r="G309" s="36"/>
-      <c r="H309" s="61"/>
-      <c r="I309" s="61"/>
+      <c r="H309" s="60"/>
+      <c r="I309" s="60"/>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A310" s="9" t="s">
@@ -11419,8 +11839,8 @@
       <c r="E310" s="36"/>
       <c r="F310" s="36"/>
       <c r="G310" s="36"/>
-      <c r="H310" s="61"/>
-      <c r="I310" s="61"/>
+      <c r="H310" s="60"/>
+      <c r="I310" s="60"/>
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A311" s="9" t="s">
@@ -11430,7 +11850,7 @@
         <v>666</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>670</v>
+        <v>961</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>667</v>
@@ -11447,7 +11867,7 @@
       <c r="H311" s="35">
         <v>3.8</v>
       </c>
-      <c r="I311" s="61"/>
+      <c r="I311" s="60"/>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A312" s="9" t="s">
@@ -11474,7 +11894,7 @@
       <c r="H312" s="10">
         <v>3.7</v>
       </c>
-      <c r="I312" s="61"/>
+      <c r="I312" s="60"/>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A313" s="9" t="s">
@@ -11486,8 +11906,8 @@
       <c r="E313" s="36"/>
       <c r="F313" s="36"/>
       <c r="G313" s="36"/>
-      <c r="H313" s="61"/>
-      <c r="I313" s="61"/>
+      <c r="H313" s="60"/>
+      <c r="I313" s="60"/>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A314" s="9" t="s">
@@ -11499,21 +11919,21 @@
       <c r="E314" s="36"/>
       <c r="F314" s="36"/>
       <c r="G314" s="36"/>
-      <c r="H314" s="61"/>
-      <c r="I314" s="61"/>
+      <c r="H314" s="60"/>
+      <c r="I314" s="60"/>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A315" s="9" t="s">
         <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>931</v>
+        <v>962</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>932</v>
+        <v>963</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11524,11 +11944,11 @@
       <c r="G315" s="36">
         <v>225</v>
       </c>
-      <c r="H315" s="61">
+      <c r="H315" s="60">
         <v>5</v>
       </c>
-      <c r="I315" s="61" t="s">
-        <v>933</v>
+      <c r="I315" s="60" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.15">
@@ -11536,13 +11956,13 @@
         <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>934</v>
+        <v>965</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>935</v>
+        <v>966</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>936</v>
+        <v>967</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11553,11 +11973,11 @@
       <c r="G316" s="36">
         <v>215</v>
       </c>
-      <c r="H316" s="61">
+      <c r="H316" s="60">
         <v>5.2</v>
       </c>
-      <c r="I316" s="61" t="s">
-        <v>937</v>
+      <c r="I316" s="60" t="s">
+        <v>968</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.15">
@@ -11565,13 +11985,13 @@
         <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>938</v>
+        <v>969</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>939</v>
+        <v>970</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>940</v>
+        <v>971</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11586,7 +12006,7 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>941</v>
+        <v>972</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.15">
@@ -11594,13 +12014,13 @@
         <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>938</v>
+        <v>973</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>940</v>
+        <v>975</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11621,28 +12041,28 @@
         <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>943</v>
+        <v>976</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>914</v>
+        <v>977</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="E319" s="18">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F319" s="31">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G319" s="32">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H319" s="18">
         <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>944</v>
+        <v>978</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.15">
@@ -11650,13 +12070,13 @@
         <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>945</v>
+        <v>979</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>946</v>
+        <v>980</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11671,7 +12091,7 @@
         <v>5.7</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>916</v>
+        <v>981</v>
       </c>
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.15">
@@ -11679,13 +12099,13 @@
         <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>947</v>
+        <v>982</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>948</v>
+        <v>983</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>949</v>
+        <v>984</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11700,7 +12120,7 @@
         <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>950</v>
+        <v>985</v>
       </c>
     </row>
     <row r="322" spans="1:9" x14ac:dyDescent="0.15">
@@ -11708,13 +12128,13 @@
         <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>951</v>
+        <v>986</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>952</v>
+        <v>987</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>929</v>
+        <v>988</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -11729,7 +12149,7 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>953</v>
+        <v>989</v>
       </c>
     </row>
     <row r="323" spans="1:9" x14ac:dyDescent="0.15">
@@ -11737,13 +12157,13 @@
         <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>954</v>
+        <v>990</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>146</v>
+        <v>991</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>949</v>
+        <v>992</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -11758,7 +12178,7 @@
         <v>4.7</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>937</v>
+        <v>993</v>
       </c>
     </row>
     <row r="324" spans="1:9" x14ac:dyDescent="0.15">
@@ -11766,13 +12186,13 @@
         <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>955</v>
+        <v>994</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>956</v>
+        <v>995</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>929</v>
+        <v>996</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -11787,7 +12207,7 @@
         <v>6.7</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>953</v>
+        <v>997</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.15">
@@ -11795,13 +12215,13 @@
         <v>684</v>
       </c>
       <c r="B325" s="18" t="s">
-        <v>957</v>
+        <v>998</v>
       </c>
       <c r="C325" s="18" t="s">
-        <v>914</v>
+        <v>945</v>
       </c>
       <c r="D325" s="18" t="s">
-        <v>958</v>
+        <v>999</v>
       </c>
       <c r="E325" s="18">
         <v>185</v>
@@ -11816,7 +12236,7 @@
         <v>5.2</v>
       </c>
       <c r="I325" s="11" t="s">
-        <v>944</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.15">
@@ -11824,13 +12244,13 @@
         <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
-        <v>959</v>
+        <v>1001</v>
       </c>
       <c r="C326" s="36" t="s">
-        <v>960</v>
+        <v>1002</v>
       </c>
       <c r="D326" s="36" t="s">
-        <v>961</v>
+        <v>1003</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -11839,11 +12259,11 @@
       <c r="G326" s="36">
         <v>220</v>
       </c>
-      <c r="H326" s="61">
+      <c r="H326" s="60">
         <v>5.8</v>
       </c>
-      <c r="I326" s="61" t="s">
-        <v>962</v>
+      <c r="I326" s="60" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.15">
@@ -11851,13 +12271,13 @@
         <v>700</v>
       </c>
       <c r="B327" s="36" t="s">
-        <v>963</v>
+        <v>1005</v>
       </c>
       <c r="C327" s="36" t="s">
-        <v>449</v>
+        <v>1006</v>
       </c>
       <c r="D327" s="36" t="s">
-        <v>964</v>
+        <v>1007</v>
       </c>
       <c r="E327" s="36">
         <v>150</v>
@@ -11868,10 +12288,10 @@
       <c r="G327" s="36">
         <v>208</v>
       </c>
-      <c r="H327" s="61">
+      <c r="H327" s="60">
         <v>5</v>
       </c>
-      <c r="I327" s="61"/>
+      <c r="I327" s="60"/>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A328" s="9" t="s">
@@ -11883,8 +12303,8 @@
       <c r="E328" s="36"/>
       <c r="F328" s="36"/>
       <c r="G328" s="36"/>
-      <c r="H328" s="61"/>
-      <c r="I328" s="61"/>
+      <c r="H328" s="60"/>
+      <c r="I328" s="60"/>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A329" s="9" t="s">
@@ -11896,8 +12316,8 @@
       <c r="E329" s="36"/>
       <c r="F329" s="36"/>
       <c r="G329" s="36"/>
-      <c r="H329" s="61"/>
-      <c r="I329" s="61"/>
+      <c r="H329" s="60"/>
+      <c r="I329" s="60"/>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A330" s="9" t="s">
@@ -11909,8 +12329,8 @@
       <c r="E330" s="36"/>
       <c r="F330" s="36"/>
       <c r="G330" s="36"/>
-      <c r="H330" s="61"/>
-      <c r="I330" s="61"/>
+      <c r="H330" s="60"/>
+      <c r="I330" s="60"/>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A331" s="9" t="s">
@@ -11922,8 +12342,8 @@
       <c r="E331" s="36"/>
       <c r="F331" s="36"/>
       <c r="G331" s="36"/>
-      <c r="H331" s="61"/>
-      <c r="I331" s="61"/>
+      <c r="H331" s="60"/>
+      <c r="I331" s="60"/>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A332" s="9" t="s">
@@ -11935,8 +12355,8 @@
       <c r="E332" s="36"/>
       <c r="F332" s="36"/>
       <c r="G332" s="36"/>
-      <c r="H332" s="61"/>
-      <c r="I332" s="61"/>
+      <c r="H332" s="60"/>
+      <c r="I332" s="60"/>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A333" s="9" t="s">
@@ -11948,8 +12368,8 @@
       <c r="E333" s="36"/>
       <c r="F333" s="36"/>
       <c r="G333" s="36"/>
-      <c r="H333" s="61"/>
-      <c r="I333" s="61"/>
+      <c r="H333" s="60"/>
+      <c r="I333" s="60"/>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A334" s="9" t="s">
@@ -11961,8 +12381,8 @@
       <c r="E334" s="36"/>
       <c r="F334" s="36"/>
       <c r="G334" s="36"/>
-      <c r="H334" s="61"/>
-      <c r="I334" s="61"/>
+      <c r="H334" s="60"/>
+      <c r="I334" s="60"/>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A335" s="9" t="s">
@@ -11974,8 +12394,8 @@
       <c r="E335" s="36"/>
       <c r="F335" s="36"/>
       <c r="G335" s="36"/>
-      <c r="H335" s="61"/>
-      <c r="I335" s="61"/>
+      <c r="H335" s="60"/>
+      <c r="I335" s="60"/>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A336" s="9" t="s">
@@ -11987,8 +12407,8 @@
       <c r="E336" s="36"/>
       <c r="F336" s="36"/>
       <c r="G336" s="36"/>
-      <c r="H336" s="61"/>
-      <c r="I336" s="61"/>
+      <c r="H336" s="60"/>
+      <c r="I336" s="60"/>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A337" s="9" t="s">
@@ -12000,8 +12420,8 @@
       <c r="E337" s="36"/>
       <c r="F337" s="36"/>
       <c r="G337" s="36"/>
-      <c r="H337" s="61"/>
-      <c r="I337" s="61"/>
+      <c r="H337" s="60"/>
+      <c r="I337" s="60"/>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A338" s="9" t="s">
@@ -12013,8 +12433,8 @@
       <c r="E338" s="36"/>
       <c r="F338" s="36"/>
       <c r="G338" s="36"/>
-      <c r="H338" s="61"/>
-      <c r="I338" s="61"/>
+      <c r="H338" s="60"/>
+      <c r="I338" s="60"/>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A339" s="9" t="s">
@@ -12026,8 +12446,8 @@
       <c r="E339" s="36"/>
       <c r="F339" s="36"/>
       <c r="G339" s="36"/>
-      <c r="H339" s="61"/>
-      <c r="I339" s="61"/>
+      <c r="H339" s="60"/>
+      <c r="I339" s="60"/>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A340" s="9" t="s">
@@ -12039,8 +12459,8 @@
       <c r="E340" s="36"/>
       <c r="F340" s="36"/>
       <c r="G340" s="36"/>
-      <c r="H340" s="61"/>
-      <c r="I340" s="61"/>
+      <c r="H340" s="60"/>
+      <c r="I340" s="60"/>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A341" s="9" t="s">
@@ -12052,8 +12472,8 @@
       <c r="E341" s="36"/>
       <c r="F341" s="36"/>
       <c r="G341" s="36"/>
-      <c r="H341" s="61"/>
-      <c r="I341" s="61"/>
+      <c r="H341" s="60"/>
+      <c r="I341" s="60"/>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A342" s="9" t="s">
@@ -12065,8 +12485,8 @@
       <c r="E342" s="36"/>
       <c r="F342" s="36"/>
       <c r="G342" s="36"/>
-      <c r="H342" s="61"/>
-      <c r="I342" s="61"/>
+      <c r="H342" s="60"/>
+      <c r="I342" s="60"/>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A343" s="9" t="s">
@@ -12078,8 +12498,8 @@
       <c r="E343" s="36"/>
       <c r="F343" s="36"/>
       <c r="G343" s="36"/>
-      <c r="H343" s="61"/>
-      <c r="I343" s="61"/>
+      <c r="H343" s="60"/>
+      <c r="I343" s="60"/>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A344" s="9" t="s">
@@ -12091,8 +12511,8 @@
       <c r="E344" s="36"/>
       <c r="F344" s="36"/>
       <c r="G344" s="36"/>
-      <c r="H344" s="61"/>
-      <c r="I344" s="61"/>
+      <c r="H344" s="60"/>
+      <c r="I344" s="60"/>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A345" s="9" t="s">
@@ -12104,8 +12524,8 @@
       <c r="E345" s="36"/>
       <c r="F345" s="36"/>
       <c r="G345" s="36"/>
-      <c r="H345" s="61"/>
-      <c r="I345" s="61"/>
+      <c r="H345" s="60"/>
+      <c r="I345" s="60"/>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A346" s="9" t="s">
@@ -12117,8 +12537,8 @@
       <c r="E346" s="36"/>
       <c r="F346" s="36"/>
       <c r="G346" s="36"/>
-      <c r="H346" s="61"/>
-      <c r="I346" s="61"/>
+      <c r="H346" s="60"/>
+      <c r="I346" s="60"/>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A347" s="9" t="s">
@@ -12130,8 +12550,8 @@
       <c r="E347" s="36"/>
       <c r="F347" s="36"/>
       <c r="G347" s="36"/>
-      <c r="H347" s="61"/>
-      <c r="I347" s="61"/>
+      <c r="H347" s="60"/>
+      <c r="I347" s="60"/>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A348" s="9" t="s">
@@ -12143,8 +12563,8 @@
       <c r="E348" s="36"/>
       <c r="F348" s="36"/>
       <c r="G348" s="36"/>
-      <c r="H348" s="61"/>
-      <c r="I348" s="61"/>
+      <c r="H348" s="60"/>
+      <c r="I348" s="60"/>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A349" s="9" t="s">
@@ -12156,8 +12576,8 @@
       <c r="E349" s="36"/>
       <c r="F349" s="36"/>
       <c r="G349" s="36"/>
-      <c r="H349" s="61"/>
-      <c r="I349" s="61"/>
+      <c r="H349" s="60"/>
+      <c r="I349" s="60"/>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A350" s="9" t="s">
@@ -12169,8 +12589,8 @@
       <c r="E350" s="36"/>
       <c r="F350" s="36"/>
       <c r="G350" s="36"/>
-      <c r="H350" s="61"/>
-      <c r="I350" s="61"/>
+      <c r="H350" s="60"/>
+      <c r="I350" s="60"/>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A351" s="9" t="s">
@@ -12182,8 +12602,8 @@
       <c r="E351" s="36"/>
       <c r="F351" s="36"/>
       <c r="G351" s="36"/>
-      <c r="H351" s="61"/>
-      <c r="I351" s="61"/>
+      <c r="H351" s="60"/>
+      <c r="I351" s="60"/>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A352" s="9" t="s">
@@ -12195,8 +12615,8 @@
       <c r="E352" s="36"/>
       <c r="F352" s="36"/>
       <c r="G352" s="36"/>
-      <c r="H352" s="61"/>
-      <c r="I352" s="61"/>
+      <c r="H352" s="60"/>
+      <c r="I352" s="60"/>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A353" s="9" t="s">
@@ -12208,8 +12628,8 @@
       <c r="E353" s="36"/>
       <c r="F353" s="36"/>
       <c r="G353" s="36"/>
-      <c r="H353" s="61"/>
-      <c r="I353" s="61"/>
+      <c r="H353" s="60"/>
+      <c r="I353" s="60"/>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A354" s="9" t="s">
@@ -12221,8 +12641,8 @@
       <c r="E354" s="36"/>
       <c r="F354" s="36"/>
       <c r="G354" s="36"/>
-      <c r="H354" s="61"/>
-      <c r="I354" s="61"/>
+      <c r="H354" s="60"/>
+      <c r="I354" s="60"/>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A355" s="9" t="s">
@@ -12234,8 +12654,8 @@
       <c r="E355" s="36"/>
       <c r="F355" s="36"/>
       <c r="G355" s="36"/>
-      <c r="H355" s="61"/>
-      <c r="I355" s="61"/>
+      <c r="H355" s="60"/>
+      <c r="I355" s="60"/>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A356" s="9" t="s">
@@ -12247,8 +12667,8 @@
       <c r="E356" s="36"/>
       <c r="F356" s="36"/>
       <c r="G356" s="36"/>
-      <c r="H356" s="61"/>
-      <c r="I356" s="61"/>
+      <c r="H356" s="60"/>
+      <c r="I356" s="60"/>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A357" s="9" t="s">
@@ -12260,8 +12680,8 @@
       <c r="E357" s="36"/>
       <c r="F357" s="36"/>
       <c r="G357" s="36"/>
-      <c r="H357" s="61"/>
-      <c r="I357" s="61"/>
+      <c r="H357" s="60"/>
+      <c r="I357" s="60"/>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A358" s="9" t="s">
@@ -12273,8 +12693,8 @@
       <c r="E358" s="36"/>
       <c r="F358" s="36"/>
       <c r="G358" s="36"/>
-      <c r="H358" s="61"/>
-      <c r="I358" s="61"/>
+      <c r="H358" s="60"/>
+      <c r="I358" s="60"/>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A359" s="9" t="s">
@@ -12286,8 +12706,8 @@
       <c r="E359" s="36"/>
       <c r="F359" s="36"/>
       <c r="G359" s="36"/>
-      <c r="H359" s="61"/>
-      <c r="I359" s="61"/>
+      <c r="H359" s="60"/>
+      <c r="I359" s="60"/>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A360" s="9" t="s">
@@ -12299,8 +12719,8 @@
       <c r="E360" s="36"/>
       <c r="F360" s="36"/>
       <c r="G360" s="36"/>
-      <c r="H360" s="61"/>
-      <c r="I360" s="61"/>
+      <c r="H360" s="60"/>
+      <c r="I360" s="60"/>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A361" s="9" t="s">
@@ -12312,8 +12732,8 @@
       <c r="E361" s="36"/>
       <c r="F361" s="36"/>
       <c r="G361" s="36"/>
-      <c r="H361" s="61"/>
-      <c r="I361" s="61"/>
+      <c r="H361" s="60"/>
+      <c r="I361" s="60"/>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A362" s="9" t="s">
@@ -12325,8 +12745,8 @@
       <c r="E362" s="36"/>
       <c r="F362" s="36"/>
       <c r="G362" s="36"/>
-      <c r="H362" s="61"/>
-      <c r="I362" s="61"/>
+      <c r="H362" s="60"/>
+      <c r="I362" s="60"/>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A363" s="9" t="s">
@@ -12338,8 +12758,8 @@
       <c r="E363" s="36"/>
       <c r="F363" s="36"/>
       <c r="G363" s="36"/>
-      <c r="H363" s="61"/>
-      <c r="I363" s="61"/>
+      <c r="H363" s="60"/>
+      <c r="I363" s="60"/>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A364" s="9" t="s">
@@ -12351,8 +12771,8 @@
       <c r="E364" s="36"/>
       <c r="F364" s="36"/>
       <c r="G364" s="36"/>
-      <c r="H364" s="61"/>
-      <c r="I364" s="61"/>
+      <c r="H364" s="60"/>
+      <c r="I364" s="60"/>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A365" s="9" t="s">
@@ -12364,8 +12784,8 @@
       <c r="E365" s="36"/>
       <c r="F365" s="36"/>
       <c r="G365" s="36"/>
-      <c r="H365" s="61"/>
-      <c r="I365" s="61"/>
+      <c r="H365" s="60"/>
+      <c r="I365" s="60"/>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A366" s="9" t="s">
@@ -12377,8 +12797,8 @@
       <c r="E366" s="36"/>
       <c r="F366" s="36"/>
       <c r="G366" s="36"/>
-      <c r="H366" s="61"/>
-      <c r="I366" s="61"/>
+      <c r="H366" s="60"/>
+      <c r="I366" s="60"/>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A367" s="9" t="s">
@@ -12390,8 +12810,8 @@
       <c r="E367" s="36"/>
       <c r="F367" s="36"/>
       <c r="G367" s="36"/>
-      <c r="H367" s="61"/>
-      <c r="I367" s="61"/>
+      <c r="H367" s="60"/>
+      <c r="I367" s="60"/>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A368" s="9" t="s">
@@ -12403,8 +12823,8 @@
       <c r="E368" s="36"/>
       <c r="F368" s="36"/>
       <c r="G368" s="36"/>
-      <c r="H368" s="61"/>
-      <c r="I368" s="61"/>
+      <c r="H368" s="60"/>
+      <c r="I368" s="60"/>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A369" s="9" t="s">
@@ -12416,8 +12836,8 @@
       <c r="E369" s="36"/>
       <c r="F369" s="36"/>
       <c r="G369" s="36"/>
-      <c r="H369" s="61"/>
-      <c r="I369" s="61"/>
+      <c r="H369" s="60"/>
+      <c r="I369" s="60"/>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A370" s="9" t="s">
@@ -12429,8 +12849,8 @@
       <c r="E370" s="36"/>
       <c r="F370" s="36"/>
       <c r="G370" s="36"/>
-      <c r="H370" s="61"/>
-      <c r="I370" s="61"/>
+      <c r="H370" s="60"/>
+      <c r="I370" s="60"/>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A371" s="9" t="s">
@@ -12442,8 +12862,8 @@
       <c r="E371" s="36"/>
       <c r="F371" s="36"/>
       <c r="G371" s="36"/>
-      <c r="H371" s="61"/>
-      <c r="I371" s="61"/>
+      <c r="H371" s="60"/>
+      <c r="I371" s="60"/>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A372" s="9" t="s">
@@ -12455,8 +12875,8 @@
       <c r="E372" s="36"/>
       <c r="F372" s="36"/>
       <c r="G372" s="36"/>
-      <c r="H372" s="61"/>
-      <c r="I372" s="61"/>
+      <c r="H372" s="60"/>
+      <c r="I372" s="60"/>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A373" s="9" t="s">
@@ -12468,8 +12888,8 @@
       <c r="E373" s="36"/>
       <c r="F373" s="36"/>
       <c r="G373" s="36"/>
-      <c r="H373" s="61"/>
-      <c r="I373" s="61"/>
+      <c r="H373" s="60"/>
+      <c r="I373" s="60"/>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A374" s="9" t="s">
@@ -12481,8 +12901,8 @@
       <c r="E374" s="36"/>
       <c r="F374" s="36"/>
       <c r="G374" s="36"/>
-      <c r="H374" s="61"/>
-      <c r="I374" s="61"/>
+      <c r="H374" s="60"/>
+      <c r="I374" s="60"/>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A375" s="9" t="s">
@@ -12494,8 +12914,8 @@
       <c r="E375" s="36"/>
       <c r="F375" s="36"/>
       <c r="G375" s="36"/>
-      <c r="H375" s="61"/>
-      <c r="I375" s="61"/>
+      <c r="H375" s="60"/>
+      <c r="I375" s="60"/>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A376" s="9" t="s">
@@ -12507,8 +12927,8 @@
       <c r="E376" s="36"/>
       <c r="F376" s="36"/>
       <c r="G376" s="36"/>
-      <c r="H376" s="61"/>
-      <c r="I376" s="61"/>
+      <c r="H376" s="60"/>
+      <c r="I376" s="60"/>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A377" s="9" t="s">
@@ -12520,8 +12940,8 @@
       <c r="E377" s="36"/>
       <c r="F377" s="36"/>
       <c r="G377" s="36"/>
-      <c r="H377" s="61"/>
-      <c r="I377" s="61"/>
+      <c r="H377" s="60"/>
+      <c r="I377" s="60"/>
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A378" s="9" t="s">
@@ -12533,8 +12953,8 @@
       <c r="E378" s="36"/>
       <c r="F378" s="36"/>
       <c r="G378" s="36"/>
-      <c r="H378" s="61"/>
-      <c r="I378" s="61"/>
+      <c r="H378" s="60"/>
+      <c r="I378" s="60"/>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A379" s="9" t="s">
@@ -12546,8 +12966,8 @@
       <c r="E379" s="36"/>
       <c r="F379" s="36"/>
       <c r="G379" s="36"/>
-      <c r="H379" s="61"/>
-      <c r="I379" s="61"/>
+      <c r="H379" s="60"/>
+      <c r="I379" s="60"/>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A380" s="9" t="s">
@@ -12559,8 +12979,8 @@
       <c r="E380" s="36"/>
       <c r="F380" s="36"/>
       <c r="G380" s="36"/>
-      <c r="H380" s="61"/>
-      <c r="I380" s="61"/>
+      <c r="H380" s="60"/>
+      <c r="I380" s="60"/>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A381" s="9" t="s">
@@ -12572,8 +12992,8 @@
       <c r="E381" s="36"/>
       <c r="F381" s="36"/>
       <c r="G381" s="36"/>
-      <c r="H381" s="61"/>
-      <c r="I381" s="61"/>
+      <c r="H381" s="60"/>
+      <c r="I381" s="60"/>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A382" s="9" t="s">
@@ -12585,8 +13005,8 @@
       <c r="E382" s="36"/>
       <c r="F382" s="36"/>
       <c r="G382" s="36"/>
-      <c r="H382" s="61"/>
-      <c r="I382" s="61"/>
+      <c r="H382" s="60"/>
+      <c r="I382" s="60"/>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A383" s="9" t="s">
@@ -12598,8 +13018,8 @@
       <c r="E383" s="36"/>
       <c r="F383" s="36"/>
       <c r="G383" s="36"/>
-      <c r="H383" s="61"/>
-      <c r="I383" s="61"/>
+      <c r="H383" s="60"/>
+      <c r="I383" s="60"/>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A384" s="9" t="s">
@@ -12611,8 +13031,8 @@
       <c r="E384" s="36"/>
       <c r="F384" s="36"/>
       <c r="G384" s="36"/>
-      <c r="H384" s="61"/>
-      <c r="I384" s="61"/>
+      <c r="H384" s="60"/>
+      <c r="I384" s="60"/>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A385" s="9" t="s">
@@ -12624,8 +13044,8 @@
       <c r="E385" s="36"/>
       <c r="F385" s="36"/>
       <c r="G385" s="36"/>
-      <c r="H385" s="61"/>
-      <c r="I385" s="61"/>
+      <c r="H385" s="60"/>
+      <c r="I385" s="60"/>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A386" s="9" t="s">
@@ -12637,8 +13057,8 @@
       <c r="E386" s="36"/>
       <c r="F386" s="36"/>
       <c r="G386" s="36"/>
-      <c r="H386" s="61"/>
-      <c r="I386" s="61"/>
+      <c r="H386" s="60"/>
+      <c r="I386" s="60"/>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A387" s="9" t="s">
@@ -12650,8 +13070,8 @@
       <c r="E387" s="36"/>
       <c r="F387" s="36"/>
       <c r="G387" s="36"/>
-      <c r="H387" s="61"/>
-      <c r="I387" s="61"/>
+      <c r="H387" s="60"/>
+      <c r="I387" s="60"/>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A388" s="9" t="s">
@@ -12663,8 +13083,8 @@
       <c r="E388" s="36"/>
       <c r="F388" s="36"/>
       <c r="G388" s="36"/>
-      <c r="H388" s="61"/>
-      <c r="I388" s="61"/>
+      <c r="H388" s="60"/>
+      <c r="I388" s="60"/>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A389" s="9" t="s">
@@ -12676,8 +13096,8 @@
       <c r="E389" s="36"/>
       <c r="F389" s="36"/>
       <c r="G389" s="36"/>
-      <c r="H389" s="61"/>
-      <c r="I389" s="61"/>
+      <c r="H389" s="60"/>
+      <c r="I389" s="60"/>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A390" s="9" t="s">
@@ -12689,8 +13109,8 @@
       <c r="E390" s="36"/>
       <c r="F390" s="36"/>
       <c r="G390" s="36"/>
-      <c r="H390" s="61"/>
-      <c r="I390" s="61"/>
+      <c r="H390" s="60"/>
+      <c r="I390" s="60"/>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A391" s="9" t="s">
@@ -12702,8 +13122,8 @@
       <c r="E391" s="36"/>
       <c r="F391" s="36"/>
       <c r="G391" s="36"/>
-      <c r="H391" s="61"/>
-      <c r="I391" s="61"/>
+      <c r="H391" s="60"/>
+      <c r="I391" s="60"/>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A392" s="9" t="s">
@@ -12715,8 +13135,8 @@
       <c r="E392" s="36"/>
       <c r="F392" s="36"/>
       <c r="G392" s="36"/>
-      <c r="H392" s="61"/>
-      <c r="I392" s="61"/>
+      <c r="H392" s="60"/>
+      <c r="I392" s="60"/>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A393" s="9" t="s">
@@ -12728,8 +13148,8 @@
       <c r="E393" s="36"/>
       <c r="F393" s="36"/>
       <c r="G393" s="36"/>
-      <c r="H393" s="61"/>
-      <c r="I393" s="61"/>
+      <c r="H393" s="60"/>
+      <c r="I393" s="60"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\2种产品规格\18962500118标签加二维码\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
   </bookViews>
@@ -16,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="965">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2334,998 +2329,601 @@
   </si>
   <si>
     <t>XC001</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>消半光珍珠点50*50*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>12*4*16</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*46</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>120D扁平4/4斜</t>
+  </si>
+  <si>
+    <t>17*4*45</t>
+  </si>
+  <si>
+    <t>米克375</t>
+  </si>
+  <si>
+    <t>100D消光多乐3/3斜</t>
+  </si>
+  <si>
+    <t>15*4*43</t>
+  </si>
+  <si>
+    <t>米克300</t>
+  </si>
+  <si>
+    <t>120D扁平1/2斜</t>
+  </si>
+  <si>
+    <t>17*4*34</t>
+  </si>
+  <si>
+    <t>米克350</t>
+  </si>
+  <si>
+    <t>120D扁平T800变化斜</t>
+  </si>
+  <si>
+    <t>17*4*29</t>
+  </si>
+  <si>
+    <t>120*150T800</t>
+  </si>
+  <si>
+    <t>米克380</t>
+  </si>
+  <si>
+    <t>120D扁平牛津</t>
+  </si>
+  <si>
+    <t>20*2*31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+  </si>
+  <si>
+    <t>13.5*4*34</t>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/1斜 31</t>
+  </si>
+  <si>
+    <t>40S*150 酷丝棉3/2斜 39</t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1 30</t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 30</t>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/2 38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+  </si>
+  <si>
+    <t>40S*300 酷丝棉3/2斜</t>
+  </si>
+  <si>
+    <t>13.5*4*27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+  </si>
+  <si>
+    <t>40S*300酷丝绵珍珠点</t>
+  </si>
+  <si>
+    <t>40S*150*300T400</t>
   </si>
   <si>
     <t>米克368</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平4/4斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克368</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光多乐3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>15*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克300</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平1/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克350</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平T800变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*4*29</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>120D扁平牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*34</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/1斜 31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150 酷丝棉3/2斜 39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300 酷丝棉3/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克380</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300酷丝绵珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵变化斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*36</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/2 30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50*50</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>半光大猫眼</t>
+  </si>
+  <si>
+    <t>100半低*150半T800</t>
+  </si>
+  <si>
+    <t>50D低弹*50T800 平纹</t>
+  </si>
+  <si>
+    <t>23*2*40</t>
+  </si>
+  <si>
+    <t>30D T8 平纹</t>
+  </si>
+  <si>
+    <t>22*3*57</t>
+  </si>
+  <si>
+    <t>75D经纬T8平纹</t>
+  </si>
+  <si>
+    <t>75经纬T8 2/2斜</t>
+  </si>
+  <si>
+    <t>19*3*38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+  </si>
+  <si>
+    <t>21*3*53</t>
+  </si>
+  <si>
+    <t>50DT8*50DT8</t>
+  </si>
+  <si>
+    <t>T8五面埋伏</t>
+  </si>
+  <si>
+    <t>14*4*38</t>
+  </si>
+  <si>
+    <t>50D*100D经纬T800珍珠点</t>
+  </si>
+  <si>
+    <t>21*3*49</t>
+  </si>
+  <si>
+    <t>50D*50D*100D T800</t>
+  </si>
+  <si>
+    <t>T800双链条</t>
+  </si>
+  <si>
+    <t>米克265</t>
+  </si>
+  <si>
+    <t>经消光低弹 双纬T800</t>
+  </si>
+  <si>
+    <t>20*2*26</t>
+  </si>
+  <si>
+    <t>75D半光T800双纬平纹</t>
+  </si>
+  <si>
+    <t>75消低弹*75T8002/2斜</t>
+  </si>
+  <si>
+    <t>17.5*4*38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
+  </si>
+  <si>
+    <t>40S*150T800</t>
+  </si>
+  <si>
+    <t>空变T8平纹</t>
+  </si>
+  <si>
+    <t>40S*75T8酷丝棉3/1.超钛棉</t>
+  </si>
+  <si>
+    <t>17.5*3*44</t>
+  </si>
+  <si>
+    <t>40S*75T800</t>
+  </si>
+  <si>
+    <t>40S*300加厚超钛棉</t>
+  </si>
+  <si>
+    <t>14*4*27</t>
+  </si>
+  <si>
+    <t>40S*150*2-T800</t>
+  </si>
+  <si>
+    <t>白坯370克</t>
+  </si>
+  <si>
+    <t>100D消光75DT800 3/3斜</t>
+  </si>
+  <si>
+    <t>15.5*4*48</t>
+  </si>
+  <si>
+    <t>100*75T8</t>
+  </si>
+  <si>
+    <t>米克250</t>
+  </si>
+  <si>
+    <t>37梭多乐绵</t>
+  </si>
+  <si>
+    <t>16*4*37</t>
+  </si>
+  <si>
+    <t>100D*40S+150D T8</t>
+  </si>
+  <si>
+    <t>白坯188克</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斜纹毛巾底 </t>
+  </si>
+  <si>
+    <t>13.5*4*51</t>
+  </si>
+  <si>
+    <t>40S*150T8*300低弹</t>
   </si>
   <si>
     <t>猫眼酷丝绵(东风)</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯365克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>半光大猫眼</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100半低*150半T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D低弹*50T800 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>23*2*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>30D T8 平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*57</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>30*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75D经纬T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75经纬T8 2/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>19*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*53</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50DT8*50DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T8五面埋伏</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D*100D经纬T800珍珠点</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*49</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50D*50D*100D T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>T800双链条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克265</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>经消光低弹 双纬T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>20*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75D半光T800双纬平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75消低弹*75T8002/2斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*4*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>空变T8平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T8酷丝棉3/1.超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*300加厚超钛棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*4*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150*2-T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯370克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D消光75DT800 3/3斜</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>15.5*4*48</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100*75T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克250</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>37梭多乐绵</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>16*4*37</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*40S+150D T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>100D*40S+150D T8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>21*3*45</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯188克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">斜纹毛巾底 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>13.5*4*51</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*150T8*300低弹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*3*43</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>00克</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯300克</t>
   </si>
   <si>
     <t>天丝棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*3*32</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*三合一</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯195克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>天丝棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>80S*三合一</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯360克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>生态棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*35S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯370克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>210-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*30S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯285克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>加厚钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯390克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>230-钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*30S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯300克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">生态棉 加厚 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*31</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*35S*2</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯390克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270单股钛金棉</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*18S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>白坯360克</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>登山布</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>12.5*4*215*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75*450</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>白坯3</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10克</t>
-    </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯310克</t>
   </si>
   <si>
     <t>40*300平纹</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*24</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300D</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3398,13 +2996,6 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -3583,7 +3174,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3761,6 +3352,10 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3837,26 +3432,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3878,19 +3453,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3932,7 +3499,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3964,10 +3531,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3999,7 +3565,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4175,10 +3740,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M393"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="9" width="9" style="4"/>
     <col min="10" max="10" width="27" customWidth="1"/>
@@ -4186,7 +3751,7 @@
     <col min="12" max="12" width="24.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>688</v>
       </c>
@@ -4224,7 +3789,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
         <v>768</v>
       </c>
@@ -4235,7 +3800,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>770</v>
+        <v>4</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4258,7 +3823,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:13">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
@@ -4286,7 +3851,7 @@
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:13">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -4314,7 +3879,7 @@
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:13">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -4339,7 +3904,7 @@
       </c>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
@@ -4364,7 +3929,7 @@
       </c>
       <c r="I6" s="11"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:13">
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
@@ -4389,7 +3954,7 @@
       </c>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
@@ -4414,7 +3979,7 @@
       </c>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:13">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
@@ -4439,7 +4004,7 @@
       </c>
       <c r="I9" s="11"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
@@ -4464,7 +4029,7 @@
       </c>
       <c r="I10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
@@ -4489,7 +4054,7 @@
       </c>
       <c r="I11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13">
       <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
@@ -4514,7 +4079,7 @@
       </c>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:13">
       <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
@@ -4539,7 +4104,7 @@
       </c>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:13">
       <c r="A14" s="9" t="s">
         <v>28</v>
       </c>
@@ -4564,7 +4129,7 @@
       </c>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13">
       <c r="A15" s="9" t="s">
         <v>30</v>
       </c>
@@ -4589,7 +4154,7 @@
       </c>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:13">
       <c r="A16" s="9" t="s">
         <v>33</v>
       </c>
@@ -4614,7 +4179,7 @@
       </c>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9">
       <c r="A17" s="9" t="s">
         <v>35</v>
       </c>
@@ -4639,7 +4204,7 @@
       </c>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9">
       <c r="A18" s="9" t="s">
         <v>37</v>
       </c>
@@ -4664,7 +4229,7 @@
       </c>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9">
       <c r="A19" s="9" t="s">
         <v>40</v>
       </c>
@@ -4689,7 +4254,7 @@
       </c>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9">
       <c r="A20" s="9" t="s">
         <v>43</v>
       </c>
@@ -4714,7 +4279,7 @@
       </c>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9">
       <c r="A21" s="9" t="s">
         <v>47</v>
       </c>
@@ -4739,7 +4304,7 @@
       </c>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9">
       <c r="A22" s="9" t="s">
         <v>49</v>
       </c>
@@ -4764,7 +4329,7 @@
       </c>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9">
       <c r="A23" s="9" t="s">
         <v>51</v>
       </c>
@@ -4789,7 +4354,7 @@
       </c>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9">
       <c r="A24" s="9" t="s">
         <v>54</v>
       </c>
@@ -4814,7 +4379,7 @@
       </c>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:9">
       <c r="A25" s="9" t="s">
         <v>56</v>
       </c>
@@ -4839,7 +4404,7 @@
       </c>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9">
       <c r="A26" s="9" t="s">
         <v>58</v>
       </c>
@@ -4864,7 +4429,7 @@
       </c>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9">
       <c r="A27" s="9" t="s">
         <v>61</v>
       </c>
@@ -4889,7 +4454,7 @@
       </c>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9">
       <c r="A28" s="9" t="s">
         <v>64</v>
       </c>
@@ -4914,7 +4479,7 @@
       </c>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9">
       <c r="A29" s="9" t="s">
         <v>67</v>
       </c>
@@ -4922,7 +4487,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4939,7 +4504,7 @@
       </c>
       <c r="I29" s="11"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9">
       <c r="A30" s="9" t="s">
         <v>69</v>
       </c>
@@ -4947,7 +4512,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -4964,7 +4529,7 @@
       </c>
       <c r="I30" s="11"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9">
       <c r="A31" s="9" t="s">
         <v>71</v>
       </c>
@@ -4989,7 +4554,7 @@
       </c>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9">
       <c r="A32" s="9" t="s">
         <v>74</v>
       </c>
@@ -5014,7 +4579,7 @@
       </c>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9">
       <c r="A33" s="9" t="s">
         <v>76</v>
       </c>
@@ -5039,7 +4604,7 @@
       </c>
       <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9">
       <c r="A34" s="9" t="s">
         <v>78</v>
       </c>
@@ -5064,7 +4629,7 @@
       </c>
       <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9">
       <c r="A35" s="9" t="s">
         <v>81</v>
       </c>
@@ -5089,7 +4654,7 @@
       </c>
       <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:9">
       <c r="A36" s="9" t="s">
         <v>83</v>
       </c>
@@ -5114,7 +4679,7 @@
       </c>
       <c r="I36" s="11"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:9">
       <c r="A37" s="9" t="s">
         <v>86</v>
       </c>
@@ -5139,7 +4704,7 @@
       </c>
       <c r="I37" s="11"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9">
       <c r="A38" s="9" t="s">
         <v>89</v>
       </c>
@@ -5160,11 +4725,11 @@
         <v>165</v>
       </c>
       <c r="H38" s="10">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I38" s="11"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9">
       <c r="A39" s="9" t="s">
         <v>92</v>
       </c>
@@ -5189,7 +4754,7 @@
       </c>
       <c r="I39" s="11"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:9">
       <c r="A40" s="9" t="s">
         <v>94</v>
       </c>
@@ -5214,7 +4779,7 @@
       </c>
       <c r="I40" s="11"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:9">
       <c r="A41" s="9" t="s">
         <v>96</v>
       </c>
@@ -5222,7 +4787,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>773</v>
+        <v>3</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>98</v>
@@ -5239,7 +4804,7 @@
       </c>
       <c r="I41" s="11"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:9">
       <c r="A42" s="9" t="s">
         <v>99</v>
       </c>
@@ -5264,7 +4829,7 @@
       </c>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:9">
       <c r="A43" s="9" t="s">
         <v>101</v>
       </c>
@@ -5289,7 +4854,7 @@
       </c>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:9">
       <c r="A44" s="9" t="s">
         <v>104</v>
       </c>
@@ -5314,7 +4879,7 @@
       </c>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9">
       <c r="A45" s="9" t="s">
         <v>108</v>
       </c>
@@ -5339,7 +4904,7 @@
       </c>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9">
       <c r="A46" s="9" t="s">
         <v>111</v>
       </c>
@@ -5364,7 +4929,7 @@
       </c>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:9">
       <c r="A47" s="9" t="s">
         <v>113</v>
       </c>
@@ -5389,12 +4954,12 @@
       </c>
       <c r="I47" s="11"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:9">
       <c r="A48" s="9" t="s">
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>116</v>
@@ -5414,7 +4979,7 @@
       </c>
       <c r="I48" s="11"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9">
       <c r="A49" s="9" t="s">
         <v>117</v>
       </c>
@@ -5439,7 +5004,7 @@
       </c>
       <c r="I49" s="11"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9">
       <c r="A50" s="9" t="s">
         <v>119</v>
       </c>
@@ -5464,7 +5029,7 @@
       </c>
       <c r="I50" s="11"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9">
       <c r="A51" s="9" t="s">
         <v>122</v>
       </c>
@@ -5489,7 +5054,7 @@
       </c>
       <c r="I51" s="11"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9">
       <c r="A52" s="9" t="s">
         <v>124</v>
       </c>
@@ -5514,7 +5079,7 @@
       </c>
       <c r="I52" s="11"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9">
       <c r="A53" s="9" t="s">
         <v>126</v>
       </c>
@@ -5539,7 +5104,7 @@
       </c>
       <c r="I53" s="11"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9">
       <c r="A54" s="9" t="s">
         <v>128</v>
       </c>
@@ -5564,7 +5129,7 @@
       </c>
       <c r="I54" s="11"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9">
       <c r="A55" s="9" t="s">
         <v>131</v>
       </c>
@@ -5591,7 +5156,7 @@
       </c>
       <c r="I55" s="11"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9">
       <c r="A56" s="9" t="s">
         <v>135</v>
       </c>
@@ -5599,7 +5164,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>134</v>
@@ -5616,7 +5181,7 @@
       </c>
       <c r="I56" s="11"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9">
       <c r="A57" s="9" t="s">
         <v>137</v>
       </c>
@@ -5643,7 +5208,7 @@
       </c>
       <c r="I57" s="11"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9">
       <c r="A58" s="9" t="s">
         <v>140</v>
       </c>
@@ -5668,7 +5233,7 @@
       </c>
       <c r="I58" s="11"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9">
       <c r="A59" s="9" t="s">
         <v>144</v>
       </c>
@@ -5693,7 +5258,7 @@
       </c>
       <c r="I59" s="11"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9">
       <c r="A60" s="9" t="s">
         <v>148</v>
       </c>
@@ -5718,7 +5283,7 @@
       </c>
       <c r="I60" s="11"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9">
       <c r="A61" s="9" t="s">
         <v>150</v>
       </c>
@@ -5743,7 +5308,7 @@
       </c>
       <c r="I61" s="11"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9">
       <c r="A62" s="9" t="s">
         <v>153</v>
       </c>
@@ -5768,7 +5333,7 @@
       </c>
       <c r="I62" s="11"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9">
       <c r="A63" s="9" t="s">
         <v>156</v>
       </c>
@@ -5793,7 +5358,7 @@
       </c>
       <c r="I63" s="11"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9">
       <c r="A64" s="9" t="s">
         <v>158</v>
       </c>
@@ -5818,7 +5383,7 @@
       </c>
       <c r="I64" s="11"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9">
       <c r="A65" s="9" t="s">
         <v>162</v>
       </c>
@@ -5843,7 +5408,7 @@
       </c>
       <c r="I65" s="11"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9">
       <c r="A66" s="9" t="s">
         <v>165</v>
       </c>
@@ -5868,7 +5433,7 @@
       </c>
       <c r="I66" s="11"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9">
       <c r="A67" s="9" t="s">
         <v>167</v>
       </c>
@@ -5893,7 +5458,7 @@
       </c>
       <c r="I67" s="11"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9">
       <c r="A68" s="9" t="s">
         <v>171</v>
       </c>
@@ -5918,7 +5483,7 @@
       </c>
       <c r="I68" s="11"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9">
       <c r="A69" s="9" t="s">
         <v>174</v>
       </c>
@@ -5943,7 +5508,7 @@
       </c>
       <c r="I69" s="11"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9">
       <c r="A70" s="9" t="s">
         <v>176</v>
       </c>
@@ -5968,7 +5533,7 @@
       </c>
       <c r="I70" s="11"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9">
       <c r="A71" s="9" t="s">
         <v>178</v>
       </c>
@@ -5993,7 +5558,7 @@
       </c>
       <c r="I71" s="11"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9">
       <c r="A72" s="9" t="s">
         <v>180</v>
       </c>
@@ -6018,7 +5583,7 @@
       </c>
       <c r="I72" s="11"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9">
       <c r="A73" s="9" t="s">
         <v>182</v>
       </c>
@@ -6043,7 +5608,7 @@
       </c>
       <c r="I73" s="11"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9">
       <c r="A74" s="9" t="s">
         <v>184</v>
       </c>
@@ -6068,7 +5633,7 @@
       </c>
       <c r="I74" s="11"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9">
       <c r="A75" s="9" t="s">
         <v>187</v>
       </c>
@@ -6093,7 +5658,7 @@
       </c>
       <c r="I75" s="11"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9">
       <c r="A76" s="9" t="s">
         <v>189</v>
       </c>
@@ -6118,7 +5683,7 @@
       </c>
       <c r="I76" s="11"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:9">
       <c r="A77" s="9" t="s">
         <v>191</v>
       </c>
@@ -6126,7 +5691,7 @@
         <v>192</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>776</v>
+        <v>73</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>143</v>
@@ -6143,7 +5708,7 @@
       </c>
       <c r="I77" s="11"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:9">
       <c r="A78" s="9" t="s">
         <v>193</v>
       </c>
@@ -6168,7 +5733,7 @@
       </c>
       <c r="I78" s="11"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9">
       <c r="A79" s="9" t="s">
         <v>196</v>
       </c>
@@ -6193,7 +5758,7 @@
       </c>
       <c r="I79" s="11"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:9">
       <c r="A80" s="9" t="s">
         <v>199</v>
       </c>
@@ -6218,7 +5783,7 @@
       </c>
       <c r="I80" s="11"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9">
       <c r="A81" s="9" t="s">
         <v>202</v>
       </c>
@@ -6243,7 +5808,7 @@
       </c>
       <c r="I81" s="11"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9">
       <c r="A82" s="9" t="s">
         <v>204</v>
       </c>
@@ -6268,7 +5833,7 @@
       </c>
       <c r="I82" s="11"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9">
       <c r="A83" s="9" t="s">
         <v>207</v>
       </c>
@@ -6293,7 +5858,7 @@
       </c>
       <c r="I83" s="11"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9">
       <c r="A84" s="9" t="s">
         <v>209</v>
       </c>
@@ -6318,7 +5883,7 @@
       </c>
       <c r="I84" s="11"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9">
       <c r="A85" s="9" t="s">
         <v>211</v>
       </c>
@@ -6343,7 +5908,7 @@
       </c>
       <c r="I85" s="11"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9">
       <c r="A86" s="9" t="s">
         <v>213</v>
       </c>
@@ -6368,7 +5933,7 @@
       </c>
       <c r="I86" s="11"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9">
       <c r="A87" s="9" t="s">
         <v>215</v>
       </c>
@@ -6393,7 +5958,7 @@
       </c>
       <c r="I87" s="11"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9">
       <c r="A88" s="9" t="s">
         <v>217</v>
       </c>
@@ -6418,7 +5983,7 @@
       </c>
       <c r="I88" s="11"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9">
       <c r="A89" s="9" t="s">
         <v>219</v>
       </c>
@@ -6443,7 +6008,7 @@
       </c>
       <c r="I89" s="11"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9">
       <c r="A90" s="9" t="s">
         <v>222</v>
       </c>
@@ -6468,7 +6033,7 @@
       </c>
       <c r="I90" s="11"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9">
       <c r="A91" s="9" t="s">
         <v>225</v>
       </c>
@@ -6493,7 +6058,7 @@
       </c>
       <c r="I91" s="11"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9">
       <c r="A92" s="9" t="s">
         <v>228</v>
       </c>
@@ -6518,7 +6083,7 @@
       </c>
       <c r="I92" s="11"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9">
       <c r="A93" s="9" t="s">
         <v>230</v>
       </c>
@@ -6543,7 +6108,7 @@
       </c>
       <c r="I93" s="11"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9">
       <c r="A94" s="9" t="s">
         <v>233</v>
       </c>
@@ -6568,7 +6133,7 @@
       </c>
       <c r="I94" s="11"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9">
       <c r="A95" s="9" t="s">
         <v>235</v>
       </c>
@@ -6593,7 +6158,7 @@
       </c>
       <c r="I95" s="11"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9">
       <c r="A96" s="9" t="s">
         <v>238</v>
       </c>
@@ -6618,7 +6183,7 @@
       </c>
       <c r="I96" s="11"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:9">
       <c r="A97" s="9" t="s">
         <v>240</v>
       </c>
@@ -6643,7 +6208,7 @@
       </c>
       <c r="I97" s="11"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9">
       <c r="A98" s="9" t="s">
         <v>242</v>
       </c>
@@ -6668,7 +6233,7 @@
       </c>
       <c r="I98" s="11"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9">
       <c r="A99" s="9" t="s">
         <v>244</v>
       </c>
@@ -6693,7 +6258,7 @@
       </c>
       <c r="I99" s="11"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9">
       <c r="A100" s="9" t="s">
         <v>246</v>
       </c>
@@ -6718,7 +6283,7 @@
       </c>
       <c r="I100" s="11"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:9">
       <c r="A101" s="9" t="s">
         <v>248</v>
       </c>
@@ -6743,7 +6308,7 @@
       </c>
       <c r="I101" s="11"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9">
       <c r="A102" s="9" t="s">
         <v>251</v>
       </c>
@@ -6768,7 +6333,7 @@
       </c>
       <c r="I102" s="11"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:9">
       <c r="A103" s="9" t="s">
         <v>255</v>
       </c>
@@ -6793,7 +6358,7 @@
       </c>
       <c r="I103" s="11"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:9">
       <c r="A104" s="9" t="s">
         <v>259</v>
       </c>
@@ -6818,7 +6383,7 @@
       </c>
       <c r="I104" s="11"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:9">
       <c r="A105" s="9" t="s">
         <v>263</v>
       </c>
@@ -6843,7 +6408,7 @@
       </c>
       <c r="I105" s="11"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:9">
       <c r="A106" s="9" t="s">
         <v>266</v>
       </c>
@@ -6851,13 +6416,13 @@
         <v>267</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>777</v>
+        <v>253</v>
       </c>
       <c r="D106" s="22" t="s">
         <v>268</v>
       </c>
       <c r="E106" s="22">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F106" s="9"/>
       <c r="G106" s="11">
@@ -6868,7 +6433,7 @@
       </c>
       <c r="I106" s="11"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9">
       <c r="A107" s="9" t="s">
         <v>269</v>
       </c>
@@ -6893,7 +6458,7 @@
       </c>
       <c r="I107" s="11"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9">
       <c r="A108" s="9" t="s">
         <v>272</v>
       </c>
@@ -6918,7 +6483,7 @@
       </c>
       <c r="I108" s="11"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:9">
       <c r="A109" s="9" t="s">
         <v>275</v>
       </c>
@@ -6943,7 +6508,7 @@
       </c>
       <c r="I109" s="11"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:9">
       <c r="A110" s="9" t="s">
         <v>277</v>
       </c>
@@ -6968,7 +6533,7 @@
       </c>
       <c r="I110" s="11"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:9">
       <c r="A111" s="9" t="s">
         <v>279</v>
       </c>
@@ -6993,7 +6558,7 @@
       </c>
       <c r="I111" s="11"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9">
       <c r="A112" s="9" t="s">
         <v>281</v>
       </c>
@@ -7018,7 +6583,7 @@
       </c>
       <c r="I112" s="11"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9">
       <c r="A113" s="9" t="s">
         <v>283</v>
       </c>
@@ -7043,7 +6608,7 @@
       </c>
       <c r="I113" s="11"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9">
       <c r="A114" s="9" t="s">
         <v>285</v>
       </c>
@@ -7068,7 +6633,7 @@
       </c>
       <c r="I114" s="11"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:9">
       <c r="A115" s="9" t="s">
         <v>287</v>
       </c>
@@ -7093,7 +6658,7 @@
       </c>
       <c r="I115" s="11"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9">
       <c r="A116" s="9" t="s">
         <v>290</v>
       </c>
@@ -7118,7 +6683,7 @@
       </c>
       <c r="I116" s="11"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:9">
       <c r="A117" s="9" t="s">
         <v>293</v>
       </c>
@@ -7143,7 +6708,7 @@
       </c>
       <c r="I117" s="11"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9">
       <c r="A118" s="9" t="s">
         <v>295</v>
       </c>
@@ -7168,7 +6733,7 @@
       </c>
       <c r="I118" s="11"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9">
       <c r="A119" s="9" t="s">
         <v>298</v>
       </c>
@@ -7193,7 +6758,7 @@
       </c>
       <c r="I119" s="11"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:9">
       <c r="A120" s="9" t="s">
         <v>300</v>
       </c>
@@ -7218,7 +6783,7 @@
       </c>
       <c r="I120" s="11"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9">
       <c r="A121" s="9" t="s">
         <v>302</v>
       </c>
@@ -7243,7 +6808,7 @@
       </c>
       <c r="I121" s="11"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:9">
       <c r="A122" s="9" t="s">
         <v>304</v>
       </c>
@@ -7268,7 +6833,7 @@
       </c>
       <c r="I122" s="11"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9">
       <c r="A123" s="9" t="s">
         <v>306</v>
       </c>
@@ -7293,7 +6858,7 @@
       </c>
       <c r="I123" s="11"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:9">
       <c r="A124" s="9" t="s">
         <v>310</v>
       </c>
@@ -7318,7 +6883,7 @@
       </c>
       <c r="I124" s="11"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9">
       <c r="A125" s="9" t="s">
         <v>314</v>
       </c>
@@ -7343,7 +6908,7 @@
       </c>
       <c r="I125" s="11"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:9">
       <c r="A126" s="9" t="s">
         <v>316</v>
       </c>
@@ -7368,7 +6933,7 @@
       </c>
       <c r="I126" s="11"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:9">
       <c r="A127" s="9" t="s">
         <v>318</v>
       </c>
@@ -7393,7 +6958,7 @@
       </c>
       <c r="I127" s="11"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:9">
       <c r="A128" s="9" t="s">
         <v>322</v>
       </c>
@@ -7418,7 +6983,7 @@
       </c>
       <c r="I128" s="11"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:9">
       <c r="A129" s="9" t="s">
         <v>324</v>
       </c>
@@ -7443,7 +7008,7 @@
       </c>
       <c r="I129" s="11"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:9">
       <c r="A130" s="9" t="s">
         <v>326</v>
       </c>
@@ -7468,7 +7033,7 @@
       </c>
       <c r="I130" s="11"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:9">
       <c r="A131" s="9" t="s">
         <v>328</v>
       </c>
@@ -7476,7 +7041,7 @@
         <v>329</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>147</v>
@@ -7493,7 +7058,7 @@
       </c>
       <c r="I131" s="11"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:9">
       <c r="A132" s="9" t="s">
         <v>330</v>
       </c>
@@ -7518,7 +7083,7 @@
       </c>
       <c r="I132" s="11"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:9">
       <c r="A133" s="9" t="s">
         <v>334</v>
       </c>
@@ -7543,7 +7108,7 @@
       </c>
       <c r="I133" s="11"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:9">
       <c r="A134" s="9" t="s">
         <v>337</v>
       </c>
@@ -7566,7 +7131,7 @@
       </c>
       <c r="I134" s="11"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:9">
       <c r="A135" s="9" t="s">
         <v>340</v>
       </c>
@@ -7591,7 +7156,7 @@
       </c>
       <c r="I135" s="11"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:9">
       <c r="A136" s="9" t="s">
         <v>342</v>
       </c>
@@ -7612,11 +7177,11 @@
         <v>165</v>
       </c>
       <c r="H136" s="26">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I136" s="11"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:9">
       <c r="A137" s="9" t="s">
         <v>344</v>
       </c>
@@ -7641,7 +7206,7 @@
       </c>
       <c r="I137" s="11"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:9">
       <c r="A138" s="9" t="s">
         <v>348</v>
       </c>
@@ -7666,7 +7231,7 @@
       </c>
       <c r="I138" s="11"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:9">
       <c r="A139" s="9" t="s">
         <v>351</v>
       </c>
@@ -7691,7 +7256,7 @@
       </c>
       <c r="I139" s="11"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:9">
       <c r="A140" s="9" t="s">
         <v>354</v>
       </c>
@@ -7716,7 +7281,7 @@
       </c>
       <c r="I140" s="11"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:9">
       <c r="A141" s="9" t="s">
         <v>357</v>
       </c>
@@ -7741,7 +7306,7 @@
       </c>
       <c r="I141" s="11"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:9">
       <c r="A142" s="9" t="s">
         <v>359</v>
       </c>
@@ -7766,7 +7331,7 @@
       </c>
       <c r="I142" s="11"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:9">
       <c r="A143" s="9" t="s">
         <v>361</v>
       </c>
@@ -7791,7 +7356,7 @@
       </c>
       <c r="I143" s="11"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:9">
       <c r="A144" s="9" t="s">
         <v>363</v>
       </c>
@@ -7816,7 +7381,7 @@
       </c>
       <c r="I144" s="11"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:9">
       <c r="A145" s="9" t="s">
         <v>365</v>
       </c>
@@ -7841,7 +7406,7 @@
       </c>
       <c r="I145" s="11"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9">
       <c r="A146" s="9" t="s">
         <v>367</v>
       </c>
@@ -7866,7 +7431,7 @@
       </c>
       <c r="I146" s="11"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:9">
       <c r="A147" s="9" t="s">
         <v>369</v>
       </c>
@@ -7891,7 +7456,7 @@
       </c>
       <c r="I147" s="11"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:9">
       <c r="A148" s="9" t="s">
         <v>371</v>
       </c>
@@ -7916,7 +7481,7 @@
       </c>
       <c r="I148" s="11"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9">
       <c r="A149" s="9" t="s">
         <v>373</v>
       </c>
@@ -7941,7 +7506,7 @@
       </c>
       <c r="I149" s="11"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:9">
       <c r="A150" s="9" t="s">
         <v>376</v>
       </c>
@@ -7966,7 +7531,7 @@
       </c>
       <c r="I150" s="11"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9">
       <c r="A151" s="9" t="s">
         <v>380</v>
       </c>
@@ -7991,7 +7556,7 @@
       </c>
       <c r="I151" s="11"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:9">
       <c r="A152" s="9" t="s">
         <v>382</v>
       </c>
@@ -8018,7 +7583,7 @@
       </c>
       <c r="I152" s="11"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:9">
       <c r="A153" s="9" t="s">
         <v>386</v>
       </c>
@@ -8041,11 +7606,11 @@
         <v>216</v>
       </c>
       <c r="H153" s="13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I153" s="11"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9">
       <c r="A154" s="9" t="s">
         <v>389</v>
       </c>
@@ -8072,7 +7637,7 @@
       </c>
       <c r="I154" s="11"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:9">
       <c r="A155" s="9" t="s">
         <v>393</v>
       </c>
@@ -8099,7 +7664,7 @@
       </c>
       <c r="I155" s="11"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:9">
       <c r="A156" s="9" t="s">
         <v>395</v>
       </c>
@@ -8126,7 +7691,7 @@
       </c>
       <c r="I156" s="11"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:9">
       <c r="A157" s="9" t="s">
         <v>398</v>
       </c>
@@ -8149,11 +7714,11 @@
         <v>208</v>
       </c>
       <c r="H157" s="13">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I157" s="11"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:9">
       <c r="A158" s="9" t="s">
         <v>401</v>
       </c>
@@ -8161,7 +7726,7 @@
         <v>402</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>392</v>
@@ -8180,7 +7745,7 @@
       </c>
       <c r="I158" s="11"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:9">
       <c r="A159" s="9" t="s">
         <v>403</v>
       </c>
@@ -8205,7 +7770,7 @@
       </c>
       <c r="I159" s="11"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:9">
       <c r="A160" s="9" t="s">
         <v>406</v>
       </c>
@@ -8230,12 +7795,12 @@
       </c>
       <c r="I160" s="11"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:9">
       <c r="A161" s="9" t="s">
         <v>410</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>411</v>
@@ -8257,7 +7822,7 @@
       </c>
       <c r="I161" s="11"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:9">
       <c r="A162" s="9" t="s">
         <v>413</v>
       </c>
@@ -8284,7 +7849,7 @@
       </c>
       <c r="I162" s="11"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:9">
       <c r="A163" s="9" t="s">
         <v>416</v>
       </c>
@@ -8311,12 +7876,12 @@
       </c>
       <c r="I163" s="11"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:9">
       <c r="A164" s="9" t="s">
         <v>419</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>420</v>
@@ -8338,15 +7903,15 @@
       </c>
       <c r="I164" s="11"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:9">
       <c r="A165" s="9" t="s">
         <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>412</v>
@@ -8365,7 +7930,7 @@
       </c>
       <c r="I165" s="11"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:9">
       <c r="A166" s="9" t="s">
         <v>422</v>
       </c>
@@ -8378,18 +7943,18 @@
       <c r="H166" s="30"/>
       <c r="I166" s="11"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:9">
       <c r="A167" s="9" t="s">
         <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8405,18 +7970,18 @@
       </c>
       <c r="I167" s="11"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:9">
       <c r="A168" s="9" t="s">
         <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>788</v>
+        <v>415</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8432,12 +7997,12 @@
       </c>
       <c r="I168" s="11"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:9">
       <c r="A169" s="31" t="s">
         <v>425</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>426</v>
@@ -8459,12 +8024,12 @@
       </c>
       <c r="I169" s="32"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:9">
       <c r="A170" s="31" t="s">
         <v>428</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>429</v>
@@ -8486,12 +8051,12 @@
       </c>
       <c r="I170" s="32"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:9">
       <c r="A171" s="31" t="s">
         <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>237</v>
@@ -8513,7 +8078,7 @@
       </c>
       <c r="I171" s="32"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:9">
       <c r="A172" s="31" t="s">
         <v>431</v>
       </c>
@@ -8540,12 +8105,12 @@
       </c>
       <c r="I172" s="32"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:9">
       <c r="A173" s="31" t="s">
         <v>433</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>434</v>
@@ -8567,12 +8132,12 @@
       </c>
       <c r="I173" s="32"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:9">
       <c r="A174" s="31" t="s">
         <v>436</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>437</v>
@@ -8594,12 +8159,12 @@
       </c>
       <c r="I174" s="32"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:9">
       <c r="A175" s="31" t="s">
         <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8621,7 +8186,7 @@
       </c>
       <c r="I175" s="32"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:9">
       <c r="A176" s="31" t="s">
         <v>439</v>
       </c>
@@ -8648,7 +8213,7 @@
       </c>
       <c r="I176" s="32"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:9">
       <c r="A177" s="31" t="s">
         <v>441</v>
       </c>
@@ -8675,12 +8240,12 @@
       </c>
       <c r="I177" s="32"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:9">
       <c r="A178" s="31" t="s">
         <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>418</v>
@@ -8702,7 +8267,7 @@
       </c>
       <c r="I178" s="32"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:9">
       <c r="A179" s="31" t="s">
         <v>445</v>
       </c>
@@ -8729,12 +8294,12 @@
       </c>
       <c r="I179" s="32"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:9">
       <c r="A180" s="31" t="s">
         <v>448</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>449</v>
@@ -8756,12 +8321,12 @@
       </c>
       <c r="I180" s="32"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:9">
       <c r="A181" s="9" t="s">
         <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>443</v>
@@ -8783,12 +8348,12 @@
       </c>
       <c r="I181" s="11"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:9">
       <c r="A182" s="9" t="s">
         <v>451</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>308</v>
@@ -8806,16 +8371,16 @@
         <v>215</v>
       </c>
       <c r="H182" s="34">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I182" s="11"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:9">
       <c r="A183" s="9" t="s">
         <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>308</v>
@@ -8833,11 +8398,11 @@
         <v>215</v>
       </c>
       <c r="H183" s="34">
-        <v>4.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I183" s="11"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:9">
       <c r="A184" s="9" t="s">
         <v>454</v>
       </c>
@@ -8864,18 +8429,18 @@
       </c>
       <c r="I184" s="38"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:9">
       <c r="A185" s="9" t="s">
         <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>802</v>
+        <v>443</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>803</v>
+        <v>427</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8891,12 +8456,12 @@
       </c>
       <c r="I185" s="11"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:9">
       <c r="A186" s="9" t="s">
         <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>308</v>
@@ -8914,19 +8479,19 @@
         <v>215</v>
       </c>
       <c r="H186" s="34">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I186" s="11"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>806</v>
+        <v>237</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>435</v>
@@ -8945,18 +8510,18 @@
       </c>
       <c r="I187" s="11"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:9">
       <c r="A188" s="9" t="s">
         <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>808</v>
+        <v>271</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8972,12 +8537,12 @@
       </c>
       <c r="I188" s="11"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:9">
       <c r="A189" s="9" t="s">
         <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>443</v>
@@ -8999,18 +8564,18 @@
       </c>
       <c r="I189" s="11"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:9">
       <c r="A190" s="9" t="s">
         <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -9026,15 +8591,15 @@
       </c>
       <c r="I190" s="11"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:9">
       <c r="A191" s="9" t="s">
         <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>814</v>
+        <v>790</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>806</v>
+        <v>237</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>435</v>
@@ -9053,7 +8618,7 @@
       </c>
       <c r="I191" s="11"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:9">
       <c r="A192" s="9" t="s">
         <v>464</v>
       </c>
@@ -9066,7 +8631,7 @@
       <c r="H192" s="27"/>
       <c r="I192" s="11"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:9">
       <c r="A193" s="9" t="s">
         <v>465</v>
       </c>
@@ -9079,15 +8644,15 @@
       <c r="H193" s="39"/>
       <c r="I193" s="37"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:9">
       <c r="A194" s="9" t="s">
         <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>816</v>
+        <v>384</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>147</v>
@@ -9096,22 +8661,22 @@
         <v>138</v>
       </c>
       <c r="F194" s="44">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="G194" s="42">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="H194" s="41">
         <v>4.0999999999999996</v>
       </c>
       <c r="I194" s="37"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:9">
       <c r="A195" s="9" t="s">
         <v>467</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>468</v>
@@ -9126,22 +8691,22 @@
         <v>165</v>
       </c>
       <c r="G195" s="42">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H195" s="41">
         <v>3.9</v>
       </c>
       <c r="I195" s="37"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:9">
       <c r="A196" s="9" t="s">
         <v>469</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>470</v>
@@ -9149,10 +8714,10 @@
       <c r="E196" s="45">
         <v>105</v>
       </c>
-      <c r="F196" s="65">
+      <c r="F196" s="36">
         <v>155</v>
       </c>
-      <c r="G196" s="66">
+      <c r="G196" s="11">
         <v>215</v>
       </c>
       <c r="H196" s="45">
@@ -9160,15 +8725,15 @@
       </c>
       <c r="I196" s="11"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:9">
       <c r="A197" s="9" t="s">
         <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>385</v>
@@ -9176,10 +8741,10 @@
       <c r="E197" s="45">
         <v>100</v>
       </c>
-      <c r="F197" s="44">
+      <c r="F197" s="29">
         <v>150</v>
       </c>
-      <c r="G197" s="66">
+      <c r="G197" s="11">
         <v>215</v>
       </c>
       <c r="H197" s="45">
@@ -9187,12 +8752,12 @@
       </c>
       <c r="I197" s="37"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:9">
       <c r="A198" s="9" t="s">
         <v>472</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>822</v>
+        <v>811</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>473</v>
@@ -9203,10 +8768,10 @@
       <c r="E198" s="45">
         <v>129</v>
       </c>
-      <c r="F198" s="67">
+      <c r="F198" s="46">
         <v>183</v>
       </c>
-      <c r="G198" s="66">
+      <c r="G198" s="11">
         <v>215</v>
       </c>
       <c r="H198" s="45">
@@ -9214,26 +8779,26 @@
       </c>
       <c r="I198" s="37"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:9">
       <c r="A199" s="9" t="s">
         <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>824</v>
+        <v>400</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
       </c>
-      <c r="F199" s="44">
+      <c r="F199" s="29">
         <v>145</v>
       </c>
-      <c r="G199" s="66">
+      <c r="G199" s="11">
         <v>215</v>
       </c>
       <c r="H199" s="45">
@@ -9241,7 +8806,7 @@
       </c>
       <c r="I199" s="37"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:9">
       <c r="A200" s="9" t="s">
         <v>476</v>
       </c>
@@ -9254,7 +8819,7 @@
       <c r="H200" s="30"/>
       <c r="I200" s="37"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:9">
       <c r="A201" s="9" t="s">
         <v>477</v>
       </c>
@@ -9267,7 +8832,7 @@
       <c r="H201" s="10"/>
       <c r="I201" s="37"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:9">
       <c r="A202" s="9" t="s">
         <v>478</v>
       </c>
@@ -9280,7 +8845,7 @@
       <c r="H202" s="10"/>
       <c r="I202" s="37"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:9">
       <c r="A203" s="9" t="s">
         <v>479</v>
       </c>
@@ -9293,7 +8858,7 @@
       <c r="H203" s="10"/>
       <c r="I203" s="37"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:9">
       <c r="A204" s="9" t="s">
         <v>480</v>
       </c>
@@ -9307,10 +8872,10 @@
         <v>483</v>
       </c>
       <c r="E204" s="24"/>
-      <c r="F204" s="46">
+      <c r="F204" s="47">
         <v>52</v>
       </c>
-      <c r="G204" s="47">
+      <c r="G204" s="48">
         <v>175</v>
       </c>
       <c r="H204" s="24">
@@ -9318,7 +8883,7 @@
       </c>
       <c r="I204" s="37"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:9">
       <c r="A205" s="9" t="s">
         <v>484</v>
       </c>
@@ -9328,16 +8893,16 @@
       <c r="C205" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="D205" s="47" t="s">
+      <c r="D205" s="48" t="s">
         <v>487</v>
       </c>
       <c r="E205" s="24">
         <v>47</v>
       </c>
-      <c r="F205" s="46">
+      <c r="F205" s="47">
         <v>58</v>
       </c>
-      <c r="G205" s="47">
+      <c r="G205" s="48">
         <v>174</v>
       </c>
       <c r="H205" s="24">
@@ -9345,7 +8910,7 @@
       </c>
       <c r="I205" s="11"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:9">
       <c r="A206" s="9" t="s">
         <v>488</v>
       </c>
@@ -9355,16 +8920,16 @@
       <c r="C206" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="D206" s="47" t="s">
+      <c r="D206" s="48" t="s">
         <v>487</v>
       </c>
       <c r="E206" s="24">
         <v>47</v>
       </c>
-      <c r="F206" s="46">
+      <c r="F206" s="47">
         <v>54</v>
       </c>
-      <c r="G206" s="47">
+      <c r="G206" s="48">
         <v>174</v>
       </c>
       <c r="H206" s="24">
@@ -9372,7 +8937,7 @@
       </c>
       <c r="I206" s="11"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:9">
       <c r="A207" s="9" t="s">
         <v>491</v>
       </c>
@@ -9395,7 +8960,7 @@
       </c>
       <c r="I207" s="37"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:9">
       <c r="A208" s="9" t="s">
         <v>493</v>
       </c>
@@ -9403,7 +8968,7 @@
         <v>494</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9422,7 +8987,7 @@
       </c>
       <c r="I208" s="11"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:9">
       <c r="A209" s="9" t="s">
         <v>495</v>
       </c>
@@ -9445,7 +9010,7 @@
       </c>
       <c r="I209" s="37"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9">
       <c r="A210" s="9" t="s">
         <v>497</v>
       </c>
@@ -9458,7 +9023,7 @@
       <c r="H210" s="10"/>
       <c r="I210" s="37"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:9">
       <c r="A211" s="9" t="s">
         <v>498</v>
       </c>
@@ -9466,7 +9031,7 @@
         <v>499</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9483,15 +9048,15 @@
       </c>
       <c r="I211" s="37"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9">
       <c r="A212" s="9" t="s">
         <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>143</v>
@@ -9508,7 +9073,7 @@
       </c>
       <c r="I212" s="37"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:9">
       <c r="A213" s="9" t="s">
         <v>501</v>
       </c>
@@ -9535,7 +9100,7 @@
       </c>
       <c r="I213" s="37"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:9">
       <c r="A214" s="9" t="s">
         <v>504</v>
       </c>
@@ -9543,7 +9108,7 @@
         <v>505</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>143</v>
@@ -9560,7 +9125,7 @@
       </c>
       <c r="I214" s="37"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9">
       <c r="A215" s="9" t="s">
         <v>506</v>
       </c>
@@ -9573,7 +9138,7 @@
       <c r="H215" s="30"/>
       <c r="I215" s="37"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:9">
       <c r="A216" s="9" t="s">
         <v>507</v>
       </c>
@@ -9598,7 +9163,7 @@
       </c>
       <c r="I216" s="37"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9">
       <c r="A217" s="9" t="s">
         <v>511</v>
       </c>
@@ -9611,7 +9176,7 @@
       <c r="H217" s="30"/>
       <c r="I217" s="11"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:9">
       <c r="A218" s="9" t="s">
         <v>512</v>
       </c>
@@ -9624,7 +9189,7 @@
       <c r="H218" s="10"/>
       <c r="I218" s="37"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:9">
       <c r="A219" s="9" t="s">
         <v>513</v>
       </c>
@@ -9651,17 +9216,17 @@
       </c>
       <c r="I219" s="37"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:9">
       <c r="A220" s="9" t="s">
         <v>517</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>832</v>
-      </c>
-      <c r="D220" s="48" t="s">
+        <v>819</v>
+      </c>
+      <c r="D220" s="49" t="s">
         <v>518</v>
       </c>
       <c r="E220" s="10">
@@ -9677,21 +9242,21 @@
         <v>3.6</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
       <c r="A221" s="9" t="s">
         <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>835</v>
-      </c>
-      <c r="D221" s="48" t="s">
-        <v>770</v>
+        <v>822</v>
+      </c>
+      <c r="D221" s="49" t="s">
+        <v>4</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9706,21 +9271,21 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.15">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
       <c r="A222" s="9" t="s">
         <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>838</v>
-      </c>
-      <c r="D222" s="48" t="s">
-        <v>839</v>
+        <v>825</v>
+      </c>
+      <c r="D222" s="49" t="s">
+        <v>518</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9736,7 +9301,7 @@
       </c>
       <c r="I222" s="37"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:9">
       <c r="A223" s="9" t="s">
         <v>521</v>
       </c>
@@ -9746,7 +9311,7 @@
       <c r="C223" s="35" t="s">
         <v>523</v>
       </c>
-      <c r="D223" s="49" t="s">
+      <c r="D223" s="50" t="s">
         <v>4</v>
       </c>
       <c r="E223" s="35">
@@ -9763,18 +9328,18 @@
       </c>
       <c r="I223" s="37"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:9">
       <c r="A224" s="9" t="s">
         <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>841</v>
+        <v>827</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>842</v>
+        <v>828</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9790,7 +9355,7 @@
       </c>
       <c r="I224" s="37"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:9">
       <c r="A225" s="9" t="s">
         <v>525</v>
       </c>
@@ -9817,15 +9382,15 @@
       </c>
       <c r="I225" s="11"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:9">
       <c r="A226" s="9" t="s">
         <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>806</v>
+        <v>237</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>435</v>
@@ -9844,15 +9409,15 @@
       </c>
       <c r="I226" s="37"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:9">
       <c r="A227" s="9" t="s">
         <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>845</v>
+        <v>237</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>435</v>
@@ -9871,7 +9436,7 @@
       </c>
       <c r="I227" s="37"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:9">
       <c r="A228" s="9" t="s">
         <v>530</v>
       </c>
@@ -9898,7 +9463,7 @@
       </c>
       <c r="I228" s="11"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:9">
       <c r="A229" s="9" t="s">
         <v>532</v>
       </c>
@@ -9925,388 +9490,388 @@
       </c>
       <c r="I229" s="11"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:9">
       <c r="A230" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="B230" s="27" t="s">
+      <c r="B230" s="51" t="s">
         <v>535</v>
       </c>
-      <c r="C230" s="27" t="s">
+      <c r="C230" s="51" t="s">
         <v>456</v>
       </c>
-      <c r="D230" s="27" t="s">
+      <c r="D230" s="51" t="s">
         <v>435</v>
       </c>
-      <c r="E230" s="27">
+      <c r="E230" s="51">
         <v>145</v>
       </c>
-      <c r="F230" s="61">
+      <c r="F230" s="36">
         <v>225</v>
       </c>
-      <c r="G230" s="20">
+      <c r="G230" s="11">
         <v>215</v>
       </c>
-      <c r="H230" s="27">
+      <c r="H230" s="51">
         <v>5</v>
       </c>
-      <c r="I230" s="20"/>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I230" s="11"/>
+    </row>
+    <row r="231" spans="1:9">
       <c r="A231" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B231" s="27"/>
-      <c r="C231" s="27"/>
-      <c r="D231" s="49"/>
-      <c r="E231" s="27"/>
-      <c r="F231" s="29"/>
-      <c r="G231" s="20"/>
-      <c r="H231" s="27"/>
-      <c r="I231" s="20"/>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B231" s="18"/>
+      <c r="C231" s="18"/>
+      <c r="D231" s="33"/>
+      <c r="E231" s="18"/>
+      <c r="F231" s="31"/>
+      <c r="G231" s="32"/>
+      <c r="H231" s="18"/>
+      <c r="I231" s="11"/>
+    </row>
+    <row r="232" spans="1:9">
       <c r="A232" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="B232" s="39"/>
-      <c r="C232" s="39"/>
-      <c r="D232" s="39"/>
-      <c r="E232" s="39"/>
-      <c r="F232" s="61"/>
-      <c r="G232" s="40"/>
-      <c r="H232" s="39"/>
-      <c r="I232" s="40"/>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B232" s="35"/>
+      <c r="C232" s="35"/>
+      <c r="D232" s="35"/>
+      <c r="E232" s="35"/>
+      <c r="F232" s="36"/>
+      <c r="G232" s="37"/>
+      <c r="H232" s="35"/>
+      <c r="I232" s="37"/>
+    </row>
+    <row r="233" spans="1:9">
       <c r="A233" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="B233" s="39" t="s">
+      <c r="B233" s="35" t="s">
         <v>539</v>
       </c>
-      <c r="C233" s="39" t="s">
+      <c r="C233" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="D233" s="39" t="s">
+      <c r="D233" s="35" t="s">
         <v>541</v>
       </c>
-      <c r="E233" s="39">
+      <c r="E233" s="35">
         <v>185</v>
       </c>
-      <c r="F233" s="61">
+      <c r="F233" s="36">
         <v>270</v>
       </c>
-      <c r="G233" s="40">
+      <c r="G233" s="37">
         <v>215</v>
       </c>
-      <c r="H233" s="39">
+      <c r="H233" s="35">
         <v>5.3</v>
       </c>
-      <c r="I233" s="40"/>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I233" s="37"/>
+    </row>
+    <row r="234" spans="1:9">
       <c r="A234" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="B234" s="68" t="s">
-        <v>846</v>
-      </c>
-      <c r="C234" s="68" t="s">
-        <v>847</v>
-      </c>
-      <c r="D234" s="49" t="s">
-        <v>848</v>
-      </c>
-      <c r="E234" s="68">
+      <c r="B234" s="52" t="s">
+        <v>831</v>
+      </c>
+      <c r="C234" s="52" t="s">
+        <v>832</v>
+      </c>
+      <c r="D234" s="50" t="s">
+        <v>833</v>
+      </c>
+      <c r="E234" s="52">
         <v>190</v>
       </c>
-      <c r="F234" s="61">
+      <c r="F234" s="36">
         <v>275</v>
       </c>
-      <c r="G234" s="69">
+      <c r="G234" s="53">
         <v>215</v>
       </c>
-      <c r="H234" s="68">
+      <c r="H234" s="52">
         <v>5.8</v>
       </c>
-      <c r="I234" s="40" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I234" s="54" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
       <c r="A235" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B235" s="27" t="s">
-        <v>850</v>
-      </c>
-      <c r="C235" s="27" t="s">
-        <v>851</v>
-      </c>
-      <c r="D235" s="27" t="s">
-        <v>852</v>
-      </c>
-      <c r="E235" s="27">
+      <c r="B235" s="51" t="s">
+        <v>835</v>
+      </c>
+      <c r="C235" s="51" t="s">
+        <v>836</v>
+      </c>
+      <c r="D235" s="51" t="s">
+        <v>837</v>
+      </c>
+      <c r="E235" s="51">
         <v>155</v>
       </c>
-      <c r="F235" s="61">
+      <c r="F235" s="36">
         <v>230</v>
       </c>
-      <c r="G235" s="20">
+      <c r="G235" s="55">
         <v>215</v>
       </c>
-      <c r="H235" s="27">
+      <c r="H235" s="51">
         <v>4.7</v>
       </c>
-      <c r="I235" s="20" t="s">
+      <c r="I235" s="55" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:9">
       <c r="A236" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="B236" s="27"/>
-      <c r="C236" s="27"/>
-      <c r="D236" s="27"/>
-      <c r="E236" s="27"/>
-      <c r="F236" s="61"/>
-      <c r="G236" s="20"/>
-      <c r="H236" s="27"/>
-      <c r="I236" s="40"/>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B236" s="51"/>
+      <c r="C236" s="51"/>
+      <c r="D236" s="51"/>
+      <c r="E236" s="51"/>
+      <c r="F236" s="36"/>
+      <c r="G236" s="55"/>
+      <c r="H236" s="51"/>
+      <c r="I236" s="54"/>
+    </row>
+    <row r="237" spans="1:9">
       <c r="A237" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="B237" s="27" t="s">
-        <v>853</v>
-      </c>
-      <c r="C237" s="27" t="s">
+      <c r="B237" s="51" t="s">
+        <v>838</v>
+      </c>
+      <c r="C237" s="51" t="s">
         <v>547</v>
       </c>
-      <c r="D237" s="27" t="s">
-        <v>854</v>
-      </c>
-      <c r="E237" s="27">
+      <c r="D237" s="51" t="s">
+        <v>839</v>
+      </c>
+      <c r="E237" s="51">
         <v>155</v>
       </c>
-      <c r="F237" s="61">
+      <c r="F237" s="36">
         <v>230</v>
       </c>
-      <c r="G237" s="20">
+      <c r="G237" s="55">
         <v>218</v>
       </c>
-      <c r="H237" s="27">
+      <c r="H237" s="51">
         <v>5</v>
       </c>
-      <c r="I237" s="20" t="s">
+      <c r="I237" s="55" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:9">
       <c r="A238" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="B238" s="27" t="s">
-        <v>855</v>
-      </c>
-      <c r="C238" s="27" t="s">
-        <v>856</v>
-      </c>
-      <c r="D238" s="27" t="s">
-        <v>857</v>
-      </c>
-      <c r="E238" s="68">
+      <c r="B238" s="51" t="s">
+        <v>840</v>
+      </c>
+      <c r="C238" s="51" t="s">
+        <v>841</v>
+      </c>
+      <c r="D238" s="51" t="s">
+        <v>842</v>
+      </c>
+      <c r="E238" s="52">
         <v>190</v>
       </c>
-      <c r="F238" s="61">
+      <c r="F238" s="36">
         <v>270</v>
       </c>
-      <c r="G238" s="20">
+      <c r="G238" s="55">
         <v>216</v>
       </c>
-      <c r="H238" s="27">
+      <c r="H238" s="51">
         <v>5.7</v>
       </c>
-      <c r="I238" s="40" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I238" s="54" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
       <c r="A239" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="B239" s="27" t="s">
-        <v>859</v>
-      </c>
-      <c r="C239" s="27" t="s">
-        <v>860</v>
-      </c>
-      <c r="D239" s="27" t="s">
-        <v>857</v>
-      </c>
-      <c r="E239" s="68">
+      <c r="B239" s="51" t="s">
+        <v>844</v>
+      </c>
+      <c r="C239" s="51" t="s">
+        <v>845</v>
+      </c>
+      <c r="D239" s="51" t="s">
+        <v>842</v>
+      </c>
+      <c r="E239" s="52">
         <v>180</v>
       </c>
-      <c r="F239" s="61">
+      <c r="F239" s="36">
         <v>268</v>
       </c>
-      <c r="G239" s="20">
+      <c r="G239" s="55">
         <v>220</v>
       </c>
-      <c r="H239" s="27">
+      <c r="H239" s="51">
         <v>5.7</v>
       </c>
-      <c r="I239" s="40" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I239" s="54" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
       <c r="A240" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B240" s="27" t="s">
-        <v>862</v>
-      </c>
-      <c r="C240" s="27" t="s">
-        <v>863</v>
-      </c>
-      <c r="D240" s="27" t="s">
-        <v>857</v>
-      </c>
-      <c r="E240" s="68">
+      <c r="B240" s="51" t="s">
+        <v>846</v>
+      </c>
+      <c r="C240" s="51" t="s">
+        <v>847</v>
+      </c>
+      <c r="D240" s="51" t="s">
+        <v>842</v>
+      </c>
+      <c r="E240" s="52">
         <v>190</v>
       </c>
-      <c r="F240" s="61">
+      <c r="F240" s="36">
         <v>270</v>
       </c>
-      <c r="G240" s="20">
+      <c r="G240" s="55">
         <v>225</v>
       </c>
-      <c r="H240" s="39">
+      <c r="H240" s="35">
         <v>5.9</v>
       </c>
-      <c r="I240" s="40" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I240" s="54" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
       <c r="A241" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="B241" s="27" t="s">
-        <v>865</v>
-      </c>
-      <c r="C241" s="27" t="s">
-        <v>866</v>
-      </c>
-      <c r="D241" s="20" t="s">
+      <c r="B241" s="51" t="s">
+        <v>849</v>
+      </c>
+      <c r="C241" s="51" t="s">
+        <v>850</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="E241" s="27">
+      <c r="E241" s="51">
         <v>150</v>
       </c>
-      <c r="F241" s="61">
+      <c r="F241" s="36">
         <v>230</v>
       </c>
-      <c r="G241" s="20">
+      <c r="G241" s="55">
         <v>220</v>
       </c>
-      <c r="H241" s="68">
+      <c r="H241" s="52">
         <v>5.3</v>
       </c>
-      <c r="I241" s="20" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I241" s="55" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
       <c r="A242" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="B242" s="27" t="s">
-        <v>868</v>
-      </c>
-      <c r="C242" s="27" t="s">
-        <v>869</v>
-      </c>
-      <c r="D242" s="27" t="s">
-        <v>870</v>
-      </c>
-      <c r="E242" s="68">
+      <c r="B242" s="51" t="s">
+        <v>852</v>
+      </c>
+      <c r="C242" s="51" t="s">
+        <v>853</v>
+      </c>
+      <c r="D242" s="51" t="s">
+        <v>842</v>
+      </c>
+      <c r="E242" s="52">
         <v>160</v>
       </c>
-      <c r="F242" s="61">
+      <c r="F242" s="36">
         <v>250</v>
       </c>
-      <c r="G242" s="20">
+      <c r="G242" s="55">
         <v>225</v>
       </c>
-      <c r="H242" s="39">
+      <c r="H242" s="35">
         <v>5.4</v>
       </c>
-      <c r="I242" s="40" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I242" s="54" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
       <c r="A243" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="B243" s="27" t="s">
-        <v>872</v>
-      </c>
-      <c r="C243" s="27" t="s">
-        <v>873</v>
-      </c>
-      <c r="D243" s="27" t="s">
-        <v>874</v>
-      </c>
-      <c r="E243" s="68">
+      <c r="B243" s="51" t="s">
+        <v>855</v>
+      </c>
+      <c r="C243" s="51" t="s">
+        <v>856</v>
+      </c>
+      <c r="D243" s="51" t="s">
+        <v>857</v>
+      </c>
+      <c r="E243" s="52">
         <v>190</v>
       </c>
-      <c r="F243" s="61">
+      <c r="F243" s="36">
         <v>280</v>
       </c>
-      <c r="G243" s="20">
+      <c r="G243" s="55">
         <v>220</v>
       </c>
-      <c r="H243" s="39">
+      <c r="H243" s="35">
         <v>5.6</v>
       </c>
-      <c r="I243" s="40" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I243" s="54" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
       <c r="A244" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="B244" s="27" t="s">
-        <v>876</v>
-      </c>
-      <c r="C244" s="27" t="s">
-        <v>877</v>
-      </c>
-      <c r="D244" s="27" t="s">
-        <v>874</v>
-      </c>
-      <c r="E244" s="27">
+      <c r="B244" s="51" t="s">
+        <v>859</v>
+      </c>
+      <c r="C244" s="51" t="s">
+        <v>860</v>
+      </c>
+      <c r="D244" s="51" t="s">
+        <v>857</v>
+      </c>
+      <c r="E244" s="51">
         <v>110</v>
       </c>
-      <c r="F244" s="61">
+      <c r="F244" s="38">
         <v>160</v>
       </c>
-      <c r="G244" s="20">
+      <c r="G244" s="55">
         <v>220</v>
       </c>
-      <c r="H244" s="39">
+      <c r="H244" s="35">
         <v>3.9</v>
       </c>
-      <c r="I244" s="40"/>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I244" s="54"/>
+    </row>
+    <row r="245" spans="1:9">
       <c r="A245" s="9" t="s">
         <v>556</v>
       </c>
@@ -10319,18 +9884,18 @@
       <c r="H245" s="38"/>
       <c r="I245" s="11"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:9">
       <c r="A246" s="9" t="s">
         <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>878</v>
+        <v>861</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>879</v>
+        <v>862</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>803</v>
+        <v>427</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10346,12 +9911,12 @@
       </c>
       <c r="I246" s="37"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:9">
       <c r="A247" s="31" t="s">
         <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>880</v>
+        <v>863</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>527</v>
@@ -10371,14 +9936,14 @@
       <c r="H247" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I247" s="55"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I247" s="56"/>
+    </row>
+    <row r="248" spans="1:9">
       <c r="A248" s="31" t="s">
         <v>559</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>881</v>
+        <v>864</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>560</v>
@@ -10398,17 +9963,17 @@
       <c r="H248" s="18">
         <v>5.0999999999999996</v>
       </c>
-      <c r="I248" s="56"/>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I248" s="57"/>
+    </row>
+    <row r="249" spans="1:9">
       <c r="A249" s="31" t="s">
         <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>883</v>
+        <v>437</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>427</v>
@@ -10416,7 +9981,7 @@
       <c r="E249" s="32">
         <v>105</v>
       </c>
-      <c r="F249" s="57">
+      <c r="F249" s="58">
         <v>155</v>
       </c>
       <c r="G249" s="32">
@@ -10425,14 +9990,14 @@
       <c r="H249" s="32">
         <v>3.4</v>
       </c>
-      <c r="I249" s="56"/>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I249" s="57"/>
+    </row>
+    <row r="250" spans="1:9">
       <c r="A250" s="31" t="s">
         <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>152</v>
@@ -10443,7 +10008,7 @@
       <c r="E250" s="32">
         <v>108</v>
       </c>
-      <c r="F250" s="57">
+      <c r="F250" s="58">
         <v>150</v>
       </c>
       <c r="G250" s="32">
@@ -10454,12 +10019,12 @@
       </c>
       <c r="I250" s="32"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:9">
       <c r="A251" s="31" t="s">
         <v>563</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>885</v>
+        <v>867</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>564</v>
@@ -10470,7 +10035,7 @@
       <c r="E251" s="18">
         <v>116</v>
       </c>
-      <c r="F251" s="57">
+      <c r="F251" s="58">
         <v>180</v>
       </c>
       <c r="G251" s="32">
@@ -10481,15 +10046,15 @@
       </c>
       <c r="I251" s="32"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:9">
       <c r="A252" s="31" t="s">
         <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>887</v>
+        <v>437</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>427</v>
@@ -10497,7 +10062,7 @@
       <c r="E252" s="18">
         <v>105</v>
       </c>
-      <c r="F252" s="57">
+      <c r="F252" s="58">
         <v>155</v>
       </c>
       <c r="G252" s="32">
@@ -10508,12 +10073,12 @@
       </c>
       <c r="I252" s="32"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:9">
       <c r="A253" s="31" t="s">
         <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>888</v>
+        <v>869</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>564</v>
@@ -10524,7 +10089,7 @@
       <c r="E253" s="18">
         <v>116</v>
       </c>
-      <c r="F253" s="57">
+      <c r="F253" s="58">
         <v>180</v>
       </c>
       <c r="G253" s="32">
@@ -10535,18 +10100,18 @@
       </c>
       <c r="I253" s="32"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:9">
       <c r="A254" s="31" t="s">
         <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>889</v>
+        <v>870</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>890</v>
+        <v>871</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10560,16 +10125,16 @@
       <c r="H254" s="18">
         <v>5.5</v>
       </c>
-      <c r="I254" s="53" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I254" s="54" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
       <c r="A255" s="31" t="s">
         <v>568</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>892</v>
+        <v>872</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>569</v>
@@ -10577,61 +10142,61 @@
       <c r="D255" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="E255" s="58">
+      <c r="E255" s="59">
         <v>88</v>
       </c>
       <c r="F255" s="31">
         <v>130</v>
       </c>
-      <c r="G255" s="55">
+      <c r="G255" s="56">
         <v>208</v>
       </c>
-      <c r="H255" s="58">
+      <c r="H255" s="59">
         <v>3</v>
       </c>
-      <c r="I255" s="53"/>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I255" s="54"/>
+    </row>
+    <row r="256" spans="1:9">
       <c r="A256" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="B256" s="51" t="s">
-        <v>893</v>
-      </c>
-      <c r="C256" s="27" t="s">
-        <v>894</v>
-      </c>
-      <c r="D256" s="49" t="s">
-        <v>895</v>
-      </c>
-      <c r="E256" s="51">
+      <c r="B256" s="52" t="s">
+        <v>873</v>
+      </c>
+      <c r="C256" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D256" s="50" t="s">
+        <v>874</v>
+      </c>
+      <c r="E256" s="52">
         <v>190</v>
       </c>
       <c r="F256" s="36">
         <v>265</v>
       </c>
-      <c r="G256" s="52">
+      <c r="G256" s="53">
         <v>215</v>
       </c>
-      <c r="H256" s="59">
+      <c r="H256" s="60">
         <v>5.4</v>
       </c>
-      <c r="I256" s="53" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I256" s="54" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
       <c r="A257" s="9" t="s">
         <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>897</v>
+        <v>320</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>898</v>
+        <v>427</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10642,17 +10207,17 @@
       <c r="G257" s="36">
         <v>215</v>
       </c>
-      <c r="H257" s="59">
+      <c r="H257" s="60">
         <v>4.7</v>
       </c>
-      <c r="I257" s="59"/>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I257" s="60"/>
+    </row>
+    <row r="258" spans="1:9">
       <c r="A258" s="9" t="s">
         <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>899</v>
+        <v>866</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>152</v>
@@ -10663,7 +10228,7 @@
       <c r="E258" s="32">
         <v>108</v>
       </c>
-      <c r="F258" s="57">
+      <c r="F258" s="58">
         <v>160</v>
       </c>
       <c r="G258" s="32">
@@ -10672,9 +10237,9 @@
       <c r="H258" s="32">
         <v>3.4</v>
       </c>
-      <c r="I258" s="59"/>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I258" s="60"/>
+    </row>
+    <row r="259" spans="1:9">
       <c r="A259" s="9" t="s">
         <v>573</v>
       </c>
@@ -10684,10 +10249,10 @@
       <c r="E259" s="36"/>
       <c r="F259" s="36"/>
       <c r="G259" s="36"/>
-      <c r="H259" s="59"/>
-      <c r="I259" s="59"/>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H259" s="60"/>
+      <c r="I259" s="60"/>
+    </row>
+    <row r="260" spans="1:9">
       <c r="A260" s="9" t="s">
         <v>574</v>
       </c>
@@ -10697,10 +10262,10 @@
       <c r="E260" s="36"/>
       <c r="F260" s="36"/>
       <c r="G260" s="36"/>
-      <c r="H260" s="59"/>
-      <c r="I260" s="59"/>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H260" s="60"/>
+      <c r="I260" s="60"/>
+    </row>
+    <row r="261" spans="1:9">
       <c r="A261" s="9" t="s">
         <v>575</v>
       </c>
@@ -10710,8 +10275,8 @@
       <c r="C261" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="D261" s="48" t="s">
-        <v>900</v>
+      <c r="D261" s="49" t="s">
+        <v>877</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10725,19 +10290,19 @@
       <c r="H261" s="10">
         <v>3.6</v>
       </c>
-      <c r="I261" s="59"/>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I261" s="60"/>
+    </row>
+    <row r="262" spans="1:9">
       <c r="A262" s="9" t="s">
         <v>578</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="D262" s="48" t="s">
+      <c r="D262" s="49" t="s">
         <v>580</v>
       </c>
       <c r="E262" s="10">
@@ -10752,9 +10317,9 @@
       <c r="H262" s="10">
         <v>3.8</v>
       </c>
-      <c r="I262" s="59"/>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I262" s="60"/>
+    </row>
+    <row r="263" spans="1:9">
       <c r="A263" s="9" t="s">
         <v>581</v>
       </c>
@@ -10779,9 +10344,9 @@
       <c r="H263" s="27">
         <v>3.4</v>
       </c>
-      <c r="I263" s="59"/>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I263" s="60"/>
+    </row>
+    <row r="264" spans="1:9">
       <c r="A264" s="9" t="s">
         <v>585</v>
       </c>
@@ -10806,9 +10371,9 @@
       <c r="H264" s="10">
         <v>3.8</v>
       </c>
-      <c r="I264" s="59"/>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I264" s="60"/>
+    </row>
+    <row r="265" spans="1:9">
       <c r="A265" s="9" t="s">
         <v>589</v>
       </c>
@@ -10833,20 +10398,20 @@
       <c r="H265" s="35">
         <v>3.6</v>
       </c>
-      <c r="I265" s="59"/>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I265" s="60"/>
+    </row>
+    <row r="266" spans="1:9">
       <c r="A266" s="9" t="s">
         <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>903</v>
+        <v>860</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10860,20 +10425,20 @@
       <c r="H266" s="35">
         <v>3.5</v>
       </c>
-      <c r="I266" s="59"/>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I266" s="60"/>
+    </row>
+    <row r="267" spans="1:9">
       <c r="A267" s="9" t="s">
         <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>906</v>
-      </c>
-      <c r="D267" s="48" t="s">
-        <v>907</v>
+        <v>882</v>
+      </c>
+      <c r="D267" s="49" t="s">
+        <v>143</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10887,9 +10452,9 @@
       <c r="H267" s="10">
         <v>4</v>
       </c>
-      <c r="I267" s="60"/>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I267" s="61"/>
+    </row>
+    <row r="268" spans="1:9">
       <c r="A268" s="9" t="s">
         <v>595</v>
       </c>
@@ -10899,10 +10464,10 @@
       <c r="E268" s="36"/>
       <c r="F268" s="36"/>
       <c r="G268" s="36"/>
-      <c r="H268" s="59"/>
-      <c r="I268" s="59"/>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H268" s="60"/>
+      <c r="I268" s="60"/>
+    </row>
+    <row r="269" spans="1:9">
       <c r="A269" s="9" t="s">
         <v>596</v>
       </c>
@@ -10912,10 +10477,10 @@
       <c r="E269" s="36"/>
       <c r="F269" s="36"/>
       <c r="G269" s="36"/>
-      <c r="H269" s="59"/>
-      <c r="I269" s="59"/>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H269" s="60"/>
+      <c r="I269" s="60"/>
+    </row>
+    <row r="270" spans="1:9">
       <c r="A270" s="9" t="s">
         <v>597</v>
       </c>
@@ -10925,10 +10490,10 @@
       <c r="E270" s="36"/>
       <c r="F270" s="36"/>
       <c r="G270" s="36"/>
-      <c r="H270" s="59"/>
-      <c r="I270" s="59"/>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H270" s="60"/>
+      <c r="I270" s="60"/>
+    </row>
+    <row r="271" spans="1:9">
       <c r="A271" s="9" t="s">
         <v>598</v>
       </c>
@@ -10938,10 +10503,10 @@
       <c r="E271" s="36"/>
       <c r="F271" s="36"/>
       <c r="G271" s="36"/>
-      <c r="H271" s="59"/>
-      <c r="I271" s="59"/>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H271" s="60"/>
+      <c r="I271" s="60"/>
+    </row>
+    <row r="272" spans="1:9">
       <c r="A272" s="9" t="s">
         <v>599</v>
       </c>
@@ -10951,10 +10516,10 @@
       <c r="E272" s="36"/>
       <c r="F272" s="36"/>
       <c r="G272" s="36"/>
-      <c r="H272" s="59"/>
-      <c r="I272" s="59"/>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H272" s="60"/>
+      <c r="I272" s="60"/>
+    </row>
+    <row r="273" spans="1:9">
       <c r="A273" s="9" t="s">
         <v>600</v>
       </c>
@@ -10964,10 +10529,10 @@
       <c r="E273" s="36"/>
       <c r="F273" s="36"/>
       <c r="G273" s="36"/>
-      <c r="H273" s="59"/>
-      <c r="I273" s="59"/>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H273" s="60"/>
+      <c r="I273" s="60"/>
+    </row>
+    <row r="274" spans="1:9">
       <c r="A274" s="9" t="s">
         <v>601</v>
       </c>
@@ -10977,10 +10542,10 @@
       <c r="E274" s="36"/>
       <c r="F274" s="36"/>
       <c r="G274" s="36"/>
-      <c r="H274" s="59"/>
-      <c r="I274" s="59"/>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H274" s="60"/>
+      <c r="I274" s="60"/>
+    </row>
+    <row r="275" spans="1:9">
       <c r="A275" s="9" t="s">
         <v>602</v>
       </c>
@@ -10990,82 +10555,66 @@
       <c r="E275" s="36"/>
       <c r="F275" s="36"/>
       <c r="G275" s="36"/>
-      <c r="H275" s="59"/>
-      <c r="I275" s="59"/>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H275" s="60"/>
+      <c r="I275" s="60"/>
+    </row>
+    <row r="276" spans="1:9">
       <c r="A276" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="B276" s="36" t="s">
-        <v>908</v>
-      </c>
-      <c r="C276" s="36" t="s">
-        <v>909</v>
-      </c>
-      <c r="D276" s="27" t="s">
-        <v>910</v>
-      </c>
-      <c r="E276" s="36">
-        <v>185</v>
-      </c>
-      <c r="F276" s="36">
-        <v>270</v>
-      </c>
-      <c r="G276" s="36">
-        <v>215</v>
-      </c>
-      <c r="H276" s="60">
-        <v>6.2</v>
-      </c>
-      <c r="I276" s="11" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B276" s="36"/>
+      <c r="C276" s="36"/>
+      <c r="D276" s="36"/>
+      <c r="E276" s="36"/>
+      <c r="F276" s="36"/>
+      <c r="G276" s="36"/>
+      <c r="H276" s="60"/>
+      <c r="I276" s="60"/>
+    </row>
+    <row r="277" spans="1:9">
       <c r="A277" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="B277" s="51" t="s">
+      <c r="B277" s="52" t="s">
         <v>605</v>
       </c>
-      <c r="C277" s="51" t="s">
+      <c r="C277" s="52" t="s">
         <v>606</v>
       </c>
-      <c r="D277" s="51" t="s">
+      <c r="D277" s="52" t="s">
         <v>607</v>
       </c>
-      <c r="E277" s="51">
+      <c r="E277" s="52">
         <v>105</v>
       </c>
       <c r="F277" s="36">
         <v>140</v>
       </c>
-      <c r="G277" s="52">
+      <c r="G277" s="53">
         <v>215</v>
       </c>
-      <c r="H277" s="51">
+      <c r="H277" s="52">
         <v>4</v>
       </c>
-      <c r="I277" s="59"/>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I277" s="60"/>
+    </row>
+    <row r="278" spans="1:9">
       <c r="A278" s="9" t="s">
         <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>912</v>
+        <v>883</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>913</v>
+        <v>547</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>914</v>
+        <v>884</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
       </c>
-      <c r="F278" s="61">
+      <c r="F278" s="62">
         <v>230</v>
       </c>
       <c r="G278" s="20">
@@ -11074,17 +10623,17 @@
       <c r="H278" s="27">
         <v>4.7</v>
       </c>
-      <c r="I278" s="59"/>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I278" s="60"/>
+    </row>
+    <row r="279" spans="1:9">
       <c r="A279" s="9" t="s">
         <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>915</v>
-      </c>
-      <c r="C279" s="48" t="s">
-        <v>916</v>
+        <v>885</v>
+      </c>
+      <c r="C279" s="49" t="s">
+        <v>886</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>143</v>
@@ -11101,20 +10650,20 @@
       <c r="H279" s="10">
         <v>3.5</v>
       </c>
-      <c r="I279" s="59"/>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I279" s="60"/>
+    </row>
+    <row r="280" spans="1:9">
       <c r="A280" s="9" t="s">
         <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>917</v>
-      </c>
-      <c r="C280" s="48" t="s">
-        <v>918</v>
+        <v>887</v>
+      </c>
+      <c r="C280" s="49" t="s">
+        <v>888</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>919</v>
+        <v>487</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -11126,16 +10675,16 @@
       <c r="H280" s="10">
         <v>4.7</v>
       </c>
-      <c r="I280" s="59"/>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I280" s="60"/>
+    </row>
+    <row r="281" spans="1:9">
       <c r="A281" s="9" t="s">
         <v>611</v>
       </c>
       <c r="B281" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="C281" s="48" t="s">
+      <c r="C281" s="49" t="s">
         <v>613</v>
       </c>
       <c r="D281" s="10" t="s">
@@ -11153,16 +10702,16 @@
       <c r="H281" s="10">
         <v>3.5</v>
       </c>
-      <c r="I281" s="59"/>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I281" s="60"/>
+    </row>
+    <row r="282" spans="1:9">
       <c r="A282" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>920</v>
-      </c>
-      <c r="C282" s="48" t="s">
+        <v>889</v>
+      </c>
+      <c r="C282" s="49" t="s">
         <v>615</v>
       </c>
       <c r="D282" s="10" t="s">
@@ -11180,17 +10729,17 @@
       <c r="H282" s="10">
         <v>2.8</v>
       </c>
-      <c r="I282" s="59"/>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I282" s="60"/>
+    </row>
+    <row r="283" spans="1:9">
       <c r="A283" s="9" t="s">
         <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>921</v>
-      </c>
-      <c r="C283" s="48" t="s">
-        <v>922</v>
+        <v>890</v>
+      </c>
+      <c r="C283" s="49" t="s">
+        <v>891</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11207,20 +10756,20 @@
       <c r="H283" s="10">
         <v>3.7</v>
       </c>
-      <c r="I283" s="59"/>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I283" s="60"/>
+    </row>
+    <row r="284" spans="1:9">
       <c r="A284" s="9" t="s">
         <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>923</v>
+        <v>892</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>924</v>
+        <v>893</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>925</v>
+        <v>894</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11231,23 +10780,23 @@
       <c r="G284" s="36">
         <v>208</v>
       </c>
-      <c r="H284" s="59">
+      <c r="H284" s="60">
         <v>4.5</v>
       </c>
-      <c r="I284" s="59"/>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I284" s="60"/>
+    </row>
+    <row r="285" spans="1:9">
       <c r="A285" s="9" t="s">
         <v>618</v>
       </c>
       <c r="B285" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C285" s="48" t="s">
+      <c r="C285" s="49" t="s">
         <v>620</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>925</v>
+        <v>894</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11261,73 +10810,73 @@
       <c r="H285" s="10">
         <v>3.7</v>
       </c>
-      <c r="I285" s="59"/>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I285" s="60"/>
+    </row>
+    <row r="286" spans="1:9">
       <c r="A286" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="51" t="s">
-        <v>926</v>
-      </c>
-      <c r="C286" s="51" t="s">
-        <v>927</v>
-      </c>
-      <c r="D286" s="51" t="s">
+      <c r="B286" s="52" t="s">
+        <v>895</v>
+      </c>
+      <c r="C286" s="52" t="s">
+        <v>896</v>
+      </c>
+      <c r="D286" s="52" t="s">
         <v>622</v>
       </c>
-      <c r="E286" s="51">
+      <c r="E286" s="52">
         <v>85</v>
       </c>
       <c r="F286" s="36">
         <v>121</v>
       </c>
-      <c r="G286" s="52">
+      <c r="G286" s="53">
         <v>208</v>
       </c>
-      <c r="H286" s="51">
+      <c r="H286" s="52">
         <v>4</v>
       </c>
-      <c r="I286" s="59"/>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I286" s="60"/>
+    </row>
+    <row r="287" spans="1:9">
       <c r="A287" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="51" t="s">
-        <v>928</v>
-      </c>
-      <c r="C287" s="51" t="s">
-        <v>929</v>
-      </c>
-      <c r="D287" s="51" t="s">
-        <v>930</v>
-      </c>
-      <c r="E287" s="51">
+      <c r="B287" s="52" t="s">
+        <v>897</v>
+      </c>
+      <c r="C287" s="52" t="s">
+        <v>898</v>
+      </c>
+      <c r="D287" s="52" t="s">
+        <v>899</v>
+      </c>
+      <c r="E287" s="52">
         <v>88</v>
       </c>
       <c r="F287" s="36">
         <v>140</v>
       </c>
-      <c r="G287" s="52">
+      <c r="G287" s="53">
         <v>218</v>
       </c>
-      <c r="H287" s="51">
+      <c r="H287" s="52">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I287" s="60"/>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I287" s="61"/>
+    </row>
+    <row r="288" spans="1:9">
       <c r="A288" s="9" t="s">
         <v>624</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>931</v>
+        <v>900</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>625</v>
       </c>
-      <c r="D288" s="49" t="s">
+      <c r="D288" s="50" t="s">
         <v>4</v>
       </c>
       <c r="E288" s="27">
@@ -11342,9 +10891,9 @@
       <c r="H288" s="27">
         <v>5</v>
       </c>
-      <c r="I288" s="60"/>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I288" s="61"/>
+    </row>
+    <row r="289" spans="1:9">
       <c r="A289" s="9" t="s">
         <v>626</v>
       </c>
@@ -11354,7 +10903,7 @@
       <c r="C289" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="D289" s="48" t="s">
+      <c r="D289" s="49" t="s">
         <v>629</v>
       </c>
       <c r="E289" s="10">
@@ -11370,10 +10919,10 @@
         <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.15">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
       <c r="A290" s="9" t="s">
         <v>630</v>
       </c>
@@ -11383,7 +10932,7 @@
       <c r="C290" s="24" t="s">
         <v>632</v>
       </c>
-      <c r="D290" s="62" t="s">
+      <c r="D290" s="63" t="s">
         <v>39</v>
       </c>
       <c r="E290" s="24">
@@ -11392,107 +10941,107 @@
       <c r="F290" s="36">
         <v>100</v>
       </c>
-      <c r="G290" s="54">
+      <c r="G290" s="55">
         <v>220</v>
       </c>
       <c r="H290" s="24">
         <v>2.7</v>
       </c>
-      <c r="I290" s="60"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I290" s="61"/>
+    </row>
+    <row r="291" spans="1:9">
       <c r="A291" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="B291" s="63" t="s">
-        <v>933</v>
-      </c>
-      <c r="C291" s="63" t="s">
-        <v>934</v>
-      </c>
-      <c r="D291" s="63" t="s">
+      <c r="B291" s="64" t="s">
+        <v>902</v>
+      </c>
+      <c r="C291" s="64" t="s">
+        <v>903</v>
+      </c>
+      <c r="D291" s="64" t="s">
         <v>634</v>
       </c>
-      <c r="E291" s="63">
+      <c r="E291" s="64">
         <v>88</v>
       </c>
       <c r="F291" s="36">
         <v>130</v>
       </c>
-      <c r="G291" s="53">
+      <c r="G291" s="54">
         <v>220</v>
       </c>
-      <c r="H291" s="63">
+      <c r="H291" s="64">
         <v>3.5</v>
       </c>
-      <c r="I291" s="60"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I291" s="61"/>
+    </row>
+    <row r="292" spans="1:9">
       <c r="A292" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="B292" s="63" t="s">
-        <v>935</v>
-      </c>
-      <c r="C292" s="63" t="s">
+      <c r="B292" s="64" t="s">
+        <v>904</v>
+      </c>
+      <c r="C292" s="64" t="s">
         <v>636</v>
       </c>
-      <c r="D292" s="63" t="s">
+      <c r="D292" s="64" t="s">
         <v>637</v>
       </c>
-      <c r="E292" s="63">
+      <c r="E292" s="64">
         <v>80</v>
       </c>
       <c r="F292" s="36">
         <v>135</v>
       </c>
-      <c r="G292" s="53">
+      <c r="G292" s="54">
         <v>215</v>
       </c>
-      <c r="H292" s="63">
+      <c r="H292" s="64">
         <v>3.6</v>
       </c>
-      <c r="I292" s="60"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I292" s="61"/>
+    </row>
+    <row r="293" spans="1:9">
       <c r="A293" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="B293" s="64" t="s">
-        <v>936</v>
-      </c>
-      <c r="C293" s="63" t="s">
-        <v>937</v>
-      </c>
-      <c r="D293" s="63" t="s">
+      <c r="B293" s="65" t="s">
+        <v>905</v>
+      </c>
+      <c r="C293" s="64" t="s">
+        <v>906</v>
+      </c>
+      <c r="D293" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E293" s="64">
+      <c r="E293" s="65">
         <v>106</v>
       </c>
       <c r="F293" s="36">
         <v>145</v>
       </c>
-      <c r="G293" s="52">
+      <c r="G293" s="53">
         <v>215</v>
       </c>
-      <c r="H293" s="64">
+      <c r="H293" s="65">
         <v>3.7</v>
       </c>
-      <c r="I293" s="60"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I293" s="61"/>
+    </row>
+    <row r="294" spans="1:9">
       <c r="A294" s="9" t="s">
         <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>802</v>
+        <v>443</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>939</v>
+        <v>908</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11506,14 +11055,14 @@
       <c r="H294" s="18">
         <v>5</v>
       </c>
-      <c r="I294" s="60"/>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I294" s="61"/>
+    </row>
+    <row r="295" spans="1:9">
       <c r="A295" s="9" t="s">
         <v>640</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>940</v>
+        <v>909</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>641</v>
@@ -11529,9 +11078,9 @@
       <c r="H295" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I295" s="60"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I295" s="61"/>
+    </row>
+    <row r="296" spans="1:9">
       <c r="A296" s="9" t="s">
         <v>643</v>
       </c>
@@ -11554,20 +11103,20 @@
       <c r="H296" s="35">
         <v>3.8</v>
       </c>
-      <c r="I296" s="60"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I296" s="61"/>
+    </row>
+    <row r="297" spans="1:9">
       <c r="A297" s="9" t="s">
         <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>941</v>
+        <v>910</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>942</v>
+        <v>911</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>943</v>
+        <v>912</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11581,20 +11130,20 @@
       <c r="H297" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I297" s="53"/>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I297" s="54"/>
+    </row>
+    <row r="298" spans="1:9">
       <c r="A298" s="9" t="s">
         <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>944</v>
+        <v>913</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>945</v>
+        <v>914</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>946</v>
+        <v>915</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11609,39 +11158,39 @@
         <v>5.8</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
       <c r="A299" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="B299" s="50" t="s">
-        <v>948</v>
-      </c>
-      <c r="C299" s="50" t="s">
-        <v>949</v>
-      </c>
-      <c r="D299" s="50" t="s">
-        <v>950</v>
-      </c>
-      <c r="E299" s="50">
+      <c r="B299" s="51" t="s">
+        <v>917</v>
+      </c>
+      <c r="C299" s="51" t="s">
+        <v>918</v>
+      </c>
+      <c r="D299" s="51" t="s">
+        <v>919</v>
+      </c>
+      <c r="E299" s="51">
         <v>124</v>
       </c>
       <c r="F299" s="36">
         <v>180</v>
       </c>
-      <c r="G299" s="54">
+      <c r="G299" s="55">
         <v>218</v>
       </c>
-      <c r="H299" s="50">
+      <c r="H299" s="51">
         <v>5</v>
       </c>
-      <c r="I299" s="54" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I299" s="55" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
       <c r="A300" s="9" t="s">
         <v>650</v>
       </c>
@@ -11651,10 +11200,10 @@
       <c r="E300" s="36"/>
       <c r="F300" s="36"/>
       <c r="G300" s="36"/>
-      <c r="H300" s="60"/>
-      <c r="I300" s="60"/>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H300" s="61"/>
+      <c r="I300" s="61"/>
+    </row>
+    <row r="301" spans="1:9">
       <c r="A301" s="9" t="s">
         <v>651</v>
       </c>
@@ -11664,21 +11213,21 @@
       <c r="E301" s="36"/>
       <c r="F301" s="36"/>
       <c r="G301" s="36"/>
-      <c r="H301" s="60"/>
-      <c r="I301" s="60"/>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H301" s="61"/>
+      <c r="I301" s="61"/>
+    </row>
+    <row r="302" spans="1:9">
       <c r="A302" s="9" t="s">
         <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>952</v>
+        <v>921</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>953</v>
+        <v>922</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>954</v>
+        <v>923</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11690,11 +11239,11 @@
         <v>215</v>
       </c>
       <c r="H302" s="11">
-        <v>4.8</v>
-      </c>
-      <c r="I302" s="60"/>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.15">
+        <v>4.7</v>
+      </c>
+      <c r="I302" s="61"/>
+    </row>
+    <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
         <v>653</v>
       </c>
@@ -11705,7 +11254,7 @@
         <v>655</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>955</v>
+        <v>923</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11717,24 +11266,24 @@
         <v>215</v>
       </c>
       <c r="H303" s="10">
-        <v>4.3</v>
-      </c>
-      <c r="I303" s="60"/>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.15">
+        <v>4.2</v>
+      </c>
+      <c r="I303" s="61"/>
+    </row>
+    <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B304" s="63" t="s">
+      <c r="B304" s="64" t="s">
         <v>657</v>
       </c>
-      <c r="C304" s="63" t="s">
-        <v>956</v>
-      </c>
-      <c r="D304" s="63" t="s">
+      <c r="C304" s="64" t="s">
+        <v>250</v>
+      </c>
+      <c r="D304" s="64" t="s">
         <v>658</v>
       </c>
-      <c r="E304" s="63">
+      <c r="E304" s="64">
         <v>90</v>
       </c>
       <c r="F304" s="36">
@@ -11743,25 +11292,25 @@
       <c r="G304" s="37">
         <v>218</v>
       </c>
-      <c r="H304" s="63">
+      <c r="H304" s="64">
         <v>4.5</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.15">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9">
       <c r="A305" s="9" t="s">
         <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>958</v>
+        <v>925</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>959</v>
-      </c>
-      <c r="D305" s="27" t="s">
-        <v>960</v>
+        <v>926</v>
+      </c>
+      <c r="D305" s="18" t="s">
+        <v>927</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11772,25 +11321,41 @@
       <c r="G305" s="36">
         <v>225</v>
       </c>
-      <c r="H305" s="60">
+      <c r="H305" s="61">
         <v>7.2</v>
       </c>
-      <c r="I305" s="60"/>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I305" s="61"/>
+    </row>
+    <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="B306" s="36"/>
-      <c r="C306" s="36"/>
-      <c r="D306" s="27"/>
-      <c r="E306" s="36"/>
-      <c r="F306" s="36"/>
-      <c r="G306" s="36"/>
-      <c r="H306" s="60"/>
-      <c r="I306" s="11"/>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B306" s="36" t="s">
+        <v>928</v>
+      </c>
+      <c r="C306" s="36" t="s">
+        <v>871</v>
+      </c>
+      <c r="D306" s="36" t="s">
+        <v>929</v>
+      </c>
+      <c r="E306" s="36">
+        <v>185</v>
+      </c>
+      <c r="F306" s="36">
+        <v>270</v>
+      </c>
+      <c r="G306" s="36">
+        <v>215</v>
+      </c>
+      <c r="H306" s="61">
+        <v>6.2</v>
+      </c>
+      <c r="I306" s="61" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
         <v>661</v>
       </c>
@@ -11800,10 +11365,10 @@
       <c r="E307" s="36"/>
       <c r="F307" s="36"/>
       <c r="G307" s="36"/>
-      <c r="H307" s="60"/>
-      <c r="I307" s="60"/>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H307" s="61"/>
+      <c r="I307" s="61"/>
+    </row>
+    <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
         <v>662</v>
       </c>
@@ -11813,10 +11378,10 @@
       <c r="E308" s="36"/>
       <c r="F308" s="36"/>
       <c r="G308" s="36"/>
-      <c r="H308" s="60"/>
-      <c r="I308" s="60"/>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H308" s="61"/>
+      <c r="I308" s="61"/>
+    </row>
+    <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
         <v>663</v>
       </c>
@@ -11826,10 +11391,10 @@
       <c r="E309" s="36"/>
       <c r="F309" s="36"/>
       <c r="G309" s="36"/>
-      <c r="H309" s="60"/>
-      <c r="I309" s="60"/>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H309" s="61"/>
+      <c r="I309" s="61"/>
+    </row>
+    <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
         <v>664</v>
       </c>
@@ -11839,10 +11404,10 @@
       <c r="E310" s="36"/>
       <c r="F310" s="36"/>
       <c r="G310" s="36"/>
-      <c r="H310" s="60"/>
-      <c r="I310" s="60"/>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H310" s="61"/>
+      <c r="I310" s="61"/>
+    </row>
+    <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
         <v>665</v>
       </c>
@@ -11850,7 +11415,7 @@
         <v>666</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>961</v>
+        <v>670</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>667</v>
@@ -11867,9 +11432,9 @@
       <c r="H311" s="35">
         <v>3.8</v>
       </c>
-      <c r="I311" s="60"/>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I311" s="61"/>
+    </row>
+    <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
         <v>668</v>
       </c>
@@ -11894,9 +11459,9 @@
       <c r="H312" s="10">
         <v>3.7</v>
       </c>
-      <c r="I312" s="60"/>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I312" s="61"/>
+    </row>
+    <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
         <v>672</v>
       </c>
@@ -11906,10 +11471,10 @@
       <c r="E313" s="36"/>
       <c r="F313" s="36"/>
       <c r="G313" s="36"/>
-      <c r="H313" s="60"/>
-      <c r="I313" s="60"/>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H313" s="61"/>
+      <c r="I313" s="61"/>
+    </row>
+    <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
         <v>673</v>
       </c>
@@ -11919,21 +11484,21 @@
       <c r="E314" s="36"/>
       <c r="F314" s="36"/>
       <c r="G314" s="36"/>
-      <c r="H314" s="60"/>
-      <c r="I314" s="60"/>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H314" s="61"/>
+      <c r="I314" s="61"/>
+    </row>
+    <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
         <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>962</v>
+        <v>931</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>963</v>
+        <v>932</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11944,25 +11509,25 @@
       <c r="G315" s="36">
         <v>225</v>
       </c>
-      <c r="H315" s="60">
+      <c r="H315" s="61">
         <v>5</v>
       </c>
-      <c r="I315" s="60" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I315" s="61" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9">
       <c r="A316" s="9" t="s">
         <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>965</v>
+        <v>934</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>966</v>
+        <v>935</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>967</v>
+        <v>936</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11973,25 +11538,25 @@
       <c r="G316" s="36">
         <v>215</v>
       </c>
-      <c r="H316" s="60">
+      <c r="H316" s="61">
         <v>5.2</v>
       </c>
-      <c r="I316" s="60" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I316" s="61" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9">
       <c r="A317" s="9" t="s">
         <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>969</v>
+        <v>938</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>970</v>
+        <v>939</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>971</v>
+        <v>940</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -12006,21 +11571,21 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.15">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9">
       <c r="A318" s="9" t="s">
         <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>973</v>
+        <v>938</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>974</v>
+        <v>942</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>975</v>
+        <v>940</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -12036,47 +11601,47 @@
       </c>
       <c r="I318" s="11"/>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:9">
       <c r="A319" s="9" t="s">
         <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>976</v>
+        <v>943</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>977</v>
+        <v>914</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>910</v>
+        <v>929</v>
       </c>
       <c r="E319" s="18">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="F319" s="31">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G319" s="32">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="H319" s="18">
         <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.15">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9">
       <c r="A320" s="9" t="s">
         <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>979</v>
+        <v>945</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>980</v>
+        <v>946</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -12091,21 +11656,21 @@
         <v>5.7</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.15">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9">
       <c r="A321" s="9" t="s">
         <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>982</v>
+        <v>947</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>983</v>
+        <v>948</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>984</v>
+        <v>949</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -12120,21 +11685,21 @@
         <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.15">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9">
       <c r="A322" s="9" t="s">
         <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>986</v>
+        <v>951</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>987</v>
+        <v>952</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>988</v>
+        <v>929</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -12149,21 +11714,21 @@
         <v>6.2</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.15">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9">
       <c r="A323" s="9" t="s">
         <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>990</v>
+        <v>954</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>991</v>
+        <v>146</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>992</v>
+        <v>949</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -12178,21 +11743,21 @@
         <v>4.7</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.15">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9">
       <c r="A324" s="9" t="s">
         <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>994</v>
+        <v>955</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>995</v>
+        <v>956</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>996</v>
+        <v>929</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -12207,50 +11772,50 @@
         <v>6.7</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.15">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="B325" s="18" t="s">
-        <v>998</v>
-      </c>
-      <c r="C325" s="18" t="s">
-        <v>945</v>
-      </c>
-      <c r="D325" s="18" t="s">
-        <v>999</v>
-      </c>
-      <c r="E325" s="18">
+      <c r="B325" s="36" t="s">
+        <v>957</v>
+      </c>
+      <c r="C325" s="36" t="s">
+        <v>914</v>
+      </c>
+      <c r="D325" s="36" t="s">
+        <v>958</v>
+      </c>
+      <c r="E325" s="36">
         <v>185</v>
       </c>
-      <c r="F325" s="31">
+      <c r="F325" s="36">
         <v>270</v>
       </c>
-      <c r="G325" s="32">
+      <c r="G325" s="36">
         <v>225</v>
       </c>
-      <c r="H325" s="18">
+      <c r="H325" s="61">
         <v>5.2</v>
       </c>
-      <c r="I325" s="11" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I325" s="61" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9">
       <c r="A326" s="9" t="s">
         <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
-        <v>1001</v>
+        <v>959</v>
       </c>
       <c r="C326" s="36" t="s">
-        <v>1002</v>
+        <v>960</v>
       </c>
       <c r="D326" s="36" t="s">
-        <v>1003</v>
+        <v>961</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -12259,25 +11824,25 @@
       <c r="G326" s="36">
         <v>220</v>
       </c>
-      <c r="H326" s="60">
+      <c r="H326" s="61">
         <v>5.8</v>
       </c>
-      <c r="I326" s="60" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I326" s="61" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9">
       <c r="A327" s="9" t="s">
         <v>700</v>
       </c>
       <c r="B327" s="36" t="s">
-        <v>1005</v>
+        <v>963</v>
       </c>
       <c r="C327" s="36" t="s">
-        <v>1006</v>
+        <v>449</v>
       </c>
       <c r="D327" s="36" t="s">
-        <v>1007</v>
+        <v>964</v>
       </c>
       <c r="E327" s="36">
         <v>150</v>
@@ -12288,12 +11853,12 @@
       <c r="G327" s="36">
         <v>208</v>
       </c>
-      <c r="H327" s="60">
+      <c r="H327" s="61">
         <v>5</v>
       </c>
-      <c r="I327" s="60"/>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="I327" s="61"/>
+    </row>
+    <row r="328" spans="1:9">
       <c r="A328" s="9" t="s">
         <v>701</v>
       </c>
@@ -12303,10 +11868,10 @@
       <c r="E328" s="36"/>
       <c r="F328" s="36"/>
       <c r="G328" s="36"/>
-      <c r="H328" s="60"/>
-      <c r="I328" s="60"/>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H328" s="61"/>
+      <c r="I328" s="61"/>
+    </row>
+    <row r="329" spans="1:9">
       <c r="A329" s="9" t="s">
         <v>702</v>
       </c>
@@ -12316,10 +11881,10 @@
       <c r="E329" s="36"/>
       <c r="F329" s="36"/>
       <c r="G329" s="36"/>
-      <c r="H329" s="60"/>
-      <c r="I329" s="60"/>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H329" s="61"/>
+      <c r="I329" s="61"/>
+    </row>
+    <row r="330" spans="1:9">
       <c r="A330" s="9" t="s">
         <v>703</v>
       </c>
@@ -12329,10 +11894,10 @@
       <c r="E330" s="36"/>
       <c r="F330" s="36"/>
       <c r="G330" s="36"/>
-      <c r="H330" s="60"/>
-      <c r="I330" s="60"/>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H330" s="61"/>
+      <c r="I330" s="61"/>
+    </row>
+    <row r="331" spans="1:9">
       <c r="A331" s="9" t="s">
         <v>704</v>
       </c>
@@ -12342,10 +11907,10 @@
       <c r="E331" s="36"/>
       <c r="F331" s="36"/>
       <c r="G331" s="36"/>
-      <c r="H331" s="60"/>
-      <c r="I331" s="60"/>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H331" s="61"/>
+      <c r="I331" s="61"/>
+    </row>
+    <row r="332" spans="1:9">
       <c r="A332" s="9" t="s">
         <v>705</v>
       </c>
@@ -12355,10 +11920,10 @@
       <c r="E332" s="36"/>
       <c r="F332" s="36"/>
       <c r="G332" s="36"/>
-      <c r="H332" s="60"/>
-      <c r="I332" s="60"/>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H332" s="61"/>
+      <c r="I332" s="61"/>
+    </row>
+    <row r="333" spans="1:9">
       <c r="A333" s="9" t="s">
         <v>706</v>
       </c>
@@ -12368,10 +11933,10 @@
       <c r="E333" s="36"/>
       <c r="F333" s="36"/>
       <c r="G333" s="36"/>
-      <c r="H333" s="60"/>
-      <c r="I333" s="60"/>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H333" s="61"/>
+      <c r="I333" s="61"/>
+    </row>
+    <row r="334" spans="1:9">
       <c r="A334" s="9" t="s">
         <v>707</v>
       </c>
@@ -12381,10 +11946,10 @@
       <c r="E334" s="36"/>
       <c r="F334" s="36"/>
       <c r="G334" s="36"/>
-      <c r="H334" s="60"/>
-      <c r="I334" s="60"/>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H334" s="61"/>
+      <c r="I334" s="61"/>
+    </row>
+    <row r="335" spans="1:9">
       <c r="A335" s="9" t="s">
         <v>708</v>
       </c>
@@ -12394,10 +11959,10 @@
       <c r="E335" s="36"/>
       <c r="F335" s="36"/>
       <c r="G335" s="36"/>
-      <c r="H335" s="60"/>
-      <c r="I335" s="60"/>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H335" s="61"/>
+      <c r="I335" s="61"/>
+    </row>
+    <row r="336" spans="1:9">
       <c r="A336" s="9" t="s">
         <v>709</v>
       </c>
@@ -12407,10 +11972,10 @@
       <c r="E336" s="36"/>
       <c r="F336" s="36"/>
       <c r="G336" s="36"/>
-      <c r="H336" s="60"/>
-      <c r="I336" s="60"/>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H336" s="61"/>
+      <c r="I336" s="61"/>
+    </row>
+    <row r="337" spans="1:9">
       <c r="A337" s="9" t="s">
         <v>710</v>
       </c>
@@ -12420,10 +11985,10 @@
       <c r="E337" s="36"/>
       <c r="F337" s="36"/>
       <c r="G337" s="36"/>
-      <c r="H337" s="60"/>
-      <c r="I337" s="60"/>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H337" s="61"/>
+      <c r="I337" s="61"/>
+    </row>
+    <row r="338" spans="1:9">
       <c r="A338" s="9" t="s">
         <v>711</v>
       </c>
@@ -12433,10 +11998,10 @@
       <c r="E338" s="36"/>
       <c r="F338" s="36"/>
       <c r="G338" s="36"/>
-      <c r="H338" s="60"/>
-      <c r="I338" s="60"/>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H338" s="61"/>
+      <c r="I338" s="61"/>
+    </row>
+    <row r="339" spans="1:9">
       <c r="A339" s="9" t="s">
         <v>712</v>
       </c>
@@ -12446,10 +12011,10 @@
       <c r="E339" s="36"/>
       <c r="F339" s="36"/>
       <c r="G339" s="36"/>
-      <c r="H339" s="60"/>
-      <c r="I339" s="60"/>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H339" s="61"/>
+      <c r="I339" s="61"/>
+    </row>
+    <row r="340" spans="1:9">
       <c r="A340" s="9" t="s">
         <v>713</v>
       </c>
@@ -12459,10 +12024,10 @@
       <c r="E340" s="36"/>
       <c r="F340" s="36"/>
       <c r="G340" s="36"/>
-      <c r="H340" s="60"/>
-      <c r="I340" s="60"/>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H340" s="61"/>
+      <c r="I340" s="61"/>
+    </row>
+    <row r="341" spans="1:9">
       <c r="A341" s="9" t="s">
         <v>714</v>
       </c>
@@ -12472,10 +12037,10 @@
       <c r="E341" s="36"/>
       <c r="F341" s="36"/>
       <c r="G341" s="36"/>
-      <c r="H341" s="60"/>
-      <c r="I341" s="60"/>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H341" s="61"/>
+      <c r="I341" s="61"/>
+    </row>
+    <row r="342" spans="1:9">
       <c r="A342" s="9" t="s">
         <v>715</v>
       </c>
@@ -12485,10 +12050,10 @@
       <c r="E342" s="36"/>
       <c r="F342" s="36"/>
       <c r="G342" s="36"/>
-      <c r="H342" s="60"/>
-      <c r="I342" s="60"/>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H342" s="61"/>
+      <c r="I342" s="61"/>
+    </row>
+    <row r="343" spans="1:9">
       <c r="A343" s="9" t="s">
         <v>716</v>
       </c>
@@ -12498,10 +12063,10 @@
       <c r="E343" s="36"/>
       <c r="F343" s="36"/>
       <c r="G343" s="36"/>
-      <c r="H343" s="60"/>
-      <c r="I343" s="60"/>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H343" s="61"/>
+      <c r="I343" s="61"/>
+    </row>
+    <row r="344" spans="1:9">
       <c r="A344" s="9" t="s">
         <v>717</v>
       </c>
@@ -12511,10 +12076,10 @@
       <c r="E344" s="36"/>
       <c r="F344" s="36"/>
       <c r="G344" s="36"/>
-      <c r="H344" s="60"/>
-      <c r="I344" s="60"/>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H344" s="61"/>
+      <c r="I344" s="61"/>
+    </row>
+    <row r="345" spans="1:9">
       <c r="A345" s="9" t="s">
         <v>718</v>
       </c>
@@ -12524,10 +12089,10 @@
       <c r="E345" s="36"/>
       <c r="F345" s="36"/>
       <c r="G345" s="36"/>
-      <c r="H345" s="60"/>
-      <c r="I345" s="60"/>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H345" s="61"/>
+      <c r="I345" s="61"/>
+    </row>
+    <row r="346" spans="1:9">
       <c r="A346" s="9" t="s">
         <v>719</v>
       </c>
@@ -12537,10 +12102,10 @@
       <c r="E346" s="36"/>
       <c r="F346" s="36"/>
       <c r="G346" s="36"/>
-      <c r="H346" s="60"/>
-      <c r="I346" s="60"/>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H346" s="61"/>
+      <c r="I346" s="61"/>
+    </row>
+    <row r="347" spans="1:9">
       <c r="A347" s="9" t="s">
         <v>720</v>
       </c>
@@ -12550,10 +12115,10 @@
       <c r="E347" s="36"/>
       <c r="F347" s="36"/>
       <c r="G347" s="36"/>
-      <c r="H347" s="60"/>
-      <c r="I347" s="60"/>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H347" s="61"/>
+      <c r="I347" s="61"/>
+    </row>
+    <row r="348" spans="1:9">
       <c r="A348" s="9" t="s">
         <v>721</v>
       </c>
@@ -12563,10 +12128,10 @@
       <c r="E348" s="36"/>
       <c r="F348" s="36"/>
       <c r="G348" s="36"/>
-      <c r="H348" s="60"/>
-      <c r="I348" s="60"/>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H348" s="61"/>
+      <c r="I348" s="61"/>
+    </row>
+    <row r="349" spans="1:9">
       <c r="A349" s="9" t="s">
         <v>722</v>
       </c>
@@ -12576,10 +12141,10 @@
       <c r="E349" s="36"/>
       <c r="F349" s="36"/>
       <c r="G349" s="36"/>
-      <c r="H349" s="60"/>
-      <c r="I349" s="60"/>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H349" s="61"/>
+      <c r="I349" s="61"/>
+    </row>
+    <row r="350" spans="1:9">
       <c r="A350" s="9" t="s">
         <v>723</v>
       </c>
@@ -12589,10 +12154,10 @@
       <c r="E350" s="36"/>
       <c r="F350" s="36"/>
       <c r="G350" s="36"/>
-      <c r="H350" s="60"/>
-      <c r="I350" s="60"/>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H350" s="61"/>
+      <c r="I350" s="61"/>
+    </row>
+    <row r="351" spans="1:9">
       <c r="A351" s="9" t="s">
         <v>724</v>
       </c>
@@ -12602,10 +12167,10 @@
       <c r="E351" s="36"/>
       <c r="F351" s="36"/>
       <c r="G351" s="36"/>
-      <c r="H351" s="60"/>
-      <c r="I351" s="60"/>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H351" s="61"/>
+      <c r="I351" s="61"/>
+    </row>
+    <row r="352" spans="1:9">
       <c r="A352" s="9" t="s">
         <v>725</v>
       </c>
@@ -12615,10 +12180,10 @@
       <c r="E352" s="36"/>
       <c r="F352" s="36"/>
       <c r="G352" s="36"/>
-      <c r="H352" s="60"/>
-      <c r="I352" s="60"/>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H352" s="61"/>
+      <c r="I352" s="61"/>
+    </row>
+    <row r="353" spans="1:9">
       <c r="A353" s="9" t="s">
         <v>726</v>
       </c>
@@ -12628,10 +12193,10 @@
       <c r="E353" s="36"/>
       <c r="F353" s="36"/>
       <c r="G353" s="36"/>
-      <c r="H353" s="60"/>
-      <c r="I353" s="60"/>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H353" s="61"/>
+      <c r="I353" s="61"/>
+    </row>
+    <row r="354" spans="1:9">
       <c r="A354" s="9" t="s">
         <v>727</v>
       </c>
@@ -12641,10 +12206,10 @@
       <c r="E354" s="36"/>
       <c r="F354" s="36"/>
       <c r="G354" s="36"/>
-      <c r="H354" s="60"/>
-      <c r="I354" s="60"/>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H354" s="61"/>
+      <c r="I354" s="61"/>
+    </row>
+    <row r="355" spans="1:9">
       <c r="A355" s="9" t="s">
         <v>728</v>
       </c>
@@ -12654,10 +12219,10 @@
       <c r="E355" s="36"/>
       <c r="F355" s="36"/>
       <c r="G355" s="36"/>
-      <c r="H355" s="60"/>
-      <c r="I355" s="60"/>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H355" s="61"/>
+      <c r="I355" s="61"/>
+    </row>
+    <row r="356" spans="1:9">
       <c r="A356" s="9" t="s">
         <v>729</v>
       </c>
@@ -12667,10 +12232,10 @@
       <c r="E356" s="36"/>
       <c r="F356" s="36"/>
       <c r="G356" s="36"/>
-      <c r="H356" s="60"/>
-      <c r="I356" s="60"/>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H356" s="61"/>
+      <c r="I356" s="61"/>
+    </row>
+    <row r="357" spans="1:9">
       <c r="A357" s="9" t="s">
         <v>730</v>
       </c>
@@ -12680,10 +12245,10 @@
       <c r="E357" s="36"/>
       <c r="F357" s="36"/>
       <c r="G357" s="36"/>
-      <c r="H357" s="60"/>
-      <c r="I357" s="60"/>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H357" s="61"/>
+      <c r="I357" s="61"/>
+    </row>
+    <row r="358" spans="1:9">
       <c r="A358" s="9" t="s">
         <v>731</v>
       </c>
@@ -12693,10 +12258,10 @@
       <c r="E358" s="36"/>
       <c r="F358" s="36"/>
       <c r="G358" s="36"/>
-      <c r="H358" s="60"/>
-      <c r="I358" s="60"/>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H358" s="61"/>
+      <c r="I358" s="61"/>
+    </row>
+    <row r="359" spans="1:9">
       <c r="A359" s="9" t="s">
         <v>732</v>
       </c>
@@ -12706,10 +12271,10 @@
       <c r="E359" s="36"/>
       <c r="F359" s="36"/>
       <c r="G359" s="36"/>
-      <c r="H359" s="60"/>
-      <c r="I359" s="60"/>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H359" s="61"/>
+      <c r="I359" s="61"/>
+    </row>
+    <row r="360" spans="1:9">
       <c r="A360" s="9" t="s">
         <v>733</v>
       </c>
@@ -12719,10 +12284,10 @@
       <c r="E360" s="36"/>
       <c r="F360" s="36"/>
       <c r="G360" s="36"/>
-      <c r="H360" s="60"/>
-      <c r="I360" s="60"/>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H360" s="61"/>
+      <c r="I360" s="61"/>
+    </row>
+    <row r="361" spans="1:9">
       <c r="A361" s="9" t="s">
         <v>734</v>
       </c>
@@ -12732,10 +12297,10 @@
       <c r="E361" s="36"/>
       <c r="F361" s="36"/>
       <c r="G361" s="36"/>
-      <c r="H361" s="60"/>
-      <c r="I361" s="60"/>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H361" s="61"/>
+      <c r="I361" s="61"/>
+    </row>
+    <row r="362" spans="1:9">
       <c r="A362" s="9" t="s">
         <v>735</v>
       </c>
@@ -12745,10 +12310,10 @@
       <c r="E362" s="36"/>
       <c r="F362" s="36"/>
       <c r="G362" s="36"/>
-      <c r="H362" s="60"/>
-      <c r="I362" s="60"/>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H362" s="61"/>
+      <c r="I362" s="61"/>
+    </row>
+    <row r="363" spans="1:9">
       <c r="A363" s="9" t="s">
         <v>736</v>
       </c>
@@ -12758,10 +12323,10 @@
       <c r="E363" s="36"/>
       <c r="F363" s="36"/>
       <c r="G363" s="36"/>
-      <c r="H363" s="60"/>
-      <c r="I363" s="60"/>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H363" s="61"/>
+      <c r="I363" s="61"/>
+    </row>
+    <row r="364" spans="1:9">
       <c r="A364" s="9" t="s">
         <v>737</v>
       </c>
@@ -12771,10 +12336,10 @@
       <c r="E364" s="36"/>
       <c r="F364" s="36"/>
       <c r="G364" s="36"/>
-      <c r="H364" s="60"/>
-      <c r="I364" s="60"/>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H364" s="61"/>
+      <c r="I364" s="61"/>
+    </row>
+    <row r="365" spans="1:9">
       <c r="A365" s="9" t="s">
         <v>738</v>
       </c>
@@ -12784,10 +12349,10 @@
       <c r="E365" s="36"/>
       <c r="F365" s="36"/>
       <c r="G365" s="36"/>
-      <c r="H365" s="60"/>
-      <c r="I365" s="60"/>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H365" s="61"/>
+      <c r="I365" s="61"/>
+    </row>
+    <row r="366" spans="1:9">
       <c r="A366" s="9" t="s">
         <v>739</v>
       </c>
@@ -12797,10 +12362,10 @@
       <c r="E366" s="36"/>
       <c r="F366" s="36"/>
       <c r="G366" s="36"/>
-      <c r="H366" s="60"/>
-      <c r="I366" s="60"/>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H366" s="61"/>
+      <c r="I366" s="61"/>
+    </row>
+    <row r="367" spans="1:9">
       <c r="A367" s="9" t="s">
         <v>740</v>
       </c>
@@ -12810,10 +12375,10 @@
       <c r="E367" s="36"/>
       <c r="F367" s="36"/>
       <c r="G367" s="36"/>
-      <c r="H367" s="60"/>
-      <c r="I367" s="60"/>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H367" s="61"/>
+      <c r="I367" s="61"/>
+    </row>
+    <row r="368" spans="1:9">
       <c r="A368" s="9" t="s">
         <v>741</v>
       </c>
@@ -12823,10 +12388,10 @@
       <c r="E368" s="36"/>
       <c r="F368" s="36"/>
       <c r="G368" s="36"/>
-      <c r="H368" s="60"/>
-      <c r="I368" s="60"/>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H368" s="61"/>
+      <c r="I368" s="61"/>
+    </row>
+    <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
         <v>742</v>
       </c>
@@ -12836,10 +12401,10 @@
       <c r="E369" s="36"/>
       <c r="F369" s="36"/>
       <c r="G369" s="36"/>
-      <c r="H369" s="60"/>
-      <c r="I369" s="60"/>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H369" s="61"/>
+      <c r="I369" s="61"/>
+    </row>
+    <row r="370" spans="1:9">
       <c r="A370" s="9" t="s">
         <v>743</v>
       </c>
@@ -12849,10 +12414,10 @@
       <c r="E370" s="36"/>
       <c r="F370" s="36"/>
       <c r="G370" s="36"/>
-      <c r="H370" s="60"/>
-      <c r="I370" s="60"/>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H370" s="61"/>
+      <c r="I370" s="61"/>
+    </row>
+    <row r="371" spans="1:9">
       <c r="A371" s="9" t="s">
         <v>744</v>
       </c>
@@ -12862,10 +12427,10 @@
       <c r="E371" s="36"/>
       <c r="F371" s="36"/>
       <c r="G371" s="36"/>
-      <c r="H371" s="60"/>
-      <c r="I371" s="60"/>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H371" s="61"/>
+      <c r="I371" s="61"/>
+    </row>
+    <row r="372" spans="1:9">
       <c r="A372" s="9" t="s">
         <v>745</v>
       </c>
@@ -12875,10 +12440,10 @@
       <c r="E372" s="36"/>
       <c r="F372" s="36"/>
       <c r="G372" s="36"/>
-      <c r="H372" s="60"/>
-      <c r="I372" s="60"/>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H372" s="61"/>
+      <c r="I372" s="61"/>
+    </row>
+    <row r="373" spans="1:9">
       <c r="A373" s="9" t="s">
         <v>746</v>
       </c>
@@ -12888,10 +12453,10 @@
       <c r="E373" s="36"/>
       <c r="F373" s="36"/>
       <c r="G373" s="36"/>
-      <c r="H373" s="60"/>
-      <c r="I373" s="60"/>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H373" s="61"/>
+      <c r="I373" s="61"/>
+    </row>
+    <row r="374" spans="1:9">
       <c r="A374" s="9" t="s">
         <v>747</v>
       </c>
@@ -12901,10 +12466,10 @@
       <c r="E374" s="36"/>
       <c r="F374" s="36"/>
       <c r="G374" s="36"/>
-      <c r="H374" s="60"/>
-      <c r="I374" s="60"/>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H374" s="61"/>
+      <c r="I374" s="61"/>
+    </row>
+    <row r="375" spans="1:9">
       <c r="A375" s="9" t="s">
         <v>748</v>
       </c>
@@ -12914,10 +12479,10 @@
       <c r="E375" s="36"/>
       <c r="F375" s="36"/>
       <c r="G375" s="36"/>
-      <c r="H375" s="60"/>
-      <c r="I375" s="60"/>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H375" s="61"/>
+      <c r="I375" s="61"/>
+    </row>
+    <row r="376" spans="1:9">
       <c r="A376" s="9" t="s">
         <v>749</v>
       </c>
@@ -12927,10 +12492,10 @@
       <c r="E376" s="36"/>
       <c r="F376" s="36"/>
       <c r="G376" s="36"/>
-      <c r="H376" s="60"/>
-      <c r="I376" s="60"/>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H376" s="61"/>
+      <c r="I376" s="61"/>
+    </row>
+    <row r="377" spans="1:9">
       <c r="A377" s="9" t="s">
         <v>750</v>
       </c>
@@ -12940,10 +12505,10 @@
       <c r="E377" s="36"/>
       <c r="F377" s="36"/>
       <c r="G377" s="36"/>
-      <c r="H377" s="60"/>
-      <c r="I377" s="60"/>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H377" s="61"/>
+      <c r="I377" s="61"/>
+    </row>
+    <row r="378" spans="1:9">
       <c r="A378" s="9" t="s">
         <v>751</v>
       </c>
@@ -12953,10 +12518,10 @@
       <c r="E378" s="36"/>
       <c r="F378" s="36"/>
       <c r="G378" s="36"/>
-      <c r="H378" s="60"/>
-      <c r="I378" s="60"/>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H378" s="61"/>
+      <c r="I378" s="61"/>
+    </row>
+    <row r="379" spans="1:9">
       <c r="A379" s="9" t="s">
         <v>752</v>
       </c>
@@ -12966,10 +12531,10 @@
       <c r="E379" s="36"/>
       <c r="F379" s="36"/>
       <c r="G379" s="36"/>
-      <c r="H379" s="60"/>
-      <c r="I379" s="60"/>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H379" s="61"/>
+      <c r="I379" s="61"/>
+    </row>
+    <row r="380" spans="1:9">
       <c r="A380" s="9" t="s">
         <v>753</v>
       </c>
@@ -12979,10 +12544,10 @@
       <c r="E380" s="36"/>
       <c r="F380" s="36"/>
       <c r="G380" s="36"/>
-      <c r="H380" s="60"/>
-      <c r="I380" s="60"/>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H380" s="61"/>
+      <c r="I380" s="61"/>
+    </row>
+    <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
         <v>754</v>
       </c>
@@ -12992,10 +12557,10 @@
       <c r="E381" s="36"/>
       <c r="F381" s="36"/>
       <c r="G381" s="36"/>
-      <c r="H381" s="60"/>
-      <c r="I381" s="60"/>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H381" s="61"/>
+      <c r="I381" s="61"/>
+    </row>
+    <row r="382" spans="1:9">
       <c r="A382" s="9" t="s">
         <v>755</v>
       </c>
@@ -13005,10 +12570,10 @@
       <c r="E382" s="36"/>
       <c r="F382" s="36"/>
       <c r="G382" s="36"/>
-      <c r="H382" s="60"/>
-      <c r="I382" s="60"/>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H382" s="61"/>
+      <c r="I382" s="61"/>
+    </row>
+    <row r="383" spans="1:9">
       <c r="A383" s="9" t="s">
         <v>756</v>
       </c>
@@ -13018,10 +12583,10 @@
       <c r="E383" s="36"/>
       <c r="F383" s="36"/>
       <c r="G383" s="36"/>
-      <c r="H383" s="60"/>
-      <c r="I383" s="60"/>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H383" s="61"/>
+      <c r="I383" s="61"/>
+    </row>
+    <row r="384" spans="1:9">
       <c r="A384" s="9" t="s">
         <v>757</v>
       </c>
@@ -13031,10 +12596,10 @@
       <c r="E384" s="36"/>
       <c r="F384" s="36"/>
       <c r="G384" s="36"/>
-      <c r="H384" s="60"/>
-      <c r="I384" s="60"/>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H384" s="61"/>
+      <c r="I384" s="61"/>
+    </row>
+    <row r="385" spans="1:9">
       <c r="A385" s="9" t="s">
         <v>758</v>
       </c>
@@ -13044,10 +12609,10 @@
       <c r="E385" s="36"/>
       <c r="F385" s="36"/>
       <c r="G385" s="36"/>
-      <c r="H385" s="60"/>
-      <c r="I385" s="60"/>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H385" s="61"/>
+      <c r="I385" s="61"/>
+    </row>
+    <row r="386" spans="1:9">
       <c r="A386" s="9" t="s">
         <v>759</v>
       </c>
@@ -13057,10 +12622,10 @@
       <c r="E386" s="36"/>
       <c r="F386" s="36"/>
       <c r="G386" s="36"/>
-      <c r="H386" s="60"/>
-      <c r="I386" s="60"/>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H386" s="61"/>
+      <c r="I386" s="61"/>
+    </row>
+    <row r="387" spans="1:9">
       <c r="A387" s="9" t="s">
         <v>760</v>
       </c>
@@ -13070,10 +12635,10 @@
       <c r="E387" s="36"/>
       <c r="F387" s="36"/>
       <c r="G387" s="36"/>
-      <c r="H387" s="60"/>
-      <c r="I387" s="60"/>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H387" s="61"/>
+      <c r="I387" s="61"/>
+    </row>
+    <row r="388" spans="1:9">
       <c r="A388" s="9" t="s">
         <v>761</v>
       </c>
@@ -13083,10 +12648,10 @@
       <c r="E388" s="36"/>
       <c r="F388" s="36"/>
       <c r="G388" s="36"/>
-      <c r="H388" s="60"/>
-      <c r="I388" s="60"/>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H388" s="61"/>
+      <c r="I388" s="61"/>
+    </row>
+    <row r="389" spans="1:9">
       <c r="A389" s="9" t="s">
         <v>762</v>
       </c>
@@ -13096,10 +12661,10 @@
       <c r="E389" s="36"/>
       <c r="F389" s="36"/>
       <c r="G389" s="36"/>
-      <c r="H389" s="60"/>
-      <c r="I389" s="60"/>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H389" s="61"/>
+      <c r="I389" s="61"/>
+    </row>
+    <row r="390" spans="1:9">
       <c r="A390" s="9" t="s">
         <v>763</v>
       </c>
@@ -13109,10 +12674,10 @@
       <c r="E390" s="36"/>
       <c r="F390" s="36"/>
       <c r="G390" s="36"/>
-      <c r="H390" s="60"/>
-      <c r="I390" s="60"/>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H390" s="61"/>
+      <c r="I390" s="61"/>
+    </row>
+    <row r="391" spans="1:9">
       <c r="A391" s="9" t="s">
         <v>764</v>
       </c>
@@ -13122,10 +12687,10 @@
       <c r="E391" s="36"/>
       <c r="F391" s="36"/>
       <c r="G391" s="36"/>
-      <c r="H391" s="60"/>
-      <c r="I391" s="60"/>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H391" s="61"/>
+      <c r="I391" s="61"/>
+    </row>
+    <row r="392" spans="1:9">
       <c r="A392" s="9" t="s">
         <v>765</v>
       </c>
@@ -13135,10 +12700,10 @@
       <c r="E392" s="36"/>
       <c r="F392" s="36"/>
       <c r="G392" s="36"/>
-      <c r="H392" s="60"/>
-      <c r="I392" s="60"/>
-    </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H392" s="61"/>
+      <c r="I392" s="61"/>
+    </row>
+    <row r="393" spans="1:9">
       <c r="A393" s="9" t="s">
         <v>766</v>
       </c>
@@ -13148,8 +12713,8 @@
       <c r="E393" s="36"/>
       <c r="F393" s="36"/>
       <c r="G393" s="36"/>
-      <c r="H393" s="60"/>
-      <c r="I393" s="60"/>
+      <c r="H393" s="61"/>
+      <c r="I393" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -13159,10 +12724,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13171,10 +12736,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="90" windowWidth="19200" windowHeight="11640"/>
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="992">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2328,602 +2328,935 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
     <t>XC001</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>1*1半光横条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>消半光珍珠点50*50*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*2*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>12*4*16</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*2*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*50S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*40S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50S*75D 酷丝棉绮兵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/3斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5*4*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50S*75D 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>XC186</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75DT400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉5/1斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*150T8 4/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*215*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150T400 消3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75T400消 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 半光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*150 消光2/2 斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75-T800消光骑士斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*5*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>X字格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*46</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条2*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4+28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>238克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4+38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯200米克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T400横条1*1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>100*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75闪电斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>18*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 小钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150酷丝绵 大钻石斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 3/2变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克385</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D半光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光*35S-3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克370</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平3/3斜-44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平4/4斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*45</t>
-  </si>
-  <si>
-    <t>米克375</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光多乐3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克300</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平1/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克350</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平T800变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17*4*29</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克380</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>120D扁平牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75 酷丝棉3/1斜 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*34</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/1斜 31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150 酷丝棉3/2斜 39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/1 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D 酷丝棉2/2 38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 30 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75D 骑兵斜 38 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300 酷丝棉3/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*75T 酷丝棉平纹 33S </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300酷丝绵珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*300T400</t>
-  </si>
-  <si>
-    <t>米克368</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75D酷丝绵变化斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*36</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T400+300T400</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>80S*75双线格酷丝绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75 T800半光0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75*75*210</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D经纬 T8 0.5格</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50*50</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫眼酷丝绵(东风)</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯365克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>半光大猫眼</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>16*4*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100半低*150半T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D低弹*50T800 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>23*2*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>30D T8 平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>22*3*57</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>30*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D经纬T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75经纬T8 2/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>19*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">50DT8*50DT8 骑兵斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*53</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50DT8*50DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T8五面埋伏</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*100D经纬T800珍珠点</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>21*3*49</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>50D*50D*100D T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>T800双链条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克265</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>经消光低弹 双纬T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>20*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D半光T800双纬平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75消低弹*75T8002/2斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*4*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150T800酷丝棉3/2斜  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>空变T8平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T8酷丝棉3/1.超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>17.5*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*75T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300加厚超钛棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>14*4*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150*2-T800</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯370克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D消光75DT800 3/3斜</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15.5*4*48</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>米克250</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>37梭多乐绵</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*37</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*40S+150D T8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*45</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯188克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">斜纹毛巾底 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>13.5*4*51</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*150T8*300低弹</t>
-  </si>
-  <si>
-    <t>猫眼酷丝绵(东风)</t>
-  </si>
-  <si>
-    <t>40S*35S*2</t>
-  </si>
-  <si>
-    <t>白坯365克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*3*43</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-180</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>75D*50S+10DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯米克245</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>网纹3/3-220</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>15*4*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100D*35S+150DT8</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>00克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>天丝棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>20*3*32</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>80S*三合一</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯195克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>21*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>270-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯360克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>生态棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*35S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>210-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*30S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯285克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>加厚钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5*4*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>白坯390克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>230-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>白坯300克</t>
-  </si>
-  <si>
-    <t>天丝棉</t>
-  </si>
-  <si>
-    <t>20*3*32</t>
-  </si>
-  <si>
-    <t>80S*三合一</t>
-  </si>
-  <si>
-    <t>白坯195克</t>
-  </si>
-  <si>
-    <t>21*3*31</t>
-  </si>
-  <si>
-    <t>270-钛金棉</t>
-  </si>
-  <si>
-    <t>白坯360克</t>
-  </si>
-  <si>
-    <t>生态棉</t>
-  </si>
-  <si>
-    <t>40S*35S</t>
-  </si>
-  <si>
-    <t>210-钛金棉</t>
-  </si>
-  <si>
-    <t>17*3*27</t>
-  </si>
-  <si>
-    <t>40S*30S</t>
-  </si>
-  <si>
-    <t>白坯285克</t>
-  </si>
-  <si>
-    <t>加厚钛金棉</t>
-  </si>
-  <si>
-    <t>15.5*4*30</t>
-  </si>
-  <si>
-    <t>白坯390克</t>
-  </si>
-  <si>
-    <t>230-钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">生态棉 加厚 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>16*4*31</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>270单股钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*18S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>登山布</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>12.5*4*215*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>100*75*450</t>
-  </si>
-  <si>
-    <t>白坯310克</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>白坯3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10克</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40*300平纹</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*24</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>40S*300D</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>加厚17S钛金棉</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*17S*2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2996,6 +3329,13 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -3174,7 +3514,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3352,10 +3692,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -3432,6 +3768,26 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3453,6 +3809,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3791,16 +4155,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>4</v>
+        <v>771</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4200,7 +4564,7 @@
         <v>165</v>
       </c>
       <c r="H17" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="I17" s="11"/>
     </row>
@@ -4487,7 +4851,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4512,7 +4876,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -4725,7 +5089,7 @@
         <v>165</v>
       </c>
       <c r="H38" s="10">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I38" s="11"/>
     </row>
@@ -4787,7 +5151,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>3</v>
+        <v>774</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>98</v>
@@ -4800,7 +5164,7 @@
         <v>165</v>
       </c>
       <c r="H41" s="10">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="I41" s="11"/>
     </row>
@@ -4959,7 +5323,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>116</v>
@@ -5152,7 +5516,7 @@
         <v>188</v>
       </c>
       <c r="H55" s="13">
-        <v>2.2999999999999998</v>
+        <v>2.5</v>
       </c>
       <c r="I55" s="11"/>
     </row>
@@ -5164,7 +5528,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>134</v>
@@ -5691,7 +6055,7 @@
         <v>192</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>73</v>
+        <v>777</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>143</v>
@@ -6416,13 +6780,13 @@
         <v>267</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>253</v>
+        <v>778</v>
       </c>
       <c r="D106" s="22" t="s">
         <v>268</v>
       </c>
       <c r="E106" s="22">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F106" s="9"/>
       <c r="G106" s="11">
@@ -7041,7 +7405,7 @@
         <v>329</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>147</v>
@@ -7177,7 +7541,7 @@
         <v>165</v>
       </c>
       <c r="H136" s="26">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I136" s="11"/>
     </row>
@@ -7579,7 +7943,7 @@
         <v>208</v>
       </c>
       <c r="H152" s="13">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I152" s="11"/>
     </row>
@@ -7606,7 +7970,7 @@
         <v>216</v>
       </c>
       <c r="H153" s="13">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I153" s="11"/>
     </row>
@@ -7633,7 +7997,7 @@
         <v>208</v>
       </c>
       <c r="H154" s="10">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I154" s="11"/>
     </row>
@@ -7660,7 +8024,7 @@
         <v>220</v>
       </c>
       <c r="H155" s="10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I155" s="11"/>
     </row>
@@ -7687,7 +8051,7 @@
         <v>215</v>
       </c>
       <c r="H156" s="10">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I156" s="11"/>
     </row>
@@ -7714,7 +8078,7 @@
         <v>208</v>
       </c>
       <c r="H157" s="13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I157" s="11"/>
     </row>
@@ -7726,7 +8090,7 @@
         <v>402</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>392</v>
@@ -7741,7 +8105,7 @@
         <v>225</v>
       </c>
       <c r="H158" s="27">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I158" s="11"/>
     </row>
@@ -7800,7 +8164,7 @@
         <v>410</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>411</v>
@@ -7818,7 +8182,7 @@
         <v>208</v>
       </c>
       <c r="H161" s="22">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I161" s="11"/>
     </row>
@@ -7881,7 +8245,7 @@
         <v>419</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>420</v>
@@ -7899,7 +8263,7 @@
         <v>208</v>
       </c>
       <c r="H164" s="22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I164" s="11"/>
     </row>
@@ -7908,10 +8272,10 @@
         <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>412</v>
@@ -7948,13 +8312,13 @@
         <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -7966,7 +8330,7 @@
         <v>220</v>
       </c>
       <c r="H167" s="18">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I167" s="11"/>
     </row>
@@ -7975,13 +8339,13 @@
         <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>415</v>
+        <v>789</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -7993,7 +8357,7 @@
         <v>208</v>
       </c>
       <c r="H168" s="18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I168" s="11"/>
     </row>
@@ -8002,7 +8366,7 @@
         <v>425</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>426</v>
@@ -8020,7 +8384,7 @@
         <v>208</v>
       </c>
       <c r="H169" s="18">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I169" s="32"/>
     </row>
@@ -8029,7 +8393,7 @@
         <v>428</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>429</v>
@@ -8047,7 +8411,7 @@
         <v>215</v>
       </c>
       <c r="H170" s="32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I170" s="32"/>
     </row>
@@ -8056,7 +8420,7 @@
         <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>237</v>
@@ -8074,7 +8438,7 @@
         <v>215</v>
       </c>
       <c r="H171" s="32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I171" s="32"/>
     </row>
@@ -8101,7 +8465,7 @@
         <v>215</v>
       </c>
       <c r="H172" s="18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I172" s="32"/>
     </row>
@@ -8110,7 +8474,7 @@
         <v>433</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>434</v>
@@ -8128,7 +8492,7 @@
         <v>208</v>
       </c>
       <c r="H173" s="18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I173" s="32"/>
     </row>
@@ -8137,7 +8501,7 @@
         <v>436</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>437</v>
@@ -8155,7 +8519,7 @@
         <v>215</v>
       </c>
       <c r="H174" s="32">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I174" s="32"/>
     </row>
@@ -8164,7 +8528,7 @@
         <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8236,7 +8600,7 @@
         <v>215</v>
       </c>
       <c r="H177" s="18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I177" s="32"/>
     </row>
@@ -8245,7 +8609,7 @@
         <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>791</v>
+        <v>768</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>418</v>
@@ -8263,7 +8627,7 @@
         <v>208</v>
       </c>
       <c r="H178" s="18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I178" s="32"/>
     </row>
@@ -8290,7 +8654,7 @@
         <v>208</v>
       </c>
       <c r="H179" s="18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I179" s="32"/>
     </row>
@@ -8299,7 +8663,7 @@
         <v>448</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>449</v>
@@ -8317,7 +8681,7 @@
         <v>208</v>
       </c>
       <c r="H180" s="18">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I180" s="32"/>
     </row>
@@ -8326,7 +8690,7 @@
         <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>443</v>
@@ -8344,7 +8708,7 @@
         <v>215</v>
       </c>
       <c r="H181" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I181" s="11"/>
     </row>
@@ -8353,7 +8717,7 @@
         <v>451</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>308</v>
@@ -8371,7 +8735,7 @@
         <v>215</v>
       </c>
       <c r="H182" s="34">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I182" s="11"/>
     </row>
@@ -8380,7 +8744,7 @@
         <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>308</v>
@@ -8398,7 +8762,7 @@
         <v>215</v>
       </c>
       <c r="H183" s="34">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I183" s="11"/>
     </row>
@@ -8425,7 +8789,7 @@
         <v>215</v>
       </c>
       <c r="H184" s="35">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I184" s="38"/>
     </row>
@@ -8434,13 +8798,13 @@
         <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>443</v>
+        <v>802</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8452,7 +8816,7 @@
         <v>215</v>
       </c>
       <c r="H185" s="18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I185" s="11"/>
     </row>
@@ -8461,7 +8825,7 @@
         <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>308</v>
@@ -8479,19 +8843,19 @@
         <v>215</v>
       </c>
       <c r="H186" s="34">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I186" s="11"/>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>435</v>
@@ -8515,13 +8879,13 @@
         <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>271</v>
+        <v>808</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8533,7 +8897,7 @@
         <v>215</v>
       </c>
       <c r="H188" s="18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I188" s="11"/>
     </row>
@@ -8542,7 +8906,7 @@
         <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>801</v>
+        <v>810</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>443</v>
@@ -8569,13 +8933,13 @@
         <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>803</v>
+        <v>812</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8596,10 +8960,10 @@
         <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>790</v>
+        <v>814</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>435</v>
@@ -8614,7 +8978,7 @@
         <v>215</v>
       </c>
       <c r="H191" s="32">
-        <v>4.5999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="I191" s="11"/>
     </row>
@@ -8649,10 +9013,10 @@
         <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>805</v>
+        <v>815</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>384</v>
+        <v>816</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>147</v>
@@ -8661,10 +9025,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="44">
+        <v>180</v>
+      </c>
+      <c r="G194" s="42">
         <v>215</v>
-      </c>
-      <c r="G194" s="42">
-        <v>225</v>
       </c>
       <c r="H194" s="41">
         <v>4.0999999999999996</v>
@@ -8676,7 +9040,7 @@
         <v>467</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>468</v>
@@ -8691,10 +9055,10 @@
         <v>165</v>
       </c>
       <c r="G195" s="42">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="H195" s="41">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I195" s="37"/>
     </row>
@@ -8703,10 +9067,10 @@
         <v>469</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>470</v>
@@ -8714,10 +9078,10 @@
       <c r="E196" s="45">
         <v>105</v>
       </c>
-      <c r="F196" s="36">
+      <c r="F196" s="65">
         <v>155</v>
       </c>
-      <c r="G196" s="11">
+      <c r="G196" s="66">
         <v>215</v>
       </c>
       <c r="H196" s="45">
@@ -8730,10 +9094,10 @@
         <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>385</v>
@@ -8741,14 +9105,14 @@
       <c r="E197" s="45">
         <v>100</v>
       </c>
-      <c r="F197" s="29">
+      <c r="F197" s="44">
         <v>150</v>
       </c>
-      <c r="G197" s="11">
+      <c r="G197" s="66">
         <v>215</v>
       </c>
       <c r="H197" s="45">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I197" s="37"/>
     </row>
@@ -8757,7 +9121,7 @@
         <v>472</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>473</v>
@@ -8768,10 +9132,10 @@
       <c r="E198" s="45">
         <v>129</v>
       </c>
-      <c r="F198" s="46">
+      <c r="F198" s="67">
         <v>183</v>
       </c>
-      <c r="G198" s="11">
+      <c r="G198" s="66">
         <v>215</v>
       </c>
       <c r="H198" s="45">
@@ -8784,21 +9148,21 @@
         <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>400</v>
+        <v>824</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
       </c>
-      <c r="F199" s="29">
+      <c r="F199" s="44">
         <v>145</v>
       </c>
-      <c r="G199" s="11">
+      <c r="G199" s="66">
         <v>215</v>
       </c>
       <c r="H199" s="45">
@@ -8872,14 +9236,14 @@
         <v>483</v>
       </c>
       <c r="E204" s="24"/>
-      <c r="F204" s="47">
+      <c r="F204" s="46">
         <v>52</v>
       </c>
-      <c r="G204" s="48">
+      <c r="G204" s="47">
         <v>175</v>
       </c>
       <c r="H204" s="24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I204" s="37"/>
     </row>
@@ -8893,16 +9257,16 @@
       <c r="C205" s="24" t="s">
         <v>486</v>
       </c>
-      <c r="D205" s="48" t="s">
+      <c r="D205" s="47" t="s">
         <v>487</v>
       </c>
       <c r="E205" s="24">
         <v>47</v>
       </c>
-      <c r="F205" s="47">
+      <c r="F205" s="46">
         <v>58</v>
       </c>
-      <c r="G205" s="48">
+      <c r="G205" s="47">
         <v>174</v>
       </c>
       <c r="H205" s="24">
@@ -8920,16 +9284,16 @@
       <c r="C206" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="D206" s="48" t="s">
+      <c r="D206" s="47" t="s">
         <v>487</v>
       </c>
       <c r="E206" s="24">
         <v>47</v>
       </c>
-      <c r="F206" s="47">
+      <c r="F206" s="46">
         <v>54</v>
       </c>
-      <c r="G206" s="48">
+      <c r="G206" s="47">
         <v>174</v>
       </c>
       <c r="H206" s="24">
@@ -8968,7 +9332,7 @@
         <v>494</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -8983,7 +9347,7 @@
         <v>170</v>
       </c>
       <c r="H208" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I208" s="11"/>
     </row>
@@ -9031,7 +9395,7 @@
         <v>499</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9053,10 +9417,10 @@
         <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>143</v>
@@ -9096,7 +9460,7 @@
         <v>178</v>
       </c>
       <c r="H213" s="10">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I213" s="37"/>
     </row>
@@ -9108,7 +9472,7 @@
         <v>505</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>143</v>
@@ -9221,12 +9585,12 @@
         <v>517</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>819</v>
-      </c>
-      <c r="D220" s="49" t="s">
+        <v>831</v>
+      </c>
+      <c r="D220" s="48" t="s">
         <v>518</v>
       </c>
       <c r="E220" s="10">
@@ -9242,7 +9606,7 @@
         <v>3.6</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9250,13 +9614,13 @@
         <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>822</v>
-      </c>
-      <c r="D221" s="49" t="s">
-        <v>4</v>
+        <v>834</v>
+      </c>
+      <c r="D221" s="48" t="s">
+        <v>835</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9271,7 +9635,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>823</v>
+        <v>836</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9279,13 +9643,13 @@
         <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>824</v>
+        <v>837</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>825</v>
-      </c>
-      <c r="D222" s="49" t="s">
-        <v>518</v>
+        <v>838</v>
+      </c>
+      <c r="D222" s="48" t="s">
+        <v>839</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9311,7 +9675,7 @@
       <c r="C223" s="35" t="s">
         <v>523</v>
       </c>
-      <c r="D223" s="50" t="s">
+      <c r="D223" s="49" t="s">
         <v>4</v>
       </c>
       <c r="E223" s="35">
@@ -9324,7 +9688,7 @@
         <v>220</v>
       </c>
       <c r="H223" s="35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I223" s="37"/>
     </row>
@@ -9333,13 +9697,13 @@
         <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9351,7 +9715,7 @@
         <v>215</v>
       </c>
       <c r="H224" s="35">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
       <c r="I224" s="37"/>
     </row>
@@ -9378,7 +9742,7 @@
         <v>215</v>
       </c>
       <c r="H225" s="35">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I225" s="11"/>
     </row>
@@ -9387,10 +9751,10 @@
         <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>435</v>
@@ -9414,10 +9778,10 @@
         <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>237</v>
+        <v>806</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>435</v>
@@ -9486,7 +9850,7 @@
         <v>215</v>
       </c>
       <c r="H229" s="35">
-        <v>4.9000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="I229" s="11"/>
     </row>
@@ -9494,137 +9858,137 @@
       <c r="A230" s="9" t="s">
         <v>534</v>
       </c>
-      <c r="B230" s="51" t="s">
+      <c r="B230" s="27" t="s">
         <v>535</v>
       </c>
-      <c r="C230" s="51" t="s">
+      <c r="C230" s="27" t="s">
         <v>456</v>
       </c>
-      <c r="D230" s="51" t="s">
+      <c r="D230" s="27" t="s">
         <v>435</v>
       </c>
-      <c r="E230" s="51">
+      <c r="E230" s="27">
         <v>145</v>
       </c>
-      <c r="F230" s="36">
+      <c r="F230" s="61">
         <v>225</v>
       </c>
-      <c r="G230" s="11">
+      <c r="G230" s="20">
         <v>215</v>
       </c>
-      <c r="H230" s="51">
+      <c r="H230" s="27">
         <v>5</v>
       </c>
-      <c r="I230" s="11"/>
+      <c r="I230" s="20"/>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B231" s="18"/>
-      <c r="C231" s="18"/>
-      <c r="D231" s="33"/>
-      <c r="E231" s="18"/>
-      <c r="F231" s="31"/>
-      <c r="G231" s="32"/>
-      <c r="H231" s="18"/>
-      <c r="I231" s="11"/>
+      <c r="B231" s="27"/>
+      <c r="C231" s="27"/>
+      <c r="D231" s="49"/>
+      <c r="E231" s="27"/>
+      <c r="F231" s="29"/>
+      <c r="G231" s="20"/>
+      <c r="H231" s="27"/>
+      <c r="I231" s="20"/>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="B232" s="35"/>
-      <c r="C232" s="35"/>
-      <c r="D232" s="35"/>
-      <c r="E232" s="35"/>
-      <c r="F232" s="36"/>
-      <c r="G232" s="37"/>
-      <c r="H232" s="35"/>
-      <c r="I232" s="37"/>
+      <c r="B232" s="39"/>
+      <c r="C232" s="39"/>
+      <c r="D232" s="39"/>
+      <c r="E232" s="39"/>
+      <c r="F232" s="61"/>
+      <c r="G232" s="40"/>
+      <c r="H232" s="39"/>
+      <c r="I232" s="40"/>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="B233" s="35" t="s">
+      <c r="B233" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="C233" s="35" t="s">
+      <c r="C233" s="39" t="s">
         <v>540</v>
       </c>
-      <c r="D233" s="35" t="s">
+      <c r="D233" s="39" t="s">
         <v>541</v>
       </c>
-      <c r="E233" s="35">
+      <c r="E233" s="39">
         <v>185</v>
       </c>
-      <c r="F233" s="36">
+      <c r="F233" s="61">
         <v>270</v>
       </c>
-      <c r="G233" s="37">
+      <c r="G233" s="40">
         <v>215</v>
       </c>
-      <c r="H233" s="35">
+      <c r="H233" s="39">
         <v>5.3</v>
       </c>
-      <c r="I233" s="37"/>
+      <c r="I233" s="40"/>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="B234" s="52" t="s">
-        <v>831</v>
-      </c>
-      <c r="C234" s="52" t="s">
-        <v>832</v>
-      </c>
-      <c r="D234" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="E234" s="52">
+      <c r="B234" s="68" t="s">
+        <v>845</v>
+      </c>
+      <c r="C234" s="68" t="s">
+        <v>846</v>
+      </c>
+      <c r="D234" s="49" t="s">
+        <v>847</v>
+      </c>
+      <c r="E234" s="68">
         <v>190</v>
       </c>
-      <c r="F234" s="36">
+      <c r="F234" s="61">
         <v>275</v>
       </c>
-      <c r="G234" s="53">
+      <c r="G234" s="69">
         <v>215</v>
       </c>
-      <c r="H234" s="52">
-        <v>5.8</v>
-      </c>
-      <c r="I234" s="54" t="s">
-        <v>834</v>
+      <c r="H234" s="68">
+        <v>6</v>
+      </c>
+      <c r="I234" s="40" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="B235" s="51" t="s">
-        <v>835</v>
-      </c>
-      <c r="C235" s="51" t="s">
-        <v>836</v>
-      </c>
-      <c r="D235" s="51" t="s">
-        <v>837</v>
-      </c>
-      <c r="E235" s="51">
+      <c r="B235" s="27" t="s">
+        <v>849</v>
+      </c>
+      <c r="C235" s="27" t="s">
+        <v>850</v>
+      </c>
+      <c r="D235" s="27" t="s">
+        <v>851</v>
+      </c>
+      <c r="E235" s="27">
         <v>155</v>
       </c>
-      <c r="F235" s="36">
+      <c r="F235" s="61">
         <v>230</v>
       </c>
-      <c r="G235" s="55">
+      <c r="G235" s="20">
         <v>215</v>
       </c>
-      <c r="H235" s="51">
-        <v>4.7</v>
-      </c>
-      <c r="I235" s="55" t="s">
+      <c r="H235" s="27">
+        <v>4.8</v>
+      </c>
+      <c r="I235" s="20" t="s">
         <v>544</v>
       </c>
     </row>
@@ -9632,41 +9996,41 @@
       <c r="A236" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="B236" s="51"/>
-      <c r="C236" s="51"/>
-      <c r="D236" s="51"/>
-      <c r="E236" s="51"/>
-      <c r="F236" s="36"/>
-      <c r="G236" s="55"/>
-      <c r="H236" s="51"/>
-      <c r="I236" s="54"/>
+      <c r="B236" s="27"/>
+      <c r="C236" s="27"/>
+      <c r="D236" s="27"/>
+      <c r="E236" s="27"/>
+      <c r="F236" s="61"/>
+      <c r="G236" s="20"/>
+      <c r="H236" s="27"/>
+      <c r="I236" s="40"/>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="B237" s="51" t="s">
-        <v>838</v>
-      </c>
-      <c r="C237" s="51" t="s">
+      <c r="B237" s="27" t="s">
+        <v>852</v>
+      </c>
+      <c r="C237" s="27" t="s">
         <v>547</v>
       </c>
-      <c r="D237" s="51" t="s">
-        <v>839</v>
-      </c>
-      <c r="E237" s="51">
+      <c r="D237" s="27" t="s">
+        <v>853</v>
+      </c>
+      <c r="E237" s="27">
         <v>155</v>
       </c>
-      <c r="F237" s="36">
+      <c r="F237" s="61">
         <v>230</v>
       </c>
-      <c r="G237" s="55">
+      <c r="G237" s="20">
         <v>218</v>
       </c>
-      <c r="H237" s="51">
-        <v>5</v>
-      </c>
-      <c r="I237" s="55" t="s">
+      <c r="H237" s="27">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I237" s="20" t="s">
         <v>544</v>
       </c>
     </row>
@@ -9674,202 +10038,202 @@
       <c r="A238" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="B238" s="51" t="s">
-        <v>840</v>
-      </c>
-      <c r="C238" s="51" t="s">
-        <v>841</v>
-      </c>
-      <c r="D238" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E238" s="52">
+      <c r="B238" s="27" t="s">
+        <v>854</v>
+      </c>
+      <c r="C238" s="27" t="s">
+        <v>855</v>
+      </c>
+      <c r="D238" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="E238" s="68">
         <v>190</v>
       </c>
-      <c r="F238" s="36">
+      <c r="F238" s="61">
         <v>270</v>
       </c>
-      <c r="G238" s="55">
+      <c r="G238" s="20">
         <v>216</v>
       </c>
-      <c r="H238" s="51">
-        <v>5.7</v>
-      </c>
-      <c r="I238" s="54" t="s">
-        <v>843</v>
+      <c r="H238" s="27">
+        <v>6</v>
+      </c>
+      <c r="I238" s="40" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="B239" s="51" t="s">
-        <v>844</v>
-      </c>
-      <c r="C239" s="51" t="s">
-        <v>845</v>
-      </c>
-      <c r="D239" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E239" s="52">
+      <c r="B239" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="C239" s="27" t="s">
+        <v>859</v>
+      </c>
+      <c r="D239" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="E239" s="68">
         <v>180</v>
       </c>
-      <c r="F239" s="36">
+      <c r="F239" s="61">
         <v>268</v>
       </c>
-      <c r="G239" s="55">
+      <c r="G239" s="20">
         <v>220</v>
       </c>
-      <c r="H239" s="51">
-        <v>5.7</v>
-      </c>
-      <c r="I239" s="54" t="s">
-        <v>843</v>
+      <c r="H239" s="27">
+        <v>5.8</v>
+      </c>
+      <c r="I239" s="40" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="B240" s="51" t="s">
-        <v>846</v>
-      </c>
-      <c r="C240" s="51" t="s">
-        <v>847</v>
-      </c>
-      <c r="D240" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E240" s="52">
+      <c r="B240" s="27" t="s">
+        <v>861</v>
+      </c>
+      <c r="C240" s="27" t="s">
+        <v>862</v>
+      </c>
+      <c r="D240" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="E240" s="68">
         <v>190</v>
       </c>
-      <c r="F240" s="36">
+      <c r="F240" s="61">
         <v>270</v>
       </c>
-      <c r="G240" s="55">
+      <c r="G240" s="20">
         <v>225</v>
       </c>
-      <c r="H240" s="35">
-        <v>5.9</v>
-      </c>
-      <c r="I240" s="54" t="s">
-        <v>848</v>
+      <c r="H240" s="39">
+        <v>6</v>
+      </c>
+      <c r="I240" s="40" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="B241" s="51" t="s">
-        <v>849</v>
-      </c>
-      <c r="C241" s="51" t="s">
-        <v>850</v>
-      </c>
-      <c r="D241" s="11" t="s">
+      <c r="B241" s="27" t="s">
+        <v>863</v>
+      </c>
+      <c r="C241" s="27" t="s">
+        <v>864</v>
+      </c>
+      <c r="D241" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="E241" s="51">
+      <c r="E241" s="27">
         <v>150</v>
       </c>
-      <c r="F241" s="36">
+      <c r="F241" s="61">
         <v>230</v>
       </c>
-      <c r="G241" s="55">
+      <c r="G241" s="20">
         <v>220</v>
       </c>
-      <c r="H241" s="52">
+      <c r="H241" s="68">
         <v>5.3</v>
       </c>
-      <c r="I241" s="55" t="s">
-        <v>851</v>
+      <c r="I241" s="20" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="B242" s="51" t="s">
-        <v>852</v>
-      </c>
-      <c r="C242" s="51" t="s">
-        <v>853</v>
-      </c>
-      <c r="D242" s="51" t="s">
-        <v>842</v>
-      </c>
-      <c r="E242" s="52">
+      <c r="B242" s="27" t="s">
+        <v>866</v>
+      </c>
+      <c r="C242" s="27" t="s">
+        <v>867</v>
+      </c>
+      <c r="D242" s="27" t="s">
+        <v>856</v>
+      </c>
+      <c r="E242" s="68">
         <v>160</v>
       </c>
-      <c r="F242" s="36">
+      <c r="F242" s="61">
         <v>250</v>
       </c>
-      <c r="G242" s="55">
+      <c r="G242" s="20">
         <v>225</v>
       </c>
-      <c r="H242" s="35">
+      <c r="H242" s="39">
         <v>5.4</v>
       </c>
-      <c r="I242" s="54" t="s">
-        <v>854</v>
+      <c r="I242" s="40" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="B243" s="51" t="s">
-        <v>855</v>
-      </c>
-      <c r="C243" s="51" t="s">
-        <v>856</v>
-      </c>
-      <c r="D243" s="51" t="s">
-        <v>857</v>
-      </c>
-      <c r="E243" s="52">
+      <c r="B243" s="27" t="s">
+        <v>869</v>
+      </c>
+      <c r="C243" s="27" t="s">
+        <v>870</v>
+      </c>
+      <c r="D243" s="27" t="s">
+        <v>871</v>
+      </c>
+      <c r="E243" s="68">
         <v>190</v>
       </c>
-      <c r="F243" s="36">
+      <c r="F243" s="61">
         <v>280</v>
       </c>
-      <c r="G243" s="55">
+      <c r="G243" s="20">
         <v>220</v>
       </c>
-      <c r="H243" s="35">
+      <c r="H243" s="39">
         <v>5.6</v>
       </c>
-      <c r="I243" s="54" t="s">
-        <v>858</v>
+      <c r="I243" s="40" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="B244" s="51" t="s">
-        <v>859</v>
-      </c>
-      <c r="C244" s="51" t="s">
-        <v>860</v>
-      </c>
-      <c r="D244" s="51" t="s">
-        <v>857</v>
-      </c>
-      <c r="E244" s="51">
+      <c r="B244" s="27" t="s">
+        <v>873</v>
+      </c>
+      <c r="C244" s="27" t="s">
+        <v>874</v>
+      </c>
+      <c r="D244" s="27" t="s">
+        <v>871</v>
+      </c>
+      <c r="E244" s="27">
         <v>110</v>
       </c>
-      <c r="F244" s="38">
+      <c r="F244" s="61">
         <v>160</v>
       </c>
-      <c r="G244" s="55">
+      <c r="G244" s="20">
         <v>220</v>
       </c>
-      <c r="H244" s="35">
-        <v>3.9</v>
-      </c>
-      <c r="I244" s="54"/>
+      <c r="H244" s="39">
+        <v>4</v>
+      </c>
+      <c r="I244" s="40"/>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" s="9" t="s">
@@ -9889,13 +10253,13 @@
         <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -9916,7 +10280,7 @@
         <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>527</v>
@@ -9936,14 +10300,14 @@
       <c r="H247" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I247" s="56"/>
+      <c r="I247" s="55"/>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" s="31" t="s">
         <v>559</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>560</v>
@@ -9961,19 +10325,19 @@
         <v>215</v>
       </c>
       <c r="H248" s="18">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I248" s="57"/>
+        <v>5.2</v>
+      </c>
+      <c r="I248" s="56"/>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" s="31" t="s">
         <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>437</v>
+        <v>880</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>427</v>
@@ -9981,23 +10345,23 @@
       <c r="E249" s="32">
         <v>105</v>
       </c>
-      <c r="F249" s="58">
+      <c r="F249" s="57">
         <v>155</v>
       </c>
       <c r="G249" s="32">
         <v>208</v>
       </c>
       <c r="H249" s="32">
-        <v>3.4</v>
-      </c>
-      <c r="I249" s="57"/>
+        <v>3.5</v>
+      </c>
+      <c r="I249" s="56"/>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" s="31" t="s">
         <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>152</v>
@@ -10008,14 +10372,14 @@
       <c r="E250" s="32">
         <v>108</v>
       </c>
-      <c r="F250" s="58">
+      <c r="F250" s="57">
         <v>150</v>
       </c>
       <c r="G250" s="32">
         <v>208</v>
       </c>
       <c r="H250" s="32">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I250" s="32"/>
     </row>
@@ -10024,7 +10388,7 @@
         <v>563</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>564</v>
@@ -10035,7 +10399,7 @@
       <c r="E251" s="18">
         <v>116</v>
       </c>
-      <c r="F251" s="58">
+      <c r="F251" s="57">
         <v>180</v>
       </c>
       <c r="G251" s="32">
@@ -10051,10 +10415,10 @@
         <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>437</v>
+        <v>880</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>427</v>
@@ -10062,14 +10426,14 @@
       <c r="E252" s="18">
         <v>105</v>
       </c>
-      <c r="F252" s="58">
+      <c r="F252" s="57">
         <v>155</v>
       </c>
       <c r="G252" s="32">
         <v>215</v>
       </c>
       <c r="H252" s="18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I252" s="32"/>
     </row>
@@ -10078,7 +10442,7 @@
         <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>564</v>
@@ -10089,7 +10453,7 @@
       <c r="E253" s="18">
         <v>116</v>
       </c>
-      <c r="F253" s="58">
+      <c r="F253" s="57">
         <v>180</v>
       </c>
       <c r="G253" s="32">
@@ -10105,28 +10469,28 @@
         <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
       </c>
       <c r="F254" s="31">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G254" s="32">
         <v>215</v>
       </c>
       <c r="H254" s="18">
-        <v>5.5</v>
-      </c>
-      <c r="I254" s="54" t="s">
-        <v>858</v>
+        <v>5.7</v>
+      </c>
+      <c r="I254" s="53" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10134,7 +10498,7 @@
         <v>568</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>569</v>
@@ -10142,47 +10506,47 @@
       <c r="D255" s="18" t="s">
         <v>427</v>
       </c>
-      <c r="E255" s="59">
+      <c r="E255" s="58">
         <v>88</v>
       </c>
       <c r="F255" s="31">
         <v>130</v>
       </c>
-      <c r="G255" s="56">
+      <c r="G255" s="55">
         <v>208</v>
       </c>
-      <c r="H255" s="59">
-        <v>3</v>
-      </c>
-      <c r="I255" s="54"/>
+      <c r="H255" s="58">
+        <v>3.2</v>
+      </c>
+      <c r="I255" s="53"/>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="B256" s="52" t="s">
-        <v>873</v>
-      </c>
-      <c r="C256" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D256" s="50" t="s">
-        <v>874</v>
-      </c>
-      <c r="E256" s="52">
+      <c r="B256" s="51" t="s">
+        <v>888</v>
+      </c>
+      <c r="C256" s="27" t="s">
+        <v>889</v>
+      </c>
+      <c r="D256" s="49" t="s">
+        <v>890</v>
+      </c>
+      <c r="E256" s="51">
         <v>190</v>
       </c>
       <c r="F256" s="36">
         <v>265</v>
       </c>
-      <c r="G256" s="53">
+      <c r="G256" s="52">
         <v>215</v>
       </c>
-      <c r="H256" s="60">
-        <v>5.4</v>
-      </c>
-      <c r="I256" s="54" t="s">
-        <v>875</v>
+      <c r="H256" s="59">
+        <v>5.5</v>
+      </c>
+      <c r="I256" s="53" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10190,13 +10554,13 @@
         <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>320</v>
+        <v>892</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>427</v>
+        <v>803</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10207,17 +10571,17 @@
       <c r="G257" s="36">
         <v>215</v>
       </c>
-      <c r="H257" s="60">
+      <c r="H257" s="59">
         <v>4.7</v>
       </c>
-      <c r="I257" s="60"/>
+      <c r="I257" s="59"/>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" s="9" t="s">
         <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>152</v>
@@ -10228,16 +10592,16 @@
       <c r="E258" s="32">
         <v>108</v>
       </c>
-      <c r="F258" s="58">
+      <c r="F258" s="57">
         <v>160</v>
       </c>
       <c r="G258" s="32">
         <v>215</v>
       </c>
       <c r="H258" s="32">
-        <v>3.4</v>
-      </c>
-      <c r="I258" s="60"/>
+        <v>3.5</v>
+      </c>
+      <c r="I258" s="59"/>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" s="9" t="s">
@@ -10249,8 +10613,8 @@
       <c r="E259" s="36"/>
       <c r="F259" s="36"/>
       <c r="G259" s="36"/>
-      <c r="H259" s="60"/>
-      <c r="I259" s="60"/>
+      <c r="H259" s="59"/>
+      <c r="I259" s="59"/>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" s="9" t="s">
@@ -10262,8 +10626,8 @@
       <c r="E260" s="36"/>
       <c r="F260" s="36"/>
       <c r="G260" s="36"/>
-      <c r="H260" s="60"/>
-      <c r="I260" s="60"/>
+      <c r="H260" s="59"/>
+      <c r="I260" s="59"/>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" s="9" t="s">
@@ -10275,8 +10639,8 @@
       <c r="C261" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="D261" s="49" t="s">
-        <v>877</v>
+      <c r="D261" s="48" t="s">
+        <v>893</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10288,21 +10652,21 @@
         <v>210</v>
       </c>
       <c r="H261" s="10">
-        <v>3.6</v>
-      </c>
-      <c r="I261" s="60"/>
+        <v>3.7</v>
+      </c>
+      <c r="I261" s="59"/>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" s="9" t="s">
         <v>578</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="D262" s="49" t="s">
+      <c r="D262" s="48" t="s">
         <v>580</v>
       </c>
       <c r="E262" s="10">
@@ -10317,7 +10681,7 @@
       <c r="H262" s="10">
         <v>3.8</v>
       </c>
-      <c r="I262" s="60"/>
+      <c r="I262" s="59"/>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" s="9" t="s">
@@ -10344,7 +10708,7 @@
       <c r="H263" s="27">
         <v>3.4</v>
       </c>
-      <c r="I263" s="60"/>
+      <c r="I263" s="59"/>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" s="9" t="s">
@@ -10369,9 +10733,9 @@
         <v>208</v>
       </c>
       <c r="H264" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="I264" s="60"/>
+        <v>3.9</v>
+      </c>
+      <c r="I264" s="59"/>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" s="9" t="s">
@@ -10396,22 +10760,22 @@
         <v>215</v>
       </c>
       <c r="H265" s="35">
-        <v>3.6</v>
-      </c>
-      <c r="I265" s="60"/>
+        <v>3.7</v>
+      </c>
+      <c r="I265" s="59"/>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" s="9" t="s">
         <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10423,22 +10787,22 @@
         <v>215</v>
       </c>
       <c r="H266" s="35">
-        <v>3.5</v>
-      </c>
-      <c r="I266" s="60"/>
+        <v>3.6</v>
+      </c>
+      <c r="I266" s="59"/>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" s="9" t="s">
         <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="D267" s="49" t="s">
-        <v>143</v>
+        <v>898</v>
+      </c>
+      <c r="D267" s="48" t="s">
+        <v>899</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10452,7 +10816,7 @@
       <c r="H267" s="10">
         <v>4</v>
       </c>
-      <c r="I267" s="61"/>
+      <c r="I267" s="60"/>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" s="9" t="s">
@@ -10464,8 +10828,8 @@
       <c r="E268" s="36"/>
       <c r="F268" s="36"/>
       <c r="G268" s="36"/>
-      <c r="H268" s="60"/>
-      <c r="I268" s="60"/>
+      <c r="H268" s="59"/>
+      <c r="I268" s="59"/>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" s="9" t="s">
@@ -10477,8 +10841,8 @@
       <c r="E269" s="36"/>
       <c r="F269" s="36"/>
       <c r="G269" s="36"/>
-      <c r="H269" s="60"/>
-      <c r="I269" s="60"/>
+      <c r="H269" s="59"/>
+      <c r="I269" s="59"/>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" s="9" t="s">
@@ -10490,8 +10854,8 @@
       <c r="E270" s="36"/>
       <c r="F270" s="36"/>
       <c r="G270" s="36"/>
-      <c r="H270" s="60"/>
-      <c r="I270" s="60"/>
+      <c r="H270" s="59"/>
+      <c r="I270" s="59"/>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" s="9" t="s">
@@ -10503,8 +10867,8 @@
       <c r="E271" s="36"/>
       <c r="F271" s="36"/>
       <c r="G271" s="36"/>
-      <c r="H271" s="60"/>
-      <c r="I271" s="60"/>
+      <c r="H271" s="59"/>
+      <c r="I271" s="59"/>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" s="9" t="s">
@@ -10516,8 +10880,8 @@
       <c r="E272" s="36"/>
       <c r="F272" s="36"/>
       <c r="G272" s="36"/>
-      <c r="H272" s="60"/>
-      <c r="I272" s="60"/>
+      <c r="H272" s="59"/>
+      <c r="I272" s="59"/>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" s="9" t="s">
@@ -10529,8 +10893,8 @@
       <c r="E273" s="36"/>
       <c r="F273" s="36"/>
       <c r="G273" s="36"/>
-      <c r="H273" s="60"/>
-      <c r="I273" s="60"/>
+      <c r="H273" s="59"/>
+      <c r="I273" s="59"/>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" s="9" t="s">
@@ -10542,8 +10906,8 @@
       <c r="E274" s="36"/>
       <c r="F274" s="36"/>
       <c r="G274" s="36"/>
-      <c r="H274" s="60"/>
-      <c r="I274" s="60"/>
+      <c r="H274" s="59"/>
+      <c r="I274" s="59"/>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" s="9" t="s">
@@ -10555,66 +10919,82 @@
       <c r="E275" s="36"/>
       <c r="F275" s="36"/>
       <c r="G275" s="36"/>
-      <c r="H275" s="60"/>
-      <c r="I275" s="60"/>
+      <c r="H275" s="59"/>
+      <c r="I275" s="59"/>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="B276" s="36"/>
-      <c r="C276" s="36"/>
-      <c r="D276" s="36"/>
-      <c r="E276" s="36"/>
-      <c r="F276" s="36"/>
-      <c r="G276" s="36"/>
-      <c r="H276" s="60"/>
-      <c r="I276" s="60"/>
+      <c r="B276" s="36" t="s">
+        <v>900</v>
+      </c>
+      <c r="C276" s="36" t="s">
+        <v>886</v>
+      </c>
+      <c r="D276" s="27" t="s">
+        <v>901</v>
+      </c>
+      <c r="E276" s="36">
+        <v>185</v>
+      </c>
+      <c r="F276" s="36">
+        <v>270</v>
+      </c>
+      <c r="G276" s="36">
+        <v>215</v>
+      </c>
+      <c r="H276" s="60">
+        <v>6.2</v>
+      </c>
+      <c r="I276" s="11" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="B277" s="52" t="s">
+      <c r="B277" s="51" t="s">
         <v>605</v>
       </c>
-      <c r="C277" s="52" t="s">
+      <c r="C277" s="51" t="s">
         <v>606</v>
       </c>
-      <c r="D277" s="52" t="s">
+      <c r="D277" s="51" t="s">
         <v>607</v>
       </c>
-      <c r="E277" s="52">
+      <c r="E277" s="51">
         <v>105</v>
       </c>
       <c r="F277" s="36">
         <v>140</v>
       </c>
-      <c r="G277" s="53">
+      <c r="G277" s="52">
         <v>215</v>
       </c>
-      <c r="H277" s="52">
+      <c r="H277" s="51">
         <v>4</v>
       </c>
-      <c r="I277" s="60"/>
+      <c r="I277" s="59"/>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" s="9" t="s">
         <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>547</v>
+        <v>904</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
       </c>
-      <c r="F278" s="62">
+      <c r="F278" s="61">
         <v>230</v>
       </c>
       <c r="G278" s="20">
@@ -10623,17 +11003,17 @@
       <c r="H278" s="27">
         <v>4.7</v>
       </c>
-      <c r="I278" s="60"/>
+      <c r="I278" s="59"/>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" s="9" t="s">
         <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>885</v>
-      </c>
-      <c r="C279" s="49" t="s">
-        <v>886</v>
+        <v>906</v>
+      </c>
+      <c r="C279" s="48" t="s">
+        <v>907</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>143</v>
@@ -10650,20 +11030,20 @@
       <c r="H279" s="10">
         <v>3.5</v>
       </c>
-      <c r="I279" s="60"/>
+      <c r="I279" s="59"/>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" s="9" t="s">
         <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>887</v>
-      </c>
-      <c r="C280" s="49" t="s">
-        <v>888</v>
+        <v>908</v>
+      </c>
+      <c r="C280" s="48" t="s">
+        <v>909</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>487</v>
+        <v>910</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -10675,7 +11055,7 @@
       <c r="H280" s="10">
         <v>4.7</v>
       </c>
-      <c r="I280" s="60"/>
+      <c r="I280" s="59"/>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="9" t="s">
@@ -10684,7 +11064,7 @@
       <c r="B281" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="C281" s="49" t="s">
+      <c r="C281" s="48" t="s">
         <v>613</v>
       </c>
       <c r="D281" s="10" t="s">
@@ -10702,16 +11082,16 @@
       <c r="H281" s="10">
         <v>3.5</v>
       </c>
-      <c r="I281" s="60"/>
+      <c r="I281" s="59"/>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" s="9" t="s">
         <v>614</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>889</v>
-      </c>
-      <c r="C282" s="49" t="s">
+        <v>911</v>
+      </c>
+      <c r="C282" s="48" t="s">
         <v>615</v>
       </c>
       <c r="D282" s="10" t="s">
@@ -10727,19 +11107,19 @@
         <v>215</v>
       </c>
       <c r="H282" s="10">
-        <v>2.8</v>
-      </c>
-      <c r="I282" s="60"/>
+        <v>2.9</v>
+      </c>
+      <c r="I282" s="59"/>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" s="9" t="s">
         <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>890</v>
-      </c>
-      <c r="C283" s="49" t="s">
-        <v>891</v>
+        <v>912</v>
+      </c>
+      <c r="C283" s="48" t="s">
+        <v>913</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -10756,20 +11136,20 @@
       <c r="H283" s="10">
         <v>3.7</v>
       </c>
-      <c r="I283" s="60"/>
+      <c r="I283" s="59"/>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" s="9" t="s">
         <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>892</v>
+        <v>914</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>893</v>
+        <v>915</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -10780,10 +11160,10 @@
       <c r="G284" s="36">
         <v>208</v>
       </c>
-      <c r="H284" s="60">
+      <c r="H284" s="59">
         <v>4.5</v>
       </c>
-      <c r="I284" s="60"/>
+      <c r="I284" s="59"/>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" s="9" t="s">
@@ -10792,11 +11172,11 @@
       <c r="B285" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C285" s="49" t="s">
+      <c r="C285" s="48" t="s">
         <v>620</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -10808,75 +11188,75 @@
         <v>208</v>
       </c>
       <c r="H285" s="10">
-        <v>3.7</v>
-      </c>
-      <c r="I285" s="60"/>
+        <v>3.8</v>
+      </c>
+      <c r="I285" s="59"/>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" s="9" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="52" t="s">
-        <v>895</v>
-      </c>
-      <c r="C286" s="52" t="s">
-        <v>896</v>
-      </c>
-      <c r="D286" s="52" t="s">
+      <c r="B286" s="51" t="s">
+        <v>917</v>
+      </c>
+      <c r="C286" s="51" t="s">
+        <v>918</v>
+      </c>
+      <c r="D286" s="51" t="s">
         <v>622</v>
       </c>
-      <c r="E286" s="52">
+      <c r="E286" s="51">
         <v>85</v>
       </c>
       <c r="F286" s="36">
         <v>121</v>
       </c>
-      <c r="G286" s="53">
+      <c r="G286" s="52">
         <v>208</v>
       </c>
-      <c r="H286" s="52">
+      <c r="H286" s="51">
         <v>4</v>
       </c>
-      <c r="I286" s="60"/>
+      <c r="I286" s="59"/>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="52" t="s">
-        <v>897</v>
-      </c>
-      <c r="C287" s="52" t="s">
-        <v>898</v>
-      </c>
-      <c r="D287" s="52" t="s">
-        <v>899</v>
-      </c>
-      <c r="E287" s="52">
+      <c r="B287" s="51" t="s">
+        <v>919</v>
+      </c>
+      <c r="C287" s="51" t="s">
+        <v>920</v>
+      </c>
+      <c r="D287" s="51" t="s">
+        <v>921</v>
+      </c>
+      <c r="E287" s="51">
         <v>88</v>
       </c>
       <c r="F287" s="36">
         <v>140</v>
       </c>
-      <c r="G287" s="53">
+      <c r="G287" s="52">
         <v>218</v>
       </c>
-      <c r="H287" s="52">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="I287" s="61"/>
+      <c r="H287" s="51">
+        <v>4.5</v>
+      </c>
+      <c r="I287" s="60"/>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" s="9" t="s">
         <v>624</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>900</v>
+        <v>922</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>625</v>
       </c>
-      <c r="D288" s="50" t="s">
+      <c r="D288" s="49" t="s">
         <v>4</v>
       </c>
       <c r="E288" s="27">
@@ -10891,7 +11271,7 @@
       <c r="H288" s="27">
         <v>5</v>
       </c>
-      <c r="I288" s="61"/>
+      <c r="I288" s="60"/>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" s="9" t="s">
@@ -10903,7 +11283,7 @@
       <c r="C289" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="D289" s="49" t="s">
+      <c r="D289" s="48" t="s">
         <v>629</v>
       </c>
       <c r="E289" s="10">
@@ -10919,7 +11299,7 @@
         <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>901</v>
+        <v>923</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -10932,7 +11312,7 @@
       <c r="C290" s="24" t="s">
         <v>632</v>
       </c>
-      <c r="D290" s="63" t="s">
+      <c r="D290" s="62" t="s">
         <v>39</v>
       </c>
       <c r="E290" s="24">
@@ -10941,107 +11321,107 @@
       <c r="F290" s="36">
         <v>100</v>
       </c>
-      <c r="G290" s="55">
+      <c r="G290" s="54">
         <v>220</v>
       </c>
       <c r="H290" s="24">
-        <v>2.7</v>
-      </c>
-      <c r="I290" s="61"/>
+        <v>2.8</v>
+      </c>
+      <c r="I290" s="60"/>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="B291" s="64" t="s">
-        <v>902</v>
-      </c>
-      <c r="C291" s="64" t="s">
-        <v>903</v>
-      </c>
-      <c r="D291" s="64" t="s">
+      <c r="B291" s="63" t="s">
+        <v>924</v>
+      </c>
+      <c r="C291" s="63" t="s">
+        <v>925</v>
+      </c>
+      <c r="D291" s="63" t="s">
         <v>634</v>
       </c>
-      <c r="E291" s="64">
+      <c r="E291" s="63">
         <v>88</v>
       </c>
       <c r="F291" s="36">
         <v>130</v>
       </c>
-      <c r="G291" s="54">
+      <c r="G291" s="53">
         <v>220</v>
       </c>
-      <c r="H291" s="64">
+      <c r="H291" s="63">
         <v>3.5</v>
       </c>
-      <c r="I291" s="61"/>
+      <c r="I291" s="60"/>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="9" t="s">
         <v>635</v>
       </c>
-      <c r="B292" s="64" t="s">
-        <v>904</v>
-      </c>
-      <c r="C292" s="64" t="s">
+      <c r="B292" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="C292" s="63" t="s">
         <v>636</v>
       </c>
-      <c r="D292" s="64" t="s">
+      <c r="D292" s="63" t="s">
         <v>637</v>
       </c>
-      <c r="E292" s="64">
+      <c r="E292" s="63">
         <v>80</v>
       </c>
       <c r="F292" s="36">
         <v>135</v>
       </c>
-      <c r="G292" s="54">
+      <c r="G292" s="53">
         <v>215</v>
       </c>
-      <c r="H292" s="64">
+      <c r="H292" s="63">
         <v>3.6</v>
       </c>
-      <c r="I292" s="61"/>
+      <c r="I292" s="60"/>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="B293" s="65" t="s">
-        <v>905</v>
-      </c>
-      <c r="C293" s="64" t="s">
-        <v>906</v>
-      </c>
-      <c r="D293" s="64" t="s">
+      <c r="B293" s="64" t="s">
+        <v>927</v>
+      </c>
+      <c r="C293" s="63" t="s">
+        <v>928</v>
+      </c>
+      <c r="D293" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="E293" s="65">
-        <v>106</v>
+      <c r="E293" s="64">
+        <v>105</v>
       </c>
       <c r="F293" s="36">
         <v>145</v>
       </c>
-      <c r="G293" s="53">
+      <c r="G293" s="52">
         <v>215</v>
       </c>
-      <c r="H293" s="65">
-        <v>3.7</v>
-      </c>
-      <c r="I293" s="61"/>
+      <c r="H293" s="64">
+        <v>3.9</v>
+      </c>
+      <c r="I293" s="60"/>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" s="9" t="s">
         <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>907</v>
+        <v>929</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>443</v>
+        <v>802</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>908</v>
+        <v>930</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11053,16 +11433,16 @@
         <v>215</v>
       </c>
       <c r="H294" s="18">
-        <v>5</v>
-      </c>
-      <c r="I294" s="61"/>
+        <v>5.2</v>
+      </c>
+      <c r="I294" s="60"/>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" s="9" t="s">
         <v>640</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>909</v>
+        <v>931</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>641</v>
@@ -11078,7 +11458,7 @@
       <c r="H295" s="10">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I295" s="61"/>
+      <c r="I295" s="60"/>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" s="9" t="s">
@@ -11103,20 +11483,20 @@
       <c r="H296" s="35">
         <v>3.8</v>
       </c>
-      <c r="I296" s="61"/>
+      <c r="I296" s="60"/>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" s="9" t="s">
         <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>910</v>
+        <v>932</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>911</v>
+        <v>933</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>912</v>
+        <v>934</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11128,22 +11508,22 @@
         <v>215</v>
       </c>
       <c r="H297" s="18">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I297" s="54"/>
+        <v>4.7</v>
+      </c>
+      <c r="I297" s="53"/>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" s="9" t="s">
         <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>913</v>
+        <v>935</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>914</v>
+        <v>936</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>915</v>
+        <v>937</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11155,39 +11535,39 @@
         <v>225</v>
       </c>
       <c r="H298" s="18">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>916</v>
+        <v>938</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="B299" s="51" t="s">
-        <v>917</v>
-      </c>
-      <c r="C299" s="51" t="s">
-        <v>918</v>
-      </c>
-      <c r="D299" s="51" t="s">
-        <v>919</v>
-      </c>
-      <c r="E299" s="51">
+      <c r="B299" s="50" t="s">
+        <v>939</v>
+      </c>
+      <c r="C299" s="50" t="s">
+        <v>940</v>
+      </c>
+      <c r="D299" s="50" t="s">
+        <v>941</v>
+      </c>
+      <c r="E299" s="50">
         <v>124</v>
       </c>
       <c r="F299" s="36">
         <v>180</v>
       </c>
-      <c r="G299" s="55">
+      <c r="G299" s="54">
         <v>218</v>
       </c>
-      <c r="H299" s="51">
+      <c r="H299" s="50">
         <v>5</v>
       </c>
-      <c r="I299" s="55" t="s">
-        <v>920</v>
+      <c r="I299" s="54" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11200,8 +11580,8 @@
       <c r="E300" s="36"/>
       <c r="F300" s="36"/>
       <c r="G300" s="36"/>
-      <c r="H300" s="61"/>
-      <c r="I300" s="61"/>
+      <c r="H300" s="60"/>
+      <c r="I300" s="60"/>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" s="9" t="s">
@@ -11213,21 +11593,21 @@
       <c r="E301" s="36"/>
       <c r="F301" s="36"/>
       <c r="G301" s="36"/>
-      <c r="H301" s="61"/>
-      <c r="I301" s="61"/>
+      <c r="H301" s="60"/>
+      <c r="I301" s="60"/>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" s="9" t="s">
         <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>921</v>
+        <v>943</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>922</v>
+        <v>944</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>923</v>
+        <v>945</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11239,9 +11619,9 @@
         <v>215</v>
       </c>
       <c r="H302" s="11">
-        <v>4.7</v>
-      </c>
-      <c r="I302" s="61"/>
+        <v>4.8</v>
+      </c>
+      <c r="I302" s="60"/>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" s="9" t="s">
@@ -11254,7 +11634,7 @@
         <v>655</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>923</v>
+        <v>945</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11266,24 +11646,24 @@
         <v>215</v>
       </c>
       <c r="H303" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="I303" s="61"/>
+        <v>4.3</v>
+      </c>
+      <c r="I303" s="60"/>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" s="9" t="s">
         <v>656</v>
       </c>
-      <c r="B304" s="64" t="s">
+      <c r="B304" s="63" t="s">
         <v>657</v>
       </c>
-      <c r="C304" s="64" t="s">
-        <v>250</v>
-      </c>
-      <c r="D304" s="64" t="s">
+      <c r="C304" s="63" t="s">
+        <v>946</v>
+      </c>
+      <c r="D304" s="63" t="s">
         <v>658</v>
       </c>
-      <c r="E304" s="64">
+      <c r="E304" s="63">
         <v>90</v>
       </c>
       <c r="F304" s="36">
@@ -11292,11 +11672,11 @@
       <c r="G304" s="37">
         <v>218</v>
       </c>
-      <c r="H304" s="64">
-        <v>4.5</v>
+      <c r="H304" s="63">
+        <v>4.5999999999999996</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>924</v>
+        <v>947</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -11304,13 +11684,13 @@
         <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>925</v>
+        <v>948</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>926</v>
-      </c>
-      <c r="D305" s="18" t="s">
-        <v>927</v>
+        <v>949</v>
+      </c>
+      <c r="D305" s="27" t="s">
+        <v>950</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11321,39 +11701,23 @@
       <c r="G305" s="36">
         <v>225</v>
       </c>
-      <c r="H305" s="61">
+      <c r="H305" s="60">
         <v>7.2</v>
       </c>
-      <c r="I305" s="61"/>
+      <c r="I305" s="60"/>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="B306" s="36" t="s">
-        <v>928</v>
-      </c>
-      <c r="C306" s="36" t="s">
-        <v>871</v>
-      </c>
-      <c r="D306" s="36" t="s">
-        <v>929</v>
-      </c>
-      <c r="E306" s="36">
-        <v>185</v>
-      </c>
-      <c r="F306" s="36">
-        <v>270</v>
-      </c>
-      <c r="G306" s="36">
-        <v>215</v>
-      </c>
-      <c r="H306" s="61">
-        <v>6.2</v>
-      </c>
-      <c r="I306" s="61" t="s">
-        <v>930</v>
-      </c>
+      <c r="B306" s="36"/>
+      <c r="C306" s="36"/>
+      <c r="D306" s="27"/>
+      <c r="E306" s="36"/>
+      <c r="F306" s="36"/>
+      <c r="G306" s="36"/>
+      <c r="H306" s="60"/>
+      <c r="I306" s="11"/>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" s="9" t="s">
@@ -11365,8 +11729,8 @@
       <c r="E307" s="36"/>
       <c r="F307" s="36"/>
       <c r="G307" s="36"/>
-      <c r="H307" s="61"/>
-      <c r="I307" s="61"/>
+      <c r="H307" s="60"/>
+      <c r="I307" s="60"/>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="9" t="s">
@@ -11378,8 +11742,8 @@
       <c r="E308" s="36"/>
       <c r="F308" s="36"/>
       <c r="G308" s="36"/>
-      <c r="H308" s="61"/>
-      <c r="I308" s="61"/>
+      <c r="H308" s="60"/>
+      <c r="I308" s="60"/>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" s="9" t="s">
@@ -11391,8 +11755,8 @@
       <c r="E309" s="36"/>
       <c r="F309" s="36"/>
       <c r="G309" s="36"/>
-      <c r="H309" s="61"/>
-      <c r="I309" s="61"/>
+      <c r="H309" s="60"/>
+      <c r="I309" s="60"/>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" s="9" t="s">
@@ -11404,8 +11768,8 @@
       <c r="E310" s="36"/>
       <c r="F310" s="36"/>
       <c r="G310" s="36"/>
-      <c r="H310" s="61"/>
-      <c r="I310" s="61"/>
+      <c r="H310" s="60"/>
+      <c r="I310" s="60"/>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="9" t="s">
@@ -11415,7 +11779,7 @@
         <v>666</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>670</v>
+        <v>951</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>667</v>
@@ -11430,9 +11794,9 @@
         <v>215</v>
       </c>
       <c r="H311" s="35">
-        <v>3.8</v>
-      </c>
-      <c r="I311" s="61"/>
+        <v>3.9</v>
+      </c>
+      <c r="I311" s="60"/>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" s="9" t="s">
@@ -11459,7 +11823,7 @@
       <c r="H312" s="10">
         <v>3.7</v>
       </c>
-      <c r="I312" s="61"/>
+      <c r="I312" s="60"/>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" s="9" t="s">
@@ -11471,8 +11835,8 @@
       <c r="E313" s="36"/>
       <c r="F313" s="36"/>
       <c r="G313" s="36"/>
-      <c r="H313" s="61"/>
-      <c r="I313" s="61"/>
+      <c r="H313" s="60"/>
+      <c r="I313" s="60"/>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" s="9" t="s">
@@ -11484,21 +11848,21 @@
       <c r="E314" s="36"/>
       <c r="F314" s="36"/>
       <c r="G314" s="36"/>
-      <c r="H314" s="61"/>
-      <c r="I314" s="61"/>
+      <c r="H314" s="60"/>
+      <c r="I314" s="60"/>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" s="9" t="s">
         <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>841</v>
+        <v>855</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11509,11 +11873,11 @@
       <c r="G315" s="36">
         <v>225</v>
       </c>
-      <c r="H315" s="61">
+      <c r="H315" s="60">
         <v>5</v>
       </c>
-      <c r="I315" s="61" t="s">
-        <v>933</v>
+      <c r="I315" s="60" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -11521,13 +11885,13 @@
         <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>934</v>
+        <v>955</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>935</v>
+        <v>956</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>936</v>
+        <v>957</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11538,11 +11902,11 @@
       <c r="G316" s="36">
         <v>215</v>
       </c>
-      <c r="H316" s="61">
+      <c r="H316" s="60">
         <v>5.2</v>
       </c>
-      <c r="I316" s="61" t="s">
-        <v>937</v>
+      <c r="I316" s="60" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -11550,13 +11914,13 @@
         <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11571,7 +11935,7 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -11579,13 +11943,13 @@
         <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11606,28 +11970,28 @@
         <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>914</v>
+        <v>965</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>929</v>
+        <v>901</v>
       </c>
       <c r="E319" s="18">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F319" s="31">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G319" s="32">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H319" s="18">
         <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>944</v>
+        <v>966</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -11635,13 +11999,13 @@
         <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>945</v>
+        <v>967</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>845</v>
+        <v>859</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>946</v>
+        <v>968</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -11653,10 +12017,10 @@
         <v>220</v>
       </c>
       <c r="H320" s="18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>916</v>
+        <v>938</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -11664,13 +12028,13 @@
         <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>947</v>
+        <v>969</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>949</v>
+        <v>971</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -11685,7 +12049,7 @@
         <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>950</v>
+        <v>972</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -11693,28 +12057,28 @@
         <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>951</v>
+        <v>973</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>952</v>
+        <v>974</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>929</v>
+        <v>901</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
       </c>
       <c r="F322" s="31">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G322" s="32">
         <v>215</v>
       </c>
       <c r="H322" s="18">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>953</v>
+        <v>975</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -11722,13 +12086,13 @@
         <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>954</v>
+        <v>976</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>146</v>
+        <v>977</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>949</v>
+        <v>971</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -11740,10 +12104,10 @@
         <v>220</v>
       </c>
       <c r="H323" s="18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>937</v>
+        <v>978</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -11751,57 +12115,57 @@
         <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>955</v>
+        <v>979</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>929</v>
+        <v>901</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
       </c>
       <c r="F324" s="31">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G324" s="32">
         <v>218</v>
       </c>
       <c r="H324" s="18">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>953</v>
+        <v>975</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="B325" s="36" t="s">
-        <v>957</v>
-      </c>
-      <c r="C325" s="36" t="s">
-        <v>914</v>
-      </c>
-      <c r="D325" s="36" t="s">
-        <v>958</v>
-      </c>
-      <c r="E325" s="36">
+      <c r="B325" s="18" t="s">
+        <v>981</v>
+      </c>
+      <c r="C325" s="18" t="s">
+        <v>936</v>
+      </c>
+      <c r="D325" s="18" t="s">
+        <v>982</v>
+      </c>
+      <c r="E325" s="18">
         <v>185</v>
       </c>
-      <c r="F325" s="36">
+      <c r="F325" s="31">
         <v>270</v>
       </c>
-      <c r="G325" s="36">
+      <c r="G325" s="32">
         <v>225</v>
       </c>
-      <c r="H325" s="61">
-        <v>5.2</v>
-      </c>
-      <c r="I325" s="61" t="s">
-        <v>944</v>
+      <c r="H325" s="18">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I325" s="11" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -11809,13 +12173,13 @@
         <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
-        <v>959</v>
+        <v>983</v>
       </c>
       <c r="C326" s="36" t="s">
-        <v>960</v>
+        <v>984</v>
       </c>
       <c r="D326" s="36" t="s">
-        <v>961</v>
+        <v>985</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -11824,11 +12188,11 @@
       <c r="G326" s="36">
         <v>220</v>
       </c>
-      <c r="H326" s="61">
-        <v>5.8</v>
-      </c>
-      <c r="I326" s="61" t="s">
-        <v>962</v>
+      <c r="H326" s="60">
+        <v>5.9</v>
+      </c>
+      <c r="I326" s="60" t="s">
+        <v>986</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -11836,13 +12200,13 @@
         <v>700</v>
       </c>
       <c r="B327" s="36" t="s">
-        <v>963</v>
+        <v>987</v>
       </c>
       <c r="C327" s="36" t="s">
-        <v>449</v>
+        <v>988</v>
       </c>
       <c r="D327" s="36" t="s">
-        <v>964</v>
+        <v>989</v>
       </c>
       <c r="E327" s="36">
         <v>150</v>
@@ -11853,23 +12217,39 @@
       <c r="G327" s="36">
         <v>208</v>
       </c>
-      <c r="H327" s="61">
+      <c r="H327" s="60">
         <v>5</v>
       </c>
-      <c r="I327" s="61"/>
+      <c r="I327" s="60"/>
     </row>
     <row r="328" spans="1:9">
       <c r="A328" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="B328" s="36"/>
-      <c r="C328" s="36"/>
-      <c r="D328" s="36"/>
-      <c r="E328" s="36"/>
-      <c r="F328" s="36"/>
-      <c r="G328" s="36"/>
-      <c r="H328" s="61"/>
-      <c r="I328" s="61"/>
+      <c r="B328" s="18" t="s">
+        <v>990</v>
+      </c>
+      <c r="C328" s="18" t="s">
+        <v>974</v>
+      </c>
+      <c r="D328" s="18" t="s">
+        <v>991</v>
+      </c>
+      <c r="E328" s="18">
+        <v>225</v>
+      </c>
+      <c r="F328" s="31">
+        <v>310</v>
+      </c>
+      <c r="G328" s="32">
+        <v>215</v>
+      </c>
+      <c r="H328" s="18">
+        <v>6</v>
+      </c>
+      <c r="I328" s="11" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="329" spans="1:9">
       <c r="A329" s="9" t="s">
@@ -11881,8 +12261,8 @@
       <c r="E329" s="36"/>
       <c r="F329" s="36"/>
       <c r="G329" s="36"/>
-      <c r="H329" s="61"/>
-      <c r="I329" s="61"/>
+      <c r="H329" s="60"/>
+      <c r="I329" s="60"/>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" s="9" t="s">
@@ -11894,8 +12274,8 @@
       <c r="E330" s="36"/>
       <c r="F330" s="36"/>
       <c r="G330" s="36"/>
-      <c r="H330" s="61"/>
-      <c r="I330" s="61"/>
+      <c r="H330" s="60"/>
+      <c r="I330" s="60"/>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" s="9" t="s">
@@ -11907,8 +12287,8 @@
       <c r="E331" s="36"/>
       <c r="F331" s="36"/>
       <c r="G331" s="36"/>
-      <c r="H331" s="61"/>
-      <c r="I331" s="61"/>
+      <c r="H331" s="60"/>
+      <c r="I331" s="60"/>
     </row>
     <row r="332" spans="1:9">
       <c r="A332" s="9" t="s">
@@ -11920,8 +12300,8 @@
       <c r="E332" s="36"/>
       <c r="F332" s="36"/>
       <c r="G332" s="36"/>
-      <c r="H332" s="61"/>
-      <c r="I332" s="61"/>
+      <c r="H332" s="60"/>
+      <c r="I332" s="60"/>
     </row>
     <row r="333" spans="1:9">
       <c r="A333" s="9" t="s">
@@ -11933,8 +12313,8 @@
       <c r="E333" s="36"/>
       <c r="F333" s="36"/>
       <c r="G333" s="36"/>
-      <c r="H333" s="61"/>
-      <c r="I333" s="61"/>
+      <c r="H333" s="60"/>
+      <c r="I333" s="60"/>
     </row>
     <row r="334" spans="1:9">
       <c r="A334" s="9" t="s">
@@ -11946,8 +12326,8 @@
       <c r="E334" s="36"/>
       <c r="F334" s="36"/>
       <c r="G334" s="36"/>
-      <c r="H334" s="61"/>
-      <c r="I334" s="61"/>
+      <c r="H334" s="60"/>
+      <c r="I334" s="60"/>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" s="9" t="s">
@@ -11959,8 +12339,8 @@
       <c r="E335" s="36"/>
       <c r="F335" s="36"/>
       <c r="G335" s="36"/>
-      <c r="H335" s="61"/>
-      <c r="I335" s="61"/>
+      <c r="H335" s="60"/>
+      <c r="I335" s="60"/>
     </row>
     <row r="336" spans="1:9">
       <c r="A336" s="9" t="s">
@@ -11972,8 +12352,8 @@
       <c r="E336" s="36"/>
       <c r="F336" s="36"/>
       <c r="G336" s="36"/>
-      <c r="H336" s="61"/>
-      <c r="I336" s="61"/>
+      <c r="H336" s="60"/>
+      <c r="I336" s="60"/>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" s="9" t="s">
@@ -11985,8 +12365,8 @@
       <c r="E337" s="36"/>
       <c r="F337" s="36"/>
       <c r="G337" s="36"/>
-      <c r="H337" s="61"/>
-      <c r="I337" s="61"/>
+      <c r="H337" s="60"/>
+      <c r="I337" s="60"/>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" s="9" t="s">
@@ -11998,8 +12378,8 @@
       <c r="E338" s="36"/>
       <c r="F338" s="36"/>
       <c r="G338" s="36"/>
-      <c r="H338" s="61"/>
-      <c r="I338" s="61"/>
+      <c r="H338" s="60"/>
+      <c r="I338" s="60"/>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" s="9" t="s">
@@ -12011,8 +12391,8 @@
       <c r="E339" s="36"/>
       <c r="F339" s="36"/>
       <c r="G339" s="36"/>
-      <c r="H339" s="61"/>
-      <c r="I339" s="61"/>
+      <c r="H339" s="60"/>
+      <c r="I339" s="60"/>
     </row>
     <row r="340" spans="1:9">
       <c r="A340" s="9" t="s">
@@ -12024,8 +12404,8 @@
       <c r="E340" s="36"/>
       <c r="F340" s="36"/>
       <c r="G340" s="36"/>
-      <c r="H340" s="61"/>
-      <c r="I340" s="61"/>
+      <c r="H340" s="60"/>
+      <c r="I340" s="60"/>
     </row>
     <row r="341" spans="1:9">
       <c r="A341" s="9" t="s">
@@ -12037,8 +12417,8 @@
       <c r="E341" s="36"/>
       <c r="F341" s="36"/>
       <c r="G341" s="36"/>
-      <c r="H341" s="61"/>
-      <c r="I341" s="61"/>
+      <c r="H341" s="60"/>
+      <c r="I341" s="60"/>
     </row>
     <row r="342" spans="1:9">
       <c r="A342" s="9" t="s">
@@ -12050,8 +12430,8 @@
       <c r="E342" s="36"/>
       <c r="F342" s="36"/>
       <c r="G342" s="36"/>
-      <c r="H342" s="61"/>
-      <c r="I342" s="61"/>
+      <c r="H342" s="60"/>
+      <c r="I342" s="60"/>
     </row>
     <row r="343" spans="1:9">
       <c r="A343" s="9" t="s">
@@ -12063,8 +12443,8 @@
       <c r="E343" s="36"/>
       <c r="F343" s="36"/>
       <c r="G343" s="36"/>
-      <c r="H343" s="61"/>
-      <c r="I343" s="61"/>
+      <c r="H343" s="60"/>
+      <c r="I343" s="60"/>
     </row>
     <row r="344" spans="1:9">
       <c r="A344" s="9" t="s">
@@ -12076,8 +12456,8 @@
       <c r="E344" s="36"/>
       <c r="F344" s="36"/>
       <c r="G344" s="36"/>
-      <c r="H344" s="61"/>
-      <c r="I344" s="61"/>
+      <c r="H344" s="60"/>
+      <c r="I344" s="60"/>
     </row>
     <row r="345" spans="1:9">
       <c r="A345" s="9" t="s">
@@ -12089,8 +12469,8 @@
       <c r="E345" s="36"/>
       <c r="F345" s="36"/>
       <c r="G345" s="36"/>
-      <c r="H345" s="61"/>
-      <c r="I345" s="61"/>
+      <c r="H345" s="60"/>
+      <c r="I345" s="60"/>
     </row>
     <row r="346" spans="1:9">
       <c r="A346" s="9" t="s">
@@ -12102,8 +12482,8 @@
       <c r="E346" s="36"/>
       <c r="F346" s="36"/>
       <c r="G346" s="36"/>
-      <c r="H346" s="61"/>
-      <c r="I346" s="61"/>
+      <c r="H346" s="60"/>
+      <c r="I346" s="60"/>
     </row>
     <row r="347" spans="1:9">
       <c r="A347" s="9" t="s">
@@ -12115,8 +12495,8 @@
       <c r="E347" s="36"/>
       <c r="F347" s="36"/>
       <c r="G347" s="36"/>
-      <c r="H347" s="61"/>
-      <c r="I347" s="61"/>
+      <c r="H347" s="60"/>
+      <c r="I347" s="60"/>
     </row>
     <row r="348" spans="1:9">
       <c r="A348" s="9" t="s">
@@ -12128,8 +12508,8 @@
       <c r="E348" s="36"/>
       <c r="F348" s="36"/>
       <c r="G348" s="36"/>
-      <c r="H348" s="61"/>
-      <c r="I348" s="61"/>
+      <c r="H348" s="60"/>
+      <c r="I348" s="60"/>
     </row>
     <row r="349" spans="1:9">
       <c r="A349" s="9" t="s">
@@ -12141,8 +12521,8 @@
       <c r="E349" s="36"/>
       <c r="F349" s="36"/>
       <c r="G349" s="36"/>
-      <c r="H349" s="61"/>
-      <c r="I349" s="61"/>
+      <c r="H349" s="60"/>
+      <c r="I349" s="60"/>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="9" t="s">
@@ -12154,8 +12534,8 @@
       <c r="E350" s="36"/>
       <c r="F350" s="36"/>
       <c r="G350" s="36"/>
-      <c r="H350" s="61"/>
-      <c r="I350" s="61"/>
+      <c r="H350" s="60"/>
+      <c r="I350" s="60"/>
     </row>
     <row r="351" spans="1:9">
       <c r="A351" s="9" t="s">
@@ -12167,8 +12547,8 @@
       <c r="E351" s="36"/>
       <c r="F351" s="36"/>
       <c r="G351" s="36"/>
-      <c r="H351" s="61"/>
-      <c r="I351" s="61"/>
+      <c r="H351" s="60"/>
+      <c r="I351" s="60"/>
     </row>
     <row r="352" spans="1:9">
       <c r="A352" s="9" t="s">
@@ -12180,8 +12560,8 @@
       <c r="E352" s="36"/>
       <c r="F352" s="36"/>
       <c r="G352" s="36"/>
-      <c r="H352" s="61"/>
-      <c r="I352" s="61"/>
+      <c r="H352" s="60"/>
+      <c r="I352" s="60"/>
     </row>
     <row r="353" spans="1:9">
       <c r="A353" s="9" t="s">
@@ -12193,8 +12573,8 @@
       <c r="E353" s="36"/>
       <c r="F353" s="36"/>
       <c r="G353" s="36"/>
-      <c r="H353" s="61"/>
-      <c r="I353" s="61"/>
+      <c r="H353" s="60"/>
+      <c r="I353" s="60"/>
     </row>
     <row r="354" spans="1:9">
       <c r="A354" s="9" t="s">
@@ -12206,8 +12586,8 @@
       <c r="E354" s="36"/>
       <c r="F354" s="36"/>
       <c r="G354" s="36"/>
-      <c r="H354" s="61"/>
-      <c r="I354" s="61"/>
+      <c r="H354" s="60"/>
+      <c r="I354" s="60"/>
     </row>
     <row r="355" spans="1:9">
       <c r="A355" s="9" t="s">
@@ -12219,8 +12599,8 @@
       <c r="E355" s="36"/>
       <c r="F355" s="36"/>
       <c r="G355" s="36"/>
-      <c r="H355" s="61"/>
-      <c r="I355" s="61"/>
+      <c r="H355" s="60"/>
+      <c r="I355" s="60"/>
     </row>
     <row r="356" spans="1:9">
       <c r="A356" s="9" t="s">
@@ -12232,8 +12612,8 @@
       <c r="E356" s="36"/>
       <c r="F356" s="36"/>
       <c r="G356" s="36"/>
-      <c r="H356" s="61"/>
-      <c r="I356" s="61"/>
+      <c r="H356" s="60"/>
+      <c r="I356" s="60"/>
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="9" t="s">
@@ -12245,8 +12625,8 @@
       <c r="E357" s="36"/>
       <c r="F357" s="36"/>
       <c r="G357" s="36"/>
-      <c r="H357" s="61"/>
-      <c r="I357" s="61"/>
+      <c r="H357" s="60"/>
+      <c r="I357" s="60"/>
     </row>
     <row r="358" spans="1:9">
       <c r="A358" s="9" t="s">
@@ -12258,8 +12638,8 @@
       <c r="E358" s="36"/>
       <c r="F358" s="36"/>
       <c r="G358" s="36"/>
-      <c r="H358" s="61"/>
-      <c r="I358" s="61"/>
+      <c r="H358" s="60"/>
+      <c r="I358" s="60"/>
     </row>
     <row r="359" spans="1:9">
       <c r="A359" s="9" t="s">
@@ -12271,8 +12651,8 @@
       <c r="E359" s="36"/>
       <c r="F359" s="36"/>
       <c r="G359" s="36"/>
-      <c r="H359" s="61"/>
-      <c r="I359" s="61"/>
+      <c r="H359" s="60"/>
+      <c r="I359" s="60"/>
     </row>
     <row r="360" spans="1:9">
       <c r="A360" s="9" t="s">
@@ -12284,8 +12664,8 @@
       <c r="E360" s="36"/>
       <c r="F360" s="36"/>
       <c r="G360" s="36"/>
-      <c r="H360" s="61"/>
-      <c r="I360" s="61"/>
+      <c r="H360" s="60"/>
+      <c r="I360" s="60"/>
     </row>
     <row r="361" spans="1:9">
       <c r="A361" s="9" t="s">
@@ -12297,8 +12677,8 @@
       <c r="E361" s="36"/>
       <c r="F361" s="36"/>
       <c r="G361" s="36"/>
-      <c r="H361" s="61"/>
-      <c r="I361" s="61"/>
+      <c r="H361" s="60"/>
+      <c r="I361" s="60"/>
     </row>
     <row r="362" spans="1:9">
       <c r="A362" s="9" t="s">
@@ -12310,8 +12690,8 @@
       <c r="E362" s="36"/>
       <c r="F362" s="36"/>
       <c r="G362" s="36"/>
-      <c r="H362" s="61"/>
-      <c r="I362" s="61"/>
+      <c r="H362" s="60"/>
+      <c r="I362" s="60"/>
     </row>
     <row r="363" spans="1:9">
       <c r="A363" s="9" t="s">
@@ -12323,8 +12703,8 @@
       <c r="E363" s="36"/>
       <c r="F363" s="36"/>
       <c r="G363" s="36"/>
-      <c r="H363" s="61"/>
-      <c r="I363" s="61"/>
+      <c r="H363" s="60"/>
+      <c r="I363" s="60"/>
     </row>
     <row r="364" spans="1:9">
       <c r="A364" s="9" t="s">
@@ -12336,8 +12716,8 @@
       <c r="E364" s="36"/>
       <c r="F364" s="36"/>
       <c r="G364" s="36"/>
-      <c r="H364" s="61"/>
-      <c r="I364" s="61"/>
+      <c r="H364" s="60"/>
+      <c r="I364" s="60"/>
     </row>
     <row r="365" spans="1:9">
       <c r="A365" s="9" t="s">
@@ -12349,8 +12729,8 @@
       <c r="E365" s="36"/>
       <c r="F365" s="36"/>
       <c r="G365" s="36"/>
-      <c r="H365" s="61"/>
-      <c r="I365" s="61"/>
+      <c r="H365" s="60"/>
+      <c r="I365" s="60"/>
     </row>
     <row r="366" spans="1:9">
       <c r="A366" s="9" t="s">
@@ -12362,8 +12742,8 @@
       <c r="E366" s="36"/>
       <c r="F366" s="36"/>
       <c r="G366" s="36"/>
-      <c r="H366" s="61"/>
-      <c r="I366" s="61"/>
+      <c r="H366" s="60"/>
+      <c r="I366" s="60"/>
     </row>
     <row r="367" spans="1:9">
       <c r="A367" s="9" t="s">
@@ -12375,8 +12755,8 @@
       <c r="E367" s="36"/>
       <c r="F367" s="36"/>
       <c r="G367" s="36"/>
-      <c r="H367" s="61"/>
-      <c r="I367" s="61"/>
+      <c r="H367" s="60"/>
+      <c r="I367" s="60"/>
     </row>
     <row r="368" spans="1:9">
       <c r="A368" s="9" t="s">
@@ -12388,8 +12768,8 @@
       <c r="E368" s="36"/>
       <c r="F368" s="36"/>
       <c r="G368" s="36"/>
-      <c r="H368" s="61"/>
-      <c r="I368" s="61"/>
+      <c r="H368" s="60"/>
+      <c r="I368" s="60"/>
     </row>
     <row r="369" spans="1:9">
       <c r="A369" s="9" t="s">
@@ -12401,8 +12781,8 @@
       <c r="E369" s="36"/>
       <c r="F369" s="36"/>
       <c r="G369" s="36"/>
-      <c r="H369" s="61"/>
-      <c r="I369" s="61"/>
+      <c r="H369" s="60"/>
+      <c r="I369" s="60"/>
     </row>
     <row r="370" spans="1:9">
       <c r="A370" s="9" t="s">
@@ -12414,8 +12794,8 @@
       <c r="E370" s="36"/>
       <c r="F370" s="36"/>
       <c r="G370" s="36"/>
-      <c r="H370" s="61"/>
-      <c r="I370" s="61"/>
+      <c r="H370" s="60"/>
+      <c r="I370" s="60"/>
     </row>
     <row r="371" spans="1:9">
       <c r="A371" s="9" t="s">
@@ -12427,8 +12807,8 @@
       <c r="E371" s="36"/>
       <c r="F371" s="36"/>
       <c r="G371" s="36"/>
-      <c r="H371" s="61"/>
-      <c r="I371" s="61"/>
+      <c r="H371" s="60"/>
+      <c r="I371" s="60"/>
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="9" t="s">
@@ -12440,8 +12820,8 @@
       <c r="E372" s="36"/>
       <c r="F372" s="36"/>
       <c r="G372" s="36"/>
-      <c r="H372" s="61"/>
-      <c r="I372" s="61"/>
+      <c r="H372" s="60"/>
+      <c r="I372" s="60"/>
     </row>
     <row r="373" spans="1:9">
       <c r="A373" s="9" t="s">
@@ -12453,8 +12833,8 @@
       <c r="E373" s="36"/>
       <c r="F373" s="36"/>
       <c r="G373" s="36"/>
-      <c r="H373" s="61"/>
-      <c r="I373" s="61"/>
+      <c r="H373" s="60"/>
+      <c r="I373" s="60"/>
     </row>
     <row r="374" spans="1:9">
       <c r="A374" s="9" t="s">
@@ -12466,8 +12846,8 @@
       <c r="E374" s="36"/>
       <c r="F374" s="36"/>
       <c r="G374" s="36"/>
-      <c r="H374" s="61"/>
-      <c r="I374" s="61"/>
+      <c r="H374" s="60"/>
+      <c r="I374" s="60"/>
     </row>
     <row r="375" spans="1:9">
       <c r="A375" s="9" t="s">
@@ -12479,8 +12859,8 @@
       <c r="E375" s="36"/>
       <c r="F375" s="36"/>
       <c r="G375" s="36"/>
-      <c r="H375" s="61"/>
-      <c r="I375" s="61"/>
+      <c r="H375" s="60"/>
+      <c r="I375" s="60"/>
     </row>
     <row r="376" spans="1:9">
       <c r="A376" s="9" t="s">
@@ -12492,8 +12872,8 @@
       <c r="E376" s="36"/>
       <c r="F376" s="36"/>
       <c r="G376" s="36"/>
-      <c r="H376" s="61"/>
-      <c r="I376" s="61"/>
+      <c r="H376" s="60"/>
+      <c r="I376" s="60"/>
     </row>
     <row r="377" spans="1:9">
       <c r="A377" s="9" t="s">
@@ -12505,8 +12885,8 @@
       <c r="E377" s="36"/>
       <c r="F377" s="36"/>
       <c r="G377" s="36"/>
-      <c r="H377" s="61"/>
-      <c r="I377" s="61"/>
+      <c r="H377" s="60"/>
+      <c r="I377" s="60"/>
     </row>
     <row r="378" spans="1:9">
       <c r="A378" s="9" t="s">
@@ -12518,8 +12898,8 @@
       <c r="E378" s="36"/>
       <c r="F378" s="36"/>
       <c r="G378" s="36"/>
-      <c r="H378" s="61"/>
-      <c r="I378" s="61"/>
+      <c r="H378" s="60"/>
+      <c r="I378" s="60"/>
     </row>
     <row r="379" spans="1:9">
       <c r="A379" s="9" t="s">
@@ -12531,8 +12911,8 @@
       <c r="E379" s="36"/>
       <c r="F379" s="36"/>
       <c r="G379" s="36"/>
-      <c r="H379" s="61"/>
-      <c r="I379" s="61"/>
+      <c r="H379" s="60"/>
+      <c r="I379" s="60"/>
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="9" t="s">
@@ -12544,8 +12924,8 @@
       <c r="E380" s="36"/>
       <c r="F380" s="36"/>
       <c r="G380" s="36"/>
-      <c r="H380" s="61"/>
-      <c r="I380" s="61"/>
+      <c r="H380" s="60"/>
+      <c r="I380" s="60"/>
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="9" t="s">
@@ -12557,8 +12937,8 @@
       <c r="E381" s="36"/>
       <c r="F381" s="36"/>
       <c r="G381" s="36"/>
-      <c r="H381" s="61"/>
-      <c r="I381" s="61"/>
+      <c r="H381" s="60"/>
+      <c r="I381" s="60"/>
     </row>
     <row r="382" spans="1:9">
       <c r="A382" s="9" t="s">
@@ -12570,8 +12950,8 @@
       <c r="E382" s="36"/>
       <c r="F382" s="36"/>
       <c r="G382" s="36"/>
-      <c r="H382" s="61"/>
-      <c r="I382" s="61"/>
+      <c r="H382" s="60"/>
+      <c r="I382" s="60"/>
     </row>
     <row r="383" spans="1:9">
       <c r="A383" s="9" t="s">
@@ -12583,8 +12963,8 @@
       <c r="E383" s="36"/>
       <c r="F383" s="36"/>
       <c r="G383" s="36"/>
-      <c r="H383" s="61"/>
-      <c r="I383" s="61"/>
+      <c r="H383" s="60"/>
+      <c r="I383" s="60"/>
     </row>
     <row r="384" spans="1:9">
       <c r="A384" s="9" t="s">
@@ -12596,8 +12976,8 @@
       <c r="E384" s="36"/>
       <c r="F384" s="36"/>
       <c r="G384" s="36"/>
-      <c r="H384" s="61"/>
-      <c r="I384" s="61"/>
+      <c r="H384" s="60"/>
+      <c r="I384" s="60"/>
     </row>
     <row r="385" spans="1:9">
       <c r="A385" s="9" t="s">
@@ -12609,8 +12989,8 @@
       <c r="E385" s="36"/>
       <c r="F385" s="36"/>
       <c r="G385" s="36"/>
-      <c r="H385" s="61"/>
-      <c r="I385" s="61"/>
+      <c r="H385" s="60"/>
+      <c r="I385" s="60"/>
     </row>
     <row r="386" spans="1:9">
       <c r="A386" s="9" t="s">
@@ -12622,8 +13002,8 @@
       <c r="E386" s="36"/>
       <c r="F386" s="36"/>
       <c r="G386" s="36"/>
-      <c r="H386" s="61"/>
-      <c r="I386" s="61"/>
+      <c r="H386" s="60"/>
+      <c r="I386" s="60"/>
     </row>
     <row r="387" spans="1:9">
       <c r="A387" s="9" t="s">
@@ -12635,8 +13015,8 @@
       <c r="E387" s="36"/>
       <c r="F387" s="36"/>
       <c r="G387" s="36"/>
-      <c r="H387" s="61"/>
-      <c r="I387" s="61"/>
+      <c r="H387" s="60"/>
+      <c r="I387" s="60"/>
     </row>
     <row r="388" spans="1:9">
       <c r="A388" s="9" t="s">
@@ -12648,8 +13028,8 @@
       <c r="E388" s="36"/>
       <c r="F388" s="36"/>
       <c r="G388" s="36"/>
-      <c r="H388" s="61"/>
-      <c r="I388" s="61"/>
+      <c r="H388" s="60"/>
+      <c r="I388" s="60"/>
     </row>
     <row r="389" spans="1:9">
       <c r="A389" s="9" t="s">
@@ -12661,8 +13041,8 @@
       <c r="E389" s="36"/>
       <c r="F389" s="36"/>
       <c r="G389" s="36"/>
-      <c r="H389" s="61"/>
-      <c r="I389" s="61"/>
+      <c r="H389" s="60"/>
+      <c r="I389" s="60"/>
     </row>
     <row r="390" spans="1:9">
       <c r="A390" s="9" t="s">
@@ -12674,8 +13054,8 @@
       <c r="E390" s="36"/>
       <c r="F390" s="36"/>
       <c r="G390" s="36"/>
-      <c r="H390" s="61"/>
-      <c r="I390" s="61"/>
+      <c r="H390" s="60"/>
+      <c r="I390" s="60"/>
     </row>
     <row r="391" spans="1:9">
       <c r="A391" s="9" t="s">
@@ -12687,8 +13067,8 @@
       <c r="E391" s="36"/>
       <c r="F391" s="36"/>
       <c r="G391" s="36"/>
-      <c r="H391" s="61"/>
-      <c r="I391" s="61"/>
+      <c r="H391" s="60"/>
+      <c r="I391" s="60"/>
     </row>
     <row r="392" spans="1:9">
       <c r="A392" s="9" t="s">
@@ -12700,8 +13080,8 @@
       <c r="E392" s="36"/>
       <c r="F392" s="36"/>
       <c r="G392" s="36"/>
-      <c r="H392" s="61"/>
-      <c r="I392" s="61"/>
+      <c r="H392" s="60"/>
+      <c r="I392" s="60"/>
     </row>
     <row r="393" spans="1:9">
       <c r="A393" s="9" t="s">
@@ -12713,8 +13093,8 @@
       <c r="E393" s="36"/>
       <c r="F393" s="36"/>
       <c r="G393" s="36"/>
-      <c r="H393" s="61"/>
-      <c r="I393" s="61"/>
+      <c r="H393" s="60"/>
+      <c r="I393" s="60"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -11,12 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="991">
   <si>
     <t>17.5*3*27</t>
   </si>
@@ -2324,126 +2324,122 @@
     <t>XC392</t>
   </si>
   <si>
-    <t>张：18962500118  盛泽温州商区13幢1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>XC001</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1*1半光横条</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>75*75*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*38</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*39</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.5*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>消半光珍珠点50*50*150</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>14*2*25</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>22*3*40</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>12*4*16</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*28</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*3*44</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>25梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>27梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>26梭T400无捻牛津</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*2*26</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>17*2*30</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>50S*50S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>18*2*27</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*40S</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>40S*75D 酷丝棉2/1</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">40S*150 酷丝棉28S平纹  </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>XC001</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>1*1半光横条</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>75*75*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*38</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*39</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17.5*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>消半光珍珠点50*50*150</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>14*2*25</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>22*3*40</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>12*4*16</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*28</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*3*44</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>25梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>27梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>26梭T400无捻牛津</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*26</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">50S*50S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>17*2*30</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>50S*50S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*40S弹力 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>18*2*27</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*40S</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75T 酷丝棉平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>40S*75D 酷丝棉2/1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*75D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉26S平纹  </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150 酷丝棉2/1 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">40S*150 酷丝棉24S平纹  </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2509,10 +2505,6 @@
   </si>
   <si>
     <t>100D*150T800</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">40S*150D 酷丝棉2/2 </t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3250,6 +3242,10 @@
   <si>
     <t>40S*17S*2</t>
     <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>张18962500118  盛泽镇温州商区13幢1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4155,16 +4151,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4184,7 +4180,7 @@
         <v>697</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>767</v>
+        <v>990</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4851,7 +4847,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4876,7 +4872,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -5151,7 +5147,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>98</v>
@@ -5323,7 +5319,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>116</v>
@@ -5528,7 +5524,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>134</v>
@@ -5793,7 +5789,7 @@
         <v>165</v>
       </c>
       <c r="H66" s="18">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I66" s="11"/>
     </row>
@@ -6055,7 +6051,7 @@
         <v>192</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>143</v>
@@ -6780,7 +6776,7 @@
         <v>267</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D106" s="22" t="s">
         <v>268</v>
@@ -7405,7 +7401,7 @@
         <v>329</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>147</v>
@@ -8090,7 +8086,7 @@
         <v>402</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>392</v>
@@ -8164,7 +8160,7 @@
         <v>410</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>411</v>
@@ -8245,7 +8241,7 @@
         <v>419</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>420</v>
@@ -8272,10 +8268,10 @@
         <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>412</v>
@@ -8312,13 +8308,13 @@
         <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
+        <v>783</v>
+      </c>
+      <c r="C167" s="18" t="s">
+        <v>784</v>
+      </c>
+      <c r="D167" s="18" t="s">
         <v>785</v>
-      </c>
-      <c r="C167" s="18" t="s">
-        <v>786</v>
-      </c>
-      <c r="D167" s="18" t="s">
-        <v>787</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8339,13 +8335,13 @@
         <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
+        <v>786</v>
+      </c>
+      <c r="C168" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="D168" s="18" t="s">
         <v>788</v>
-      </c>
-      <c r="C168" s="18" t="s">
-        <v>789</v>
-      </c>
-      <c r="D168" s="18" t="s">
-        <v>790</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8366,7 +8362,7 @@
         <v>425</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>426</v>
@@ -8393,7 +8389,7 @@
         <v>428</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>429</v>
@@ -8420,7 +8416,7 @@
         <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>237</v>
@@ -8474,7 +8470,7 @@
         <v>433</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>434</v>
@@ -8501,7 +8497,7 @@
         <v>436</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>437</v>
@@ -8528,7 +8524,7 @@
         <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8609,7 +8605,7 @@
         <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>418</v>
@@ -8663,7 +8659,7 @@
         <v>448</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>449</v>
@@ -8690,7 +8686,7 @@
         <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>443</v>
@@ -8717,7 +8713,7 @@
         <v>451</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>308</v>
@@ -8744,7 +8740,7 @@
         <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>308</v>
@@ -8798,13 +8794,13 @@
         <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
+        <v>800</v>
+      </c>
+      <c r="C185" s="18" t="s">
         <v>801</v>
       </c>
-      <c r="C185" s="18" t="s">
+      <c r="D185" s="18" t="s">
         <v>802</v>
-      </c>
-      <c r="D185" s="18" t="s">
-        <v>803</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8825,7 +8821,7 @@
         <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>308</v>
@@ -8849,13 +8845,13 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>435</v>
@@ -8879,13 +8875,13 @@
         <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
+        <v>806</v>
+      </c>
+      <c r="C188" s="18" t="s">
         <v>807</v>
       </c>
-      <c r="C188" s="18" t="s">
+      <c r="D188" s="18" t="s">
         <v>808</v>
-      </c>
-      <c r="D188" s="18" t="s">
-        <v>809</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8906,7 +8902,7 @@
         <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>443</v>
@@ -8933,13 +8929,13 @@
         <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="C190" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="C190" s="10" t="s">
+      <c r="D190" s="10" t="s">
         <v>812</v>
-      </c>
-      <c r="D190" s="10" t="s">
-        <v>813</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8960,10 +8956,10 @@
         <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>435</v>
@@ -9013,10 +9009,10 @@
         <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>147</v>
@@ -9040,7 +9036,7 @@
         <v>467</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>468</v>
@@ -9067,10 +9063,10 @@
         <v>469</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>470</v>
@@ -9094,10 +9090,10 @@
         <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>385</v>
@@ -9121,7 +9117,7 @@
         <v>472</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>473</v>
@@ -9148,13 +9144,13 @@
         <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
+        <v>821</v>
+      </c>
+      <c r="C199" s="45" t="s">
+        <v>822</v>
+      </c>
+      <c r="D199" s="45" t="s">
         <v>823</v>
-      </c>
-      <c r="C199" s="45" t="s">
-        <v>824</v>
-      </c>
-      <c r="D199" s="45" t="s">
-        <v>825</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -9332,7 +9328,7 @@
         <v>494</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9395,7 +9391,7 @@
         <v>499</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9417,10 +9413,10 @@
         <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>143</v>
@@ -9472,7 +9468,7 @@
         <v>505</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>143</v>
@@ -9585,10 +9581,10 @@
         <v>517</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D220" s="48" t="s">
         <v>518</v>
@@ -9606,7 +9602,7 @@
         <v>3.6</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9614,13 +9610,13 @@
         <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="C221" s="10" t="s">
+        <v>832</v>
+      </c>
+      <c r="D221" s="48" t="s">
         <v>833</v>
-      </c>
-      <c r="C221" s="10" t="s">
-        <v>834</v>
-      </c>
-      <c r="D221" s="48" t="s">
-        <v>835</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9635,7 +9631,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9643,13 +9639,13 @@
         <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>836</v>
+      </c>
+      <c r="D222" s="48" t="s">
         <v>837</v>
-      </c>
-      <c r="C222" s="10" t="s">
-        <v>838</v>
-      </c>
-      <c r="D222" s="48" t="s">
-        <v>839</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9688,7 +9684,7 @@
         <v>220</v>
       </c>
       <c r="H223" s="35">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I223" s="37"/>
     </row>
@@ -9697,13 +9693,13 @@
         <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
+        <v>838</v>
+      </c>
+      <c r="C224" s="35" t="s">
+        <v>839</v>
+      </c>
+      <c r="D224" s="35" t="s">
         <v>840</v>
-      </c>
-      <c r="C224" s="35" t="s">
-        <v>841</v>
-      </c>
-      <c r="D224" s="35" t="s">
-        <v>842</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9751,10 +9747,10 @@
         <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>435</v>
@@ -9778,10 +9774,10 @@
         <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>435</v>
@@ -9939,13 +9935,13 @@
         <v>542</v>
       </c>
       <c r="B234" s="68" t="s">
+        <v>843</v>
+      </c>
+      <c r="C234" s="68" t="s">
+        <v>844</v>
+      </c>
+      <c r="D234" s="49" t="s">
         <v>845</v>
-      </c>
-      <c r="C234" s="68" t="s">
-        <v>846</v>
-      </c>
-      <c r="D234" s="49" t="s">
-        <v>847</v>
       </c>
       <c r="E234" s="68">
         <v>190</v>
@@ -9960,7 +9956,7 @@
         <v>6</v>
       </c>
       <c r="I234" s="40" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9968,13 +9964,13 @@
         <v>543</v>
       </c>
       <c r="B235" s="27" t="s">
+        <v>847</v>
+      </c>
+      <c r="C235" s="27" t="s">
+        <v>848</v>
+      </c>
+      <c r="D235" s="27" t="s">
         <v>849</v>
-      </c>
-      <c r="C235" s="27" t="s">
-        <v>850</v>
-      </c>
-      <c r="D235" s="27" t="s">
-        <v>851</v>
       </c>
       <c r="E235" s="27">
         <v>155</v>
@@ -10010,13 +10006,13 @@
         <v>546</v>
       </c>
       <c r="B237" s="27" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C237" s="27" t="s">
         <v>547</v>
       </c>
       <c r="D237" s="27" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E237" s="27">
         <v>155</v>
@@ -10039,13 +10035,13 @@
         <v>548</v>
       </c>
       <c r="B238" s="27" t="s">
+        <v>852</v>
+      </c>
+      <c r="C238" s="27" t="s">
+        <v>853</v>
+      </c>
+      <c r="D238" s="27" t="s">
         <v>854</v>
-      </c>
-      <c r="C238" s="27" t="s">
-        <v>855</v>
-      </c>
-      <c r="D238" s="27" t="s">
-        <v>856</v>
       </c>
       <c r="E238" s="68">
         <v>190</v>
@@ -10060,7 +10056,7 @@
         <v>6</v>
       </c>
       <c r="I238" s="40" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -10068,13 +10064,13 @@
         <v>549</v>
       </c>
       <c r="B239" s="27" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D239" s="27" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E239" s="68">
         <v>180</v>
@@ -10089,7 +10085,7 @@
         <v>5.8</v>
       </c>
       <c r="I239" s="40" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -10097,13 +10093,13 @@
         <v>550</v>
       </c>
       <c r="B240" s="27" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C240" s="27" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D240" s="27" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E240" s="68">
         <v>190</v>
@@ -10118,7 +10114,7 @@
         <v>6</v>
       </c>
       <c r="I240" s="40" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -10126,10 +10122,10 @@
         <v>551</v>
       </c>
       <c r="B241" s="27" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C241" s="27" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>552</v>
@@ -10147,7 +10143,7 @@
         <v>5.3</v>
       </c>
       <c r="I241" s="20" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -10155,13 +10151,13 @@
         <v>553</v>
       </c>
       <c r="B242" s="27" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C242" s="27" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D242" s="27" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E242" s="68">
         <v>160</v>
@@ -10176,7 +10172,7 @@
         <v>5.4</v>
       </c>
       <c r="I242" s="40" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -10184,13 +10180,13 @@
         <v>554</v>
       </c>
       <c r="B243" s="27" t="s">
+        <v>867</v>
+      </c>
+      <c r="C243" s="27" t="s">
+        <v>868</v>
+      </c>
+      <c r="D243" s="27" t="s">
         <v>869</v>
-      </c>
-      <c r="C243" s="27" t="s">
-        <v>870</v>
-      </c>
-      <c r="D243" s="27" t="s">
-        <v>871</v>
       </c>
       <c r="E243" s="68">
         <v>190</v>
@@ -10205,7 +10201,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="40" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -10213,13 +10209,13 @@
         <v>555</v>
       </c>
       <c r="B244" s="27" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C244" s="27" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D244" s="27" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E244" s="27">
         <v>110</v>
@@ -10253,13 +10249,13 @@
         <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10280,7 +10276,7 @@
         <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>527</v>
@@ -10307,7 +10303,7 @@
         <v>559</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>560</v>
@@ -10334,10 +10330,10 @@
         <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>427</v>
@@ -10361,7 +10357,7 @@
         <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>152</v>
@@ -10388,7 +10384,7 @@
         <v>563</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>564</v>
@@ -10415,10 +10411,10 @@
         <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>427</v>
@@ -10442,7 +10438,7 @@
         <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>564</v>
@@ -10469,13 +10465,13 @@
         <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10490,7 +10486,7 @@
         <v>5.7</v>
       </c>
       <c r="I254" s="53" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10498,7 +10494,7 @@
         <v>568</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>569</v>
@@ -10525,13 +10521,13 @@
         <v>570</v>
       </c>
       <c r="B256" s="51" t="s">
+        <v>886</v>
+      </c>
+      <c r="C256" s="27" t="s">
+        <v>887</v>
+      </c>
+      <c r="D256" s="49" t="s">
         <v>888</v>
-      </c>
-      <c r="C256" s="27" t="s">
-        <v>889</v>
-      </c>
-      <c r="D256" s="49" t="s">
-        <v>890</v>
       </c>
       <c r="E256" s="51">
         <v>190</v>
@@ -10546,7 +10542,7 @@
         <v>5.5</v>
       </c>
       <c r="I256" s="53" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10554,13 +10550,13 @@
         <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10581,7 +10577,7 @@
         <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>152</v>
@@ -10640,7 +10636,7 @@
         <v>577</v>
       </c>
       <c r="D261" s="48" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10661,7 +10657,7 @@
         <v>578</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>579</v>
@@ -10679,7 +10675,7 @@
         <v>208</v>
       </c>
       <c r="H262" s="10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I262" s="59"/>
     </row>
@@ -10769,13 +10765,13 @@
         <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10796,13 +10792,13 @@
         <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="C267" s="10" t="s">
+        <v>896</v>
+      </c>
+      <c r="D267" s="48" t="s">
         <v>897</v>
-      </c>
-      <c r="C267" s="10" t="s">
-        <v>898</v>
-      </c>
-      <c r="D267" s="48" t="s">
-        <v>899</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10927,13 +10923,13 @@
         <v>603</v>
       </c>
       <c r="B276" s="36" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C276" s="36" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D276" s="27" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E276" s="36">
         <v>185</v>
@@ -10948,7 +10944,7 @@
         <v>6.2</v>
       </c>
       <c r="I276" s="11" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -10983,13 +10979,13 @@
         <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
+        <v>901</v>
+      </c>
+      <c r="C278" s="27" t="s">
+        <v>902</v>
+      </c>
+      <c r="D278" s="27" t="s">
         <v>903</v>
-      </c>
-      <c r="C278" s="27" t="s">
-        <v>904</v>
-      </c>
-      <c r="D278" s="27" t="s">
-        <v>905</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -11010,10 +11006,10 @@
         <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C279" s="48" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>143</v>
@@ -11037,13 +11033,13 @@
         <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="C280" s="48" t="s">
+        <v>907</v>
+      </c>
+      <c r="D280" s="10" t="s">
         <v>908</v>
-      </c>
-      <c r="C280" s="48" t="s">
-        <v>909</v>
-      </c>
-      <c r="D280" s="10" t="s">
-        <v>910</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -11089,7 +11085,7 @@
         <v>614</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C282" s="48" t="s">
         <v>615</v>
@@ -11116,10 +11112,10 @@
         <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C283" s="48" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11134,7 +11130,7 @@
         <v>208</v>
       </c>
       <c r="H283" s="10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I283" s="59"/>
     </row>
@@ -11143,13 +11139,13 @@
         <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
+        <v>912</v>
+      </c>
+      <c r="C284" s="36" t="s">
+        <v>913</v>
+      </c>
+      <c r="D284" s="36" t="s">
         <v>914</v>
-      </c>
-      <c r="C284" s="36" t="s">
-        <v>915</v>
-      </c>
-      <c r="D284" s="36" t="s">
-        <v>916</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11176,7 +11172,7 @@
         <v>620</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11197,10 +11193,10 @@
         <v>621</v>
       </c>
       <c r="B286" s="51" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C286" s="51" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D286" s="51" t="s">
         <v>622</v>
@@ -11224,13 +11220,13 @@
         <v>623</v>
       </c>
       <c r="B287" s="51" t="s">
+        <v>917</v>
+      </c>
+      <c r="C287" s="51" t="s">
+        <v>918</v>
+      </c>
+      <c r="D287" s="51" t="s">
         <v>919</v>
-      </c>
-      <c r="C287" s="51" t="s">
-        <v>920</v>
-      </c>
-      <c r="D287" s="51" t="s">
-        <v>921</v>
       </c>
       <c r="E287" s="51">
         <v>88</v>
@@ -11251,7 +11247,7 @@
         <v>624</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>625</v>
@@ -11299,7 +11295,7 @@
         <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -11334,10 +11330,10 @@
         <v>633</v>
       </c>
       <c r="B291" s="63" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C291" s="63" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D291" s="63" t="s">
         <v>634</v>
@@ -11361,7 +11357,7 @@
         <v>635</v>
       </c>
       <c r="B292" s="63" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C292" s="63" t="s">
         <v>636</v>
@@ -11388,10 +11384,10 @@
         <v>638</v>
       </c>
       <c r="B293" s="64" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C293" s="63" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D293" s="63" t="s">
         <v>39</v>
@@ -11415,13 +11411,13 @@
         <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11442,7 +11438,7 @@
         <v>640</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>641</v>
@@ -11490,13 +11486,13 @@
         <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
+        <v>930</v>
+      </c>
+      <c r="C297" s="18" t="s">
+        <v>931</v>
+      </c>
+      <c r="D297" s="33" t="s">
         <v>932</v>
-      </c>
-      <c r="C297" s="18" t="s">
-        <v>933</v>
-      </c>
-      <c r="D297" s="33" t="s">
-        <v>934</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11517,13 +11513,13 @@
         <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
+        <v>933</v>
+      </c>
+      <c r="C298" s="18" t="s">
+        <v>934</v>
+      </c>
+      <c r="D298" s="33" t="s">
         <v>935</v>
-      </c>
-      <c r="C298" s="18" t="s">
-        <v>936</v>
-      </c>
-      <c r="D298" s="33" t="s">
-        <v>937</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11538,7 +11534,7 @@
         <v>6</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -11546,13 +11542,13 @@
         <v>649</v>
       </c>
       <c r="B299" s="50" t="s">
+        <v>937</v>
+      </c>
+      <c r="C299" s="50" t="s">
+        <v>938</v>
+      </c>
+      <c r="D299" s="50" t="s">
         <v>939</v>
-      </c>
-      <c r="C299" s="50" t="s">
-        <v>940</v>
-      </c>
-      <c r="D299" s="50" t="s">
-        <v>941</v>
       </c>
       <c r="E299" s="50">
         <v>124</v>
@@ -11567,7 +11563,7 @@
         <v>5</v>
       </c>
       <c r="I299" s="54" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11601,13 +11597,13 @@
         <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="C302" s="11" t="s">
+        <v>942</v>
+      </c>
+      <c r="D302" s="11" t="s">
         <v>943</v>
-      </c>
-      <c r="C302" s="11" t="s">
-        <v>944</v>
-      </c>
-      <c r="D302" s="11" t="s">
-        <v>945</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11634,7 +11630,7 @@
         <v>655</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11658,7 +11654,7 @@
         <v>657</v>
       </c>
       <c r="C304" s="63" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D304" s="63" t="s">
         <v>658</v>
@@ -11676,7 +11672,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -11684,13 +11680,13 @@
         <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
+        <v>946</v>
+      </c>
+      <c r="C305" s="36" t="s">
+        <v>947</v>
+      </c>
+      <c r="D305" s="27" t="s">
         <v>948</v>
-      </c>
-      <c r="C305" s="36" t="s">
-        <v>949</v>
-      </c>
-      <c r="D305" s="27" t="s">
-        <v>950</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11779,7 +11775,7 @@
         <v>666</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>667</v>
@@ -11856,13 +11852,13 @@
         <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11877,7 +11873,7 @@
         <v>5</v>
       </c>
       <c r="I315" s="60" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -11885,13 +11881,13 @@
         <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
+        <v>953</v>
+      </c>
+      <c r="C316" s="36" t="s">
+        <v>954</v>
+      </c>
+      <c r="D316" s="11" t="s">
         <v>955</v>
-      </c>
-      <c r="C316" s="36" t="s">
-        <v>956</v>
-      </c>
-      <c r="D316" s="11" t="s">
-        <v>957</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11906,7 +11902,7 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="60" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -11914,13 +11910,13 @@
         <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="C317" s="11" t="s">
+        <v>958</v>
+      </c>
+      <c r="D317" s="11" t="s">
         <v>959</v>
-      </c>
-      <c r="C317" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="D317" s="11" t="s">
-        <v>961</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11935,7 +11931,7 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -11943,13 +11939,13 @@
         <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
+        <v>957</v>
+      </c>
+      <c r="C318" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="D318" s="11" t="s">
         <v>959</v>
-      </c>
-      <c r="C318" s="11" t="s">
-        <v>963</v>
-      </c>
-      <c r="D318" s="11" t="s">
-        <v>961</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11970,13 +11966,13 @@
         <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E319" s="18">
         <v>170</v>
@@ -11991,7 +11987,7 @@
         <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -11999,13 +11995,13 @@
         <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -12020,7 +12016,7 @@
         <v>5.8</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -12028,13 +12024,13 @@
         <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
+        <v>967</v>
+      </c>
+      <c r="C321" s="18" t="s">
+        <v>968</v>
+      </c>
+      <c r="D321" s="18" t="s">
         <v>969</v>
-      </c>
-      <c r="C321" s="18" t="s">
-        <v>970</v>
-      </c>
-      <c r="D321" s="18" t="s">
-        <v>971</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -12049,7 +12045,7 @@
         <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -12057,13 +12053,13 @@
         <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -12078,7 +12074,7 @@
         <v>5.7</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -12086,13 +12082,13 @@
         <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -12107,7 +12103,7 @@
         <v>4.8</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -12115,13 +12111,13 @@
         <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -12136,7 +12132,7 @@
         <v>6.6</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -12144,13 +12140,13 @@
         <v>684</v>
       </c>
       <c r="B325" s="18" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C325" s="18" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D325" s="18" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E325" s="18">
         <v>185</v>
@@ -12165,7 +12161,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I325" s="11" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -12173,13 +12169,13 @@
         <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
+        <v>981</v>
+      </c>
+      <c r="C326" s="36" t="s">
+        <v>982</v>
+      </c>
+      <c r="D326" s="36" t="s">
         <v>983</v>
-      </c>
-      <c r="C326" s="36" t="s">
-        <v>984</v>
-      </c>
-      <c r="D326" s="36" t="s">
-        <v>985</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -12192,7 +12188,7 @@
         <v>5.9</v>
       </c>
       <c r="I326" s="60" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -12200,13 +12196,13 @@
         <v>700</v>
       </c>
       <c r="B327" s="36" t="s">
+        <v>985</v>
+      </c>
+      <c r="C327" s="36" t="s">
+        <v>986</v>
+      </c>
+      <c r="D327" s="36" t="s">
         <v>987</v>
-      </c>
-      <c r="C327" s="36" t="s">
-        <v>988</v>
-      </c>
-      <c r="D327" s="36" t="s">
-        <v>989</v>
       </c>
       <c r="E327" s="36">
         <v>150</v>
@@ -12227,13 +12223,13 @@
         <v>701</v>
       </c>
       <c r="B328" s="18" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C328" s="18" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="D328" s="18" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="E328" s="18">
         <v>225</v>
@@ -12248,7 +12244,7 @@
         <v>6</v>
       </c>
       <c r="I328" s="11" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="329" spans="1:9">

--- a/产品规格.xlsx
+++ b/产品规格.xlsx
@@ -2324,6 +2324,10 @@
     <t>XC392</t>
   </si>
   <si>
+    <t>张18962500118  盛泽镇温州商区13幢1号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>XC001</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -2680,7 +2684,7 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>120D扁平3/3斜-44</t>
+    <t>120D扁平3/3斜</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -3242,10 +3246,6 @@
   <si>
     <t>40S*17S*2</t>
     <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>张18962500118  盛泽镇温州商区13幢1号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4151,16 +4151,16 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E2" s="10">
         <v>79</v>
@@ -4180,7 +4180,7 @@
         <v>697</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>990</v>
+        <v>767</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4847,7 +4847,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>46</v>
@@ -4872,7 +4872,7 @@
         <v>70</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>46</v>
@@ -5147,7 +5147,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>98</v>
@@ -5319,7 +5319,7 @@
         <v>115</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>116</v>
@@ -5524,7 +5524,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>134</v>
@@ -6051,7 +6051,7 @@
         <v>192</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>143</v>
@@ -6776,7 +6776,7 @@
         <v>267</v>
       </c>
       <c r="C106" s="22" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D106" s="22" t="s">
         <v>268</v>
@@ -7401,7 +7401,7 @@
         <v>329</v>
       </c>
       <c r="C131" s="24" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D131" s="24" t="s">
         <v>147</v>
@@ -8086,7 +8086,7 @@
         <v>402</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D158" s="27" t="s">
         <v>392</v>
@@ -8160,7 +8160,7 @@
         <v>410</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>411</v>
@@ -8241,7 +8241,7 @@
         <v>419</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C164" s="22" t="s">
         <v>420</v>
@@ -8268,10 +8268,10 @@
         <v>421</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D165" s="22" t="s">
         <v>412</v>
@@ -8308,13 +8308,13 @@
         <v>423</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D167" s="18" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E167" s="18">
         <v>80</v>
@@ -8335,13 +8335,13 @@
         <v>424</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D168" s="18" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E168" s="18">
         <v>110</v>
@@ -8362,7 +8362,7 @@
         <v>425</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C169" s="18" t="s">
         <v>426</v>
@@ -8389,7 +8389,7 @@
         <v>428</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>429</v>
@@ -8416,7 +8416,7 @@
         <v>430</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C171" s="18" t="s">
         <v>237</v>
@@ -8470,7 +8470,7 @@
         <v>433</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C173" s="18" t="s">
         <v>434</v>
@@ -8497,7 +8497,7 @@
         <v>436</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>437</v>
@@ -8524,7 +8524,7 @@
         <v>438</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C175" s="18" t="s">
         <v>32</v>
@@ -8605,7 +8605,7 @@
         <v>444</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>418</v>
@@ -8650,7 +8650,7 @@
         <v>208</v>
       </c>
       <c r="H179" s="18">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I179" s="32"/>
     </row>
@@ -8659,7 +8659,7 @@
         <v>448</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>449</v>
@@ -8686,7 +8686,7 @@
         <v>450</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C181" s="18" t="s">
         <v>443</v>
@@ -8704,7 +8704,7 @@
         <v>215</v>
       </c>
       <c r="H181" s="18">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I181" s="11"/>
     </row>
@@ -8713,7 +8713,7 @@
         <v>451</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C182" s="34" t="s">
         <v>308</v>
@@ -8731,7 +8731,7 @@
         <v>215</v>
       </c>
       <c r="H182" s="34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I182" s="11"/>
     </row>
@@ -8740,7 +8740,7 @@
         <v>453</v>
       </c>
       <c r="B183" s="34" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C183" s="34" t="s">
         <v>308</v>
@@ -8758,7 +8758,7 @@
         <v>215</v>
       </c>
       <c r="H183" s="34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I183" s="11"/>
     </row>
@@ -8785,7 +8785,7 @@
         <v>215</v>
       </c>
       <c r="H184" s="35">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I184" s="38"/>
     </row>
@@ -8794,13 +8794,13 @@
         <v>458</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C185" s="18" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D185" s="18" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E185" s="18">
         <v>112</v>
@@ -8821,7 +8821,7 @@
         <v>459</v>
       </c>
       <c r="B186" s="34" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C186" s="34" t="s">
         <v>308</v>
@@ -8839,19 +8839,19 @@
         <v>215</v>
       </c>
       <c r="H186" s="34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I186" s="11"/>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="9" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B187" s="18" t="s">
         <v>440</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D187" s="18" t="s">
         <v>435</v>
@@ -8875,13 +8875,13 @@
         <v>460</v>
       </c>
       <c r="B188" s="18" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C188" s="18" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E188" s="18">
         <v>110</v>
@@ -8902,7 +8902,7 @@
         <v>461</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C189" s="18" t="s">
         <v>443</v>
@@ -8920,7 +8920,7 @@
         <v>215</v>
       </c>
       <c r="H189" s="18">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I189" s="11"/>
     </row>
@@ -8929,13 +8929,13 @@
         <v>462</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D190" s="10" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E190" s="11">
         <v>152</v>
@@ -8947,7 +8947,7 @@
         <v>215</v>
       </c>
       <c r="H190" s="10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I190" s="11"/>
     </row>
@@ -8956,10 +8956,10 @@
         <v>463</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C191" s="18" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>435</v>
@@ -9009,10 +9009,10 @@
         <v>466</v>
       </c>
       <c r="B194" s="41" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C194" s="42" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D194" s="43" t="s">
         <v>147</v>
@@ -9036,7 +9036,7 @@
         <v>467</v>
       </c>
       <c r="B195" s="41" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C195" s="42" t="s">
         <v>468</v>
@@ -9063,10 +9063,10 @@
         <v>469</v>
       </c>
       <c r="B196" s="45" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C196" s="45" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D196" s="45" t="s">
         <v>470</v>
@@ -9090,10 +9090,10 @@
         <v>471</v>
       </c>
       <c r="B197" s="45" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C197" s="45" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D197" s="45" t="s">
         <v>385</v>
@@ -9117,7 +9117,7 @@
         <v>472</v>
       </c>
       <c r="B198" s="45" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C198" s="45" t="s">
         <v>473</v>
@@ -9144,13 +9144,13 @@
         <v>475</v>
       </c>
       <c r="B199" s="45" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C199" s="45" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D199" s="45" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E199" s="45">
         <v>95</v>
@@ -9328,7 +9328,7 @@
         <v>494</v>
       </c>
       <c r="C208" s="10" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D208" s="10" t="s">
         <v>39</v>
@@ -9391,7 +9391,7 @@
         <v>499</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D211" s="10" t="s">
         <v>39</v>
@@ -9413,10 +9413,10 @@
         <v>500</v>
       </c>
       <c r="B212" s="35" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C212" s="35" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D212" s="35" t="s">
         <v>143</v>
@@ -9468,7 +9468,7 @@
         <v>505</v>
       </c>
       <c r="C214" s="35" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D214" s="35" t="s">
         <v>143</v>
@@ -9581,10 +9581,10 @@
         <v>517</v>
       </c>
       <c r="B220" s="10" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C220" s="10" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D220" s="48" t="s">
         <v>518</v>
@@ -9599,10 +9599,10 @@
         <v>215</v>
       </c>
       <c r="H220" s="10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I220" s="11" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -9610,13 +9610,13 @@
         <v>519</v>
       </c>
       <c r="B221" s="10" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D221" s="48" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E221" s="10">
         <v>100</v>
@@ -9631,7 +9631,7 @@
         <v>3.3</v>
       </c>
       <c r="I221" s="37" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -9639,13 +9639,13 @@
         <v>520</v>
       </c>
       <c r="B222" s="10" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D222" s="48" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E222" s="10">
         <v>115</v>
@@ -9657,7 +9657,7 @@
         <v>215</v>
       </c>
       <c r="H222" s="10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I222" s="37"/>
     </row>
@@ -9693,13 +9693,13 @@
         <v>524</v>
       </c>
       <c r="B224" s="35" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E224" s="35">
         <v>120</v>
@@ -9747,10 +9747,10 @@
         <v>528</v>
       </c>
       <c r="B226" s="35" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C226" s="35" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D226" s="35" t="s">
         <v>435</v>
@@ -9765,7 +9765,7 @@
         <v>215</v>
       </c>
       <c r="H226" s="35">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I226" s="37"/>
     </row>
@@ -9774,10 +9774,10 @@
         <v>529</v>
       </c>
       <c r="B227" s="35" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C227" s="35" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D227" s="35" t="s">
         <v>435</v>
@@ -9792,7 +9792,7 @@
         <v>215</v>
       </c>
       <c r="H227" s="35">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I227" s="37"/>
     </row>
@@ -9846,7 +9846,7 @@
         <v>215</v>
       </c>
       <c r="H229" s="35">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I229" s="11"/>
     </row>
@@ -9873,7 +9873,7 @@
         <v>215</v>
       </c>
       <c r="H230" s="27">
-        <v>5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I230" s="20"/>
     </row>
@@ -9935,13 +9935,13 @@
         <v>542</v>
       </c>
       <c r="B234" s="68" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C234" s="68" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D234" s="49" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E234" s="68">
         <v>190</v>
@@ -9956,7 +9956,7 @@
         <v>6</v>
       </c>
       <c r="I234" s="40" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -9964,13 +9964,13 @@
         <v>543</v>
       </c>
       <c r="B235" s="27" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C235" s="27" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D235" s="27" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E235" s="27">
         <v>155</v>
@@ -10006,13 +10006,13 @@
         <v>546</v>
       </c>
       <c r="B237" s="27" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C237" s="27" t="s">
         <v>547</v>
       </c>
       <c r="D237" s="27" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E237" s="27">
         <v>155</v>
@@ -10024,7 +10024,7 @@
         <v>218</v>
       </c>
       <c r="H237" s="27">
-        <v>5.0999999999999996</v>
+        <v>5.2</v>
       </c>
       <c r="I237" s="20" t="s">
         <v>544</v>
@@ -10035,13 +10035,13 @@
         <v>548</v>
       </c>
       <c r="B238" s="27" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C238" s="27" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D238" s="27" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E238" s="68">
         <v>190</v>
@@ -10056,7 +10056,7 @@
         <v>6</v>
       </c>
       <c r="I238" s="40" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -10064,13 +10064,13 @@
         <v>549</v>
       </c>
       <c r="B239" s="27" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D239" s="27" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E239" s="68">
         <v>180</v>
@@ -10082,10 +10082,10 @@
         <v>220</v>
       </c>
       <c r="H239" s="27">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I239" s="40" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -10093,13 +10093,13 @@
         <v>550</v>
       </c>
       <c r="B240" s="27" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C240" s="27" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D240" s="27" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E240" s="68">
         <v>190</v>
@@ -10111,10 +10111,10 @@
         <v>225</v>
       </c>
       <c r="H240" s="39">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I240" s="40" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -10122,10 +10122,10 @@
         <v>551</v>
       </c>
       <c r="B241" s="27" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C241" s="27" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>552</v>
@@ -10143,7 +10143,7 @@
         <v>5.3</v>
       </c>
       <c r="I241" s="20" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -10151,13 +10151,13 @@
         <v>553</v>
       </c>
       <c r="B242" s="27" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C242" s="27" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D242" s="27" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E242" s="68">
         <v>160</v>
@@ -10169,10 +10169,10 @@
         <v>225</v>
       </c>
       <c r="H242" s="39">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I242" s="40" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -10180,13 +10180,13 @@
         <v>554</v>
       </c>
       <c r="B243" s="27" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C243" s="27" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D243" s="27" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E243" s="68">
         <v>190</v>
@@ -10201,7 +10201,7 @@
         <v>5.6</v>
       </c>
       <c r="I243" s="40" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -10209,13 +10209,13 @@
         <v>555</v>
       </c>
       <c r="B244" s="27" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C244" s="27" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D244" s="27" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E244" s="27">
         <v>110</v>
@@ -10249,13 +10249,13 @@
         <v>557</v>
       </c>
       <c r="B246" s="18" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C246" s="18" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D246" s="33" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E246" s="18">
         <v>112</v>
@@ -10276,7 +10276,7 @@
         <v>558</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C247" s="18" t="s">
         <v>527</v>
@@ -10303,7 +10303,7 @@
         <v>559</v>
       </c>
       <c r="B248" s="18" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C248" s="18" t="s">
         <v>560</v>
@@ -10321,7 +10321,7 @@
         <v>215</v>
       </c>
       <c r="H248" s="18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I248" s="56"/>
     </row>
@@ -10330,10 +10330,10 @@
         <v>561</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C249" s="18" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>427</v>
@@ -10357,7 +10357,7 @@
         <v>562</v>
       </c>
       <c r="B250" s="18" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C250" s="18" t="s">
         <v>152</v>
@@ -10384,7 +10384,7 @@
         <v>563</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C251" s="18" t="s">
         <v>564</v>
@@ -10411,10 +10411,10 @@
         <v>565</v>
       </c>
       <c r="B252" s="18" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C252" s="18" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D252" s="18" t="s">
         <v>427</v>
@@ -10438,7 +10438,7 @@
         <v>566</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C253" s="18" t="s">
         <v>564</v>
@@ -10465,13 +10465,13 @@
         <v>567</v>
       </c>
       <c r="B254" s="18" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C254" s="18" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D254" s="18" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E254" s="18">
         <v>190</v>
@@ -10486,7 +10486,7 @@
         <v>5.7</v>
       </c>
       <c r="I254" s="53" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -10494,7 +10494,7 @@
         <v>568</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C255" s="18" t="s">
         <v>569</v>
@@ -10521,13 +10521,13 @@
         <v>570</v>
       </c>
       <c r="B256" s="51" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C256" s="27" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D256" s="49" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E256" s="51">
         <v>190</v>
@@ -10539,10 +10539,10 @@
         <v>215</v>
       </c>
       <c r="H256" s="59">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I256" s="53" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -10550,13 +10550,13 @@
         <v>571</v>
       </c>
       <c r="B257" s="36" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C257" s="36" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D257" s="36" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E257" s="36">
         <v>118</v>
@@ -10577,7 +10577,7 @@
         <v>572</v>
       </c>
       <c r="B258" s="18" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C258" s="18" t="s">
         <v>152</v>
@@ -10636,7 +10636,7 @@
         <v>577</v>
       </c>
       <c r="D261" s="48" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="E261" s="10">
         <v>108</v>
@@ -10657,7 +10657,7 @@
         <v>578</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C262" s="10" t="s">
         <v>579</v>
@@ -10729,7 +10729,7 @@
         <v>208</v>
       </c>
       <c r="H264" s="10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I264" s="59"/>
     </row>
@@ -10765,13 +10765,13 @@
         <v>593</v>
       </c>
       <c r="B266" s="35" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E266" s="35">
         <v>78</v>
@@ -10783,7 +10783,7 @@
         <v>215</v>
       </c>
       <c r="H266" s="35">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I266" s="59"/>
     </row>
@@ -10792,13 +10792,13 @@
         <v>594</v>
       </c>
       <c r="B267" s="10" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C267" s="10" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D267" s="48" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E267" s="10">
         <v>60</v>
@@ -10923,13 +10923,13 @@
         <v>603</v>
       </c>
       <c r="B276" s="36" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C276" s="36" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D276" s="27" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E276" s="36">
         <v>185</v>
@@ -10941,10 +10941,10 @@
         <v>215</v>
       </c>
       <c r="H276" s="60">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I276" s="11" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -10979,13 +10979,13 @@
         <v>608</v>
       </c>
       <c r="B278" s="27" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C278" s="27" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="E278" s="27">
         <v>159</v>
@@ -10997,7 +10997,7 @@
         <v>212</v>
       </c>
       <c r="H278" s="27">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I278" s="59"/>
     </row>
@@ -11006,10 +11006,10 @@
         <v>609</v>
       </c>
       <c r="B279" s="10" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C279" s="48" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D279" s="10" t="s">
         <v>143</v>
@@ -11033,13 +11033,13 @@
         <v>610</v>
       </c>
       <c r="B280" s="10" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C280" s="48" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D280" s="10" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="E280" s="10"/>
       <c r="F280" s="9">
@@ -11085,7 +11085,7 @@
         <v>614</v>
       </c>
       <c r="B282" s="10" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C282" s="48" t="s">
         <v>615</v>
@@ -11112,10 +11112,10 @@
         <v>616</v>
       </c>
       <c r="B283" s="10" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C283" s="48" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D283" s="10" t="s">
         <v>39</v>
@@ -11139,13 +11139,13 @@
         <v>617</v>
       </c>
       <c r="B284" s="27" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C284" s="36" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D284" s="36" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E284" s="36">
         <v>80</v>
@@ -11172,7 +11172,7 @@
         <v>620</v>
       </c>
       <c r="D285" s="36" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="E285" s="10">
         <v>73</v>
@@ -11193,10 +11193,10 @@
         <v>621</v>
       </c>
       <c r="B286" s="51" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C286" s="51" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D286" s="51" t="s">
         <v>622</v>
@@ -11220,13 +11220,13 @@
         <v>623</v>
       </c>
       <c r="B287" s="51" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C287" s="51" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D287" s="51" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E287" s="51">
         <v>88</v>
@@ -11247,7 +11247,7 @@
         <v>624</v>
       </c>
       <c r="B288" s="27" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C288" s="27" t="s">
         <v>625</v>
@@ -11295,7 +11295,7 @@
         <v>4</v>
       </c>
       <c r="I289" s="11" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -11330,10 +11330,10 @@
         <v>633</v>
       </c>
       <c r="B291" s="63" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C291" s="63" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D291" s="63" t="s">
         <v>634</v>
@@ -11357,7 +11357,7 @@
         <v>635</v>
       </c>
       <c r="B292" s="63" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C292" s="63" t="s">
         <v>636</v>
@@ -11384,10 +11384,10 @@
         <v>638</v>
       </c>
       <c r="B293" s="64" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C293" s="63" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D293" s="63" t="s">
         <v>39</v>
@@ -11411,13 +11411,13 @@
         <v>639</v>
       </c>
       <c r="B294" s="18" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C294" s="18" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D294" s="18" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E294" s="18">
         <v>150</v>
@@ -11429,7 +11429,7 @@
         <v>215</v>
       </c>
       <c r="H294" s="18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I294" s="60"/>
     </row>
@@ -11438,7 +11438,7 @@
         <v>640</v>
       </c>
       <c r="B295" s="10" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C295" s="10" t="s">
         <v>641</v>
@@ -11486,13 +11486,13 @@
         <v>647</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C297" s="18" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D297" s="33" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="E297" s="18">
         <v>125</v>
@@ -11513,13 +11513,13 @@
         <v>648</v>
       </c>
       <c r="B298" s="18" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C298" s="18" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D298" s="33" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E298" s="18">
         <v>190</v>
@@ -11534,7 +11534,7 @@
         <v>6</v>
       </c>
       <c r="I298" s="11" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="299" spans="1:9">
@@ -11542,13 +11542,13 @@
         <v>649</v>
       </c>
       <c r="B299" s="50" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C299" s="50" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D299" s="50" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E299" s="50">
         <v>124</v>
@@ -11563,7 +11563,7 @@
         <v>5</v>
       </c>
       <c r="I299" s="54" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -11597,13 +11597,13 @@
         <v>652</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C302" s="11" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D302" s="11" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E302" s="11">
         <v>150</v>
@@ -11615,7 +11615,7 @@
         <v>215</v>
       </c>
       <c r="H302" s="11">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="I302" s="60"/>
     </row>
@@ -11630,7 +11630,7 @@
         <v>655</v>
       </c>
       <c r="D303" s="10" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E303" s="11">
         <v>140</v>
@@ -11642,7 +11642,7 @@
         <v>215</v>
       </c>
       <c r="H303" s="10">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I303" s="60"/>
     </row>
@@ -11654,7 +11654,7 @@
         <v>657</v>
       </c>
       <c r="C304" s="63" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D304" s="63" t="s">
         <v>658</v>
@@ -11672,7 +11672,7 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="I304" s="37" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -11680,13 +11680,13 @@
         <v>659</v>
       </c>
       <c r="B305" s="36" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C305" s="36" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D305" s="27" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="E305" s="36">
         <v>215</v>
@@ -11775,7 +11775,7 @@
         <v>666</v>
       </c>
       <c r="C311" s="35" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D311" s="35" t="s">
         <v>667</v>
@@ -11790,7 +11790,7 @@
         <v>215</v>
       </c>
       <c r="H311" s="35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I311" s="60"/>
     </row>
@@ -11852,13 +11852,13 @@
         <v>674</v>
       </c>
       <c r="B315" s="36" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C315" s="36" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="E315" s="36">
         <v>116</v>
@@ -11873,7 +11873,7 @@
         <v>5</v>
       </c>
       <c r="I315" s="60" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="316" spans="1:9">
@@ -11881,13 +11881,13 @@
         <v>675</v>
       </c>
       <c r="B316" s="36" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C316" s="36" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E316" s="36">
         <v>160</v>
@@ -11902,7 +11902,7 @@
         <v>5.2</v>
       </c>
       <c r="I316" s="60" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -11910,13 +11910,13 @@
         <v>676</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C317" s="11" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D317" s="11" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E317" s="11">
         <v>110</v>
@@ -11931,7 +11931,7 @@
         <v>3.7</v>
       </c>
       <c r="I317" s="11" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="318" spans="1:9">
@@ -11939,13 +11939,13 @@
         <v>677</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C318" s="11" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E318" s="11">
         <v>110</v>
@@ -11966,13 +11966,13 @@
         <v>678</v>
       </c>
       <c r="B319" s="18" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C319" s="18" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D319" s="18" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E319" s="18">
         <v>170</v>
@@ -11987,7 +11987,7 @@
         <v>5.5</v>
       </c>
       <c r="I319" s="11" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -11995,13 +11995,13 @@
         <v>679</v>
       </c>
       <c r="B320" s="18" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C320" s="18" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D320" s="18" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E320" s="18">
         <v>182</v>
@@ -12016,7 +12016,7 @@
         <v>5.8</v>
       </c>
       <c r="I320" s="11" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="321" spans="1:9">
@@ -12024,13 +12024,13 @@
         <v>680</v>
       </c>
       <c r="B321" s="18" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C321" s="18" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E321" s="18">
         <v>138</v>
@@ -12045,7 +12045,7 @@
         <v>4.5</v>
       </c>
       <c r="I321" s="11" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="322" spans="1:9">
@@ -12053,13 +12053,13 @@
         <v>681</v>
       </c>
       <c r="B322" s="18" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C322" s="18" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E322" s="18">
         <v>225</v>
@@ -12074,7 +12074,7 @@
         <v>5.7</v>
       </c>
       <c r="I322" s="11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="323" spans="1:9">
@@ -12082,13 +12082,13 @@
         <v>682</v>
       </c>
       <c r="B323" s="18" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C323" s="18" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E323" s="18">
         <v>150</v>
@@ -12103,7 +12103,7 @@
         <v>4.8</v>
       </c>
       <c r="I323" s="11" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="324" spans="1:9">
@@ -12111,13 +12111,13 @@
         <v>683</v>
       </c>
       <c r="B324" s="18" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C324" s="18" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E324" s="18">
         <v>220</v>
@@ -12132,7 +12132,7 @@
         <v>6.6</v>
       </c>
       <c r="I324" s="11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="325" spans="1:9">
@@ -12140,13 +12140,13 @@
         <v>684</v>
       </c>
       <c r="B325" s="18" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C325" s="18" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D325" s="18" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E325" s="18">
         <v>185</v>
@@ -12161,7 +12161,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I325" s="11" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="326" spans="1:9">
@@ -12169,13 +12169,13 @@
         <v>699</v>
       </c>
       <c r="B326" s="36" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C326" s="36" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D326" s="36" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E326" s="36">
         <v>145</v>
@@ -12188,7 +12188,7 @@
         <v>5.9</v>
       </c>
       <c r="I326" s="60" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="327" spans="1:9">
@@ -12196,13 +12196,13 @@
         <v>700</v>
       </c>
       <c r="B327" s="36" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C327" s="36" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D327" s="36" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E327" s="36">
         <v>150</v>
@@ -12223,13 +12223,13 @@
         <v>701</v>
       </c>
       <c r="B328" s="18" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C328" s="18" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D328" s="18" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="E328" s="18">
         <v>225</v>
@@ -12244,7 +12244,7 @@
         <v>6</v>
       </c>
       <c r="I328" s="11" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="329" spans="1:9">
